--- a/database/event/8413/event_8413_evp_summary.xlsx
+++ b/database/event/8413/event_8413_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -504,26 +492,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.6315</v>
+        <v>9.5311</v>
       </c>
       <c r="C2" t="n">
-        <v>4.407819900000001</v>
+        <v>2.4444</v>
       </c>
       <c r="D2" t="n">
-        <v>5.910263696864322</v>
+        <v>3.429</v>
       </c>
       <c r="E2" t="n">
-        <v>51.3803</v>
+        <v>9.5311</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>51.38031331656574</v>
+        <v>9.5311</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -532,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>51.38031331656574</v>
+        <v>7.3316</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -541,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>51.3803</v>
+        <v>7.3316</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -550,26 +538,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.5249</v>
+        <v>7.5766</v>
       </c>
       <c r="C3" t="n">
-        <v>4.363623540000001</v>
+        <v>1.9431</v>
       </c>
       <c r="D3" t="n">
-        <v>5.777548726482923</v>
+        <v>2.6394</v>
       </c>
       <c r="E3" t="n">
-        <v>50.2266</v>
+        <v>7.5766</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>50.2265683891418</v>
+        <v>7.5766</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -578,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>50.2265683891418</v>
+        <v>5.8281</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -587,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>50.2266</v>
+        <v>5.8281</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -596,26 +584,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.2774</v>
+        <v>6.3006</v>
       </c>
       <c r="C4" t="n">
-        <v>3.43181004</v>
+        <v>1.6159</v>
       </c>
       <c r="D4" t="n">
-        <v>3.504056059406361</v>
+        <v>2.1239</v>
       </c>
       <c r="E4" t="n">
-        <v>30.4622</v>
+        <v>6.3006</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>30.46217689180757</v>
+        <v>6.3006</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -624,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>30.46217689180757</v>
+        <v>4.8466</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -633,7 +621,7 @@
         <v>206</v>
       </c>
       <c r="M4" t="n">
-        <v>30.4622</v>
+        <v>4.8466</v>
       </c>
       <c r="N4" t="n">
         <v>206</v>
@@ -642,26 +630,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.116300000000001</v>
+        <v>5.4871</v>
       </c>
       <c r="C5" t="n">
-        <v>3.365017980000001</v>
+        <v>1.4073</v>
       </c>
       <c r="D5" t="n">
-        <v>3.374045753378502</v>
+        <v>1.7953</v>
       </c>
       <c r="E5" t="n">
-        <v>29.3319</v>
+        <v>5.4871</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>29.33194470578209</v>
+        <v>5.4871</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -670,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>29.33194470578209</v>
+        <v>4.2208</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -679,7 +667,7 @@
         <v>206</v>
       </c>
       <c r="M5" t="n">
-        <v>29.3319</v>
+        <v>4.2208</v>
       </c>
       <c r="N5" t="n">
         <v>206</v>
@@ -688,26 +676,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.7322</v>
+        <v>5.2755</v>
       </c>
       <c r="C6" t="n">
-        <v>3.20577012</v>
+        <v>1.353</v>
       </c>
       <c r="D6" t="n">
-        <v>3.078977280183286</v>
+        <v>1.7098</v>
       </c>
       <c r="E6" t="n">
-        <v>26.7668</v>
+        <v>5.2755</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>26.76679509821816</v>
+        <v>5.2755</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -716,90 +704,90 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>26.76679509821816</v>
+        <v>4.0581</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="M6" t="n">
-        <v>26.7668</v>
+        <v>4.0581</v>
       </c>
       <c r="N6" t="n">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.4531</v>
+        <v>3.9962</v>
       </c>
       <c r="C7" t="n">
-        <v>3.09005526</v>
+        <v>1.0249</v>
       </c>
       <c r="D7" t="n">
-        <v>2.87714912500457</v>
+        <v>1.193</v>
       </c>
       <c r="E7" t="n">
-        <v>25.0122</v>
+        <v>3.9962</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.8824</v>
       </c>
       <c r="G7" t="n">
-        <v>25.01222129558247</v>
+        <v>3.1137</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.8824</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.8824</v>
       </c>
       <c r="J7" t="n">
-        <v>25.01222129558247</v>
+        <v>2.3952</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L7" t="n">
-        <v>206</v>
+        <v>101</v>
       </c>
       <c r="M7" t="n">
-        <v>25.0122</v>
+        <v>3.2776</v>
       </c>
       <c r="N7" t="n">
-        <v>206</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.2413</v>
+        <v>3.9757</v>
       </c>
       <c r="C8" t="n">
-        <v>3.00224298</v>
+        <v>1.0196</v>
       </c>
       <c r="D8" t="n">
-        <v>2.730699434722897</v>
+        <v>1.1847</v>
       </c>
       <c r="E8" t="n">
-        <v>23.7391</v>
+        <v>3.9757</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>23.73907489167861</v>
+        <v>3.9757</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -808,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>23.73907489167861</v>
+        <v>3.0582</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -817,7 +805,7 @@
         <v>190</v>
       </c>
       <c r="M8" t="n">
-        <v>23.7391</v>
+        <v>3.0582</v>
       </c>
       <c r="N8" t="n">
         <v>190</v>
@@ -826,26 +814,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lauNX</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.2531</v>
+        <v>3.7948</v>
       </c>
       <c r="C9" t="n">
-        <v>2.59253526</v>
+        <v>0.9732</v>
       </c>
       <c r="D9" t="n">
-        <v>2.117156008950317</v>
+        <v>1.1117</v>
       </c>
       <c r="E9" t="n">
-        <v>18.4053</v>
+        <v>3.7948</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>18.40529368218041</v>
+        <v>3.7948</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -854,19 +842,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>18.40529368218041</v>
+        <v>2.9191</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="M9" t="n">
-        <v>18.4053</v>
+        <v>2.9191</v>
       </c>
       <c r="N9" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -876,40 +864,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.8948</v>
+        <v>2.7689</v>
       </c>
       <c r="C10" t="n">
-        <v>2.44398408</v>
+        <v>0.7101</v>
       </c>
       <c r="D10" t="n">
-        <v>1.92057719122462</v>
+        <v>0.6972</v>
       </c>
       <c r="E10" t="n">
-        <v>16.6964</v>
+        <v>2.7689</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.8764</v>
       </c>
       <c r="G10" t="n">
-        <v>16.69635449364554</v>
+        <v>1.8925</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.8764</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.8764</v>
       </c>
       <c r="J10" t="n">
-        <v>16.69635449364554</v>
+        <v>1.4558</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L10" t="n">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>16.6964</v>
+        <v>2.3322</v>
       </c>
       <c r="N10" t="n">
         <v>167</v>
@@ -918,118 +906,118 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.8528</v>
+        <v>2.1181</v>
       </c>
       <c r="C11" t="n">
-        <v>2.42657088</v>
+        <v>0.5432</v>
       </c>
       <c r="D11" t="n">
-        <v>1.898336084219105</v>
+        <v>0.4343</v>
       </c>
       <c r="E11" t="n">
-        <v>16.503</v>
+        <v>2.1181</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.2046</v>
       </c>
       <c r="G11" t="n">
-        <v>16.50300355279719</v>
+        <v>1.9135</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.2046</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.2046</v>
       </c>
       <c r="J11" t="n">
-        <v>16.50300355279719</v>
+        <v>1.4719</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L11" t="n">
-        <v>190</v>
+        <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>16.503</v>
+        <v>1.6765</v>
       </c>
       <c r="N11" t="n">
-        <v>190</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>lauNX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.8438</v>
+        <v>1.9818</v>
       </c>
       <c r="C12" t="n">
-        <v>2.42283948</v>
+        <v>0.5083</v>
       </c>
       <c r="D12" t="n">
-        <v>1.893627245959956</v>
+        <v>0.3792</v>
       </c>
       <c r="E12" t="n">
-        <v>16.4621</v>
+        <v>1.9818</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.2762</v>
       </c>
       <c r="G12" t="n">
-        <v>16.46206771684786</v>
+        <v>1.7056</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.2762</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.2762</v>
       </c>
       <c r="J12" t="n">
-        <v>16.46206771684786</v>
+        <v>1.312</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L12" t="n">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="M12" t="n">
-        <v>16.4621</v>
+        <v>1.5882</v>
       </c>
       <c r="N12" t="n">
-        <v>167</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.9578</v>
+        <v>1.4904</v>
       </c>
       <c r="C13" t="n">
-        <v>1.64090388</v>
+        <v>0.3822</v>
       </c>
       <c r="D13" t="n">
-        <v>1.053600466193451</v>
+        <v>0.1807</v>
       </c>
       <c r="E13" t="n">
-        <v>9.1594</v>
+        <v>1.4904</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>9.159375087142067</v>
+        <v>1.4904</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1038,44 +1026,44 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>9.159375087142067</v>
+        <v>1.1465</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>199</v>
+        <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>9.1594</v>
+        <v>1.1465</v>
       </c>
       <c r="N13" t="n">
-        <v>199</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.8301</v>
+        <v>1.1869</v>
       </c>
       <c r="C14" t="n">
-        <v>1.58795946</v>
+        <v>0.3044</v>
       </c>
       <c r="D14" t="n">
-        <v>1.006469785640289</v>
+        <v>0.0581</v>
       </c>
       <c r="E14" t="n">
-        <v>8.749599999999999</v>
+        <v>1.1869</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8.749649014356308</v>
+        <v>1.1869</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1084,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>8.749649014356308</v>
+        <v>0.913</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>199</v>
+        <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>8.749599999999999</v>
+        <v>0.913</v>
       </c>
       <c r="N14" t="n">
-        <v>199</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.7402</v>
+        <v>1.0369</v>
       </c>
       <c r="C15" t="n">
-        <v>1.55068692</v>
+        <v>0.2659</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9739468378204236</v>
+        <v>-0.0025</v>
       </c>
       <c r="E15" t="n">
-        <v>8.466900000000001</v>
+        <v>1.0369</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8.466913871785673</v>
+        <v>1.0369</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1130,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>8.466913871785673</v>
+        <v>0.7976</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="M15" t="n">
-        <v>8.466900000000001</v>
+        <v>0.7976</v>
       </c>
       <c r="N15" t="n">
-        <v>71</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.5994</v>
+        <v>0.8284</v>
       </c>
       <c r="C16" t="n">
-        <v>1.49231124</v>
+        <v>0.2125</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9240545079066003</v>
+        <v>-0.0867</v>
       </c>
       <c r="E16" t="n">
-        <v>8.033200000000001</v>
+        <v>0.8284</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>8.033179663881251</v>
+        <v>0.8284</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1176,90 +1164,90 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>8.033179663881251</v>
+        <v>0.6372</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="M16" t="n">
-        <v>8.033200000000001</v>
+        <v>0.6372</v>
       </c>
       <c r="N16" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dziugss</t>
+          <t>ryu</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.4372</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>1.42506312</v>
+        <v>0.1493</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8681292909702165</v>
+        <v>-0.1862</v>
       </c>
       <c r="E17" t="n">
-        <v>7.547</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.5214</v>
       </c>
       <c r="G17" t="n">
-        <v>7.546999128482668</v>
+        <v>1.1036</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0.5214</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.5214</v>
       </c>
       <c r="J17" t="n">
-        <v>7.546999128482668</v>
+        <v>0.8489</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L17" t="n">
-        <v>199</v>
+        <v>101</v>
       </c>
       <c r="M17" t="n">
-        <v>7.547</v>
+        <v>0.3275</v>
       </c>
       <c r="N17" t="n">
-        <v>199</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.3486</v>
+        <v>0.5313</v>
       </c>
       <c r="C18" t="n">
-        <v>1.38832956</v>
+        <v>0.1363</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8382986981681895</v>
+        <v>-0.2067</v>
       </c>
       <c r="E18" t="n">
-        <v>7.2877</v>
+        <v>0.5313</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>7.28766971727548</v>
+        <v>0.5313</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1268,136 +1256,136 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>7.28766971727548</v>
+        <v>0.4087</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>7.2877</v>
+        <v>0.4087</v>
       </c>
       <c r="N18" t="n">
-        <v>206</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>dziugss</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.2413</v>
+        <v>0.3409</v>
       </c>
       <c r="C19" t="n">
-        <v>1.34384298</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8027590408122858</v>
+        <v>-0.2836</v>
       </c>
       <c r="E19" t="n">
-        <v>6.9787</v>
+        <v>0.3409</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.2742</v>
       </c>
       <c r="G19" t="n">
-        <v>6.978709098296918</v>
+        <v>0.0667</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.2742</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.2742</v>
       </c>
       <c r="J19" t="n">
-        <v>6.978709098296918</v>
+        <v>0.0513</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L19" t="n">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="M19" t="n">
-        <v>6.9787</v>
+        <v>0.3255</v>
       </c>
       <c r="N19" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.0951</v>
+        <v>0.3406</v>
       </c>
       <c r="C20" t="n">
-        <v>1.28322846</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7554737567296201</v>
+        <v>-0.2838</v>
       </c>
       <c r="E20" t="n">
-        <v>6.5676</v>
+        <v>0.3406</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.0237</v>
       </c>
       <c r="G20" t="n">
-        <v>6.567638994484264</v>
+        <v>0.3643</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-0.0237</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.0237</v>
       </c>
       <c r="J20" t="n">
-        <v>6.567638994484264</v>
+        <v>0.2802</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L20" t="n">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="M20" t="n">
-        <v>6.5676</v>
+        <v>0.2565</v>
       </c>
       <c r="N20" t="n">
-        <v>71</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.6004</v>
+        <v>0.171</v>
       </c>
       <c r="C21" t="n">
-        <v>1.07812584</v>
+        <v>0.0439</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6044890854026495</v>
+        <v>-0.3523</v>
       </c>
       <c r="E21" t="n">
-        <v>5.2551</v>
+        <v>0.171</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>5.255068165725092</v>
+        <v>0.171</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1406,44 +1394,44 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>5.255068165725092</v>
+        <v>0.1315</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="M21" t="n">
-        <v>5.2551</v>
+        <v>0.1315</v>
       </c>
       <c r="N21" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.3882</v>
+        <v>0.0659</v>
       </c>
       <c r="C22" t="n">
-        <v>0.99014772</v>
+        <v>0.0169</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5437425302896112</v>
+        <v>-0.3947</v>
       </c>
       <c r="E22" t="n">
-        <v>4.727</v>
+        <v>0.0659</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>4.726973787082414</v>
+        <v>0.0659</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1452,44 +1440,44 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>4.726973787082414</v>
+        <v>0.0507</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M22" t="n">
-        <v>4.727</v>
+        <v>0.0507</v>
       </c>
       <c r="N22" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.341</v>
+        <v>-0.004</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9705786000000002</v>
+        <v>-0.001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5305573136313059</v>
+        <v>-0.423</v>
       </c>
       <c r="E23" t="n">
-        <v>4.6123</v>
+        <v>-0.004</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>4.612349364586689</v>
+        <v>-0.004</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1498,90 +1486,90 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>4.612349364586689</v>
+        <v>-0.0031</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="M23" t="n">
-        <v>4.6123</v>
+        <v>-0.0031</v>
       </c>
       <c r="N23" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9735</v>
+        <v>-0.0337</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8182131</v>
+        <v>-0.0086</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4316402566486177</v>
+        <v>-0.435</v>
       </c>
       <c r="E24" t="n">
-        <v>3.7524</v>
+        <v>-0.0337</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="G24" t="n">
-        <v>3.752423371298173</v>
+        <v>0.4663</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.752423371298173</v>
+        <v>0.3587</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L24" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7524</v>
+        <v>-0.1413</v>
       </c>
       <c r="N24" t="n">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7371</v>
+        <v>-0.0406</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7202016600000001</v>
+        <v>-0.0104</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3714004054344592</v>
+        <v>-0.4378</v>
       </c>
       <c r="E25" t="n">
-        <v>3.2287</v>
+        <v>-0.0406</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3.228733974635739</v>
+        <v>-0.0406</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1590,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3.228733974635739</v>
+        <v>-0.0312</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>39</v>
+        <v>206</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2287</v>
+        <v>-0.0312</v>
       </c>
       <c r="N25" t="n">
-        <v>39</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4806</v>
+        <v>-0.4042</v>
       </c>
       <c r="C26" t="n">
-        <v>0.61385676</v>
+        <v>-0.1037</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3089176676409857</v>
+        <v>-0.5847</v>
       </c>
       <c r="E26" t="n">
-        <v>2.6855</v>
+        <v>-0.4042</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2.685546257578587</v>
+        <v>-0.4042</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1636,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2.685546257578587</v>
+        <v>-0.3109</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>199</v>
+        <v>57</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6855</v>
+        <v>-0.3109</v>
       </c>
       <c r="N26" t="n">
-        <v>199</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ryu</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9809</v>
+        <v>-0.4074</v>
       </c>
       <c r="C27" t="n">
-        <v>0.40668114</v>
+        <v>-0.1045</v>
       </c>
       <c r="D27" t="n">
-        <v>0.195241920653615</v>
+        <v>-0.5859</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6973</v>
+        <v>-0.4074</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.697317001444969</v>
+        <v>-0.4074</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1682,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1.697317001444969</v>
+        <v>-0.3134</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6973</v>
+        <v>-0.3134</v>
       </c>
       <c r="N27" t="n">
-        <v>167</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8075</v>
+        <v>-0.5138</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3347895</v>
+        <v>-0.1318</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1581500504048733</v>
+        <v>-0.6289</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3749</v>
+        <v>-0.5138</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1.374862367840572</v>
+        <v>-0.5138</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1728,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1.374862367840572</v>
+        <v>-0.3952</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3749</v>
+        <v>-0.3952</v>
       </c>
       <c r="N28" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.765</v>
+        <v>-0.644</v>
       </c>
       <c r="C29" t="n">
-        <v>0.317169</v>
+        <v>-0.1652</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1492284837853802</v>
+        <v>-0.6815</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2973</v>
+        <v>-0.644</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.2973035799937</v>
+        <v>-0.644</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1774,19 +1762,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1.2973035799937</v>
+        <v>-0.4954</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2973</v>
+        <v>-0.4954</v>
       </c>
       <c r="N29" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
@@ -1796,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7224</v>
+        <v>-0.6973</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2995070400000001</v>
+        <v>-0.1788</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1403559399542737</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2202</v>
+        <v>-0.6973</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1.220170967078463</v>
+        <v>-0.6973</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1820,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1.220170967078463</v>
+        <v>-0.5364</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1829,7 +1817,7 @@
         <v>41</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2202</v>
+        <v>-0.5364</v>
       </c>
       <c r="N30" t="n">
         <v>41</v>
@@ -1842,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6523</v>
+        <v>-0.7179</v>
       </c>
       <c r="C31" t="n">
-        <v>0.27044358</v>
+        <v>-0.1841</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1259190565665411</v>
+        <v>-0.7114</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0947</v>
+        <v>-0.7179</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1.094665299341511</v>
+        <v>-0.7179</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1866,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1.094665299341511</v>
+        <v>-0.5522</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1875,7 +1863,7 @@
         <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0947</v>
+        <v>-0.5522</v>
       </c>
       <c r="N31" t="n">
         <v>39</v>
@@ -1884,26 +1872,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6248</v>
+        <v>-0.8921</v>
       </c>
       <c r="C32" t="n">
-        <v>0.25904208</v>
+        <v>-0.2288</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1203122340714119</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>1.0459</v>
+        <v>-0.8921</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.045922923148897</v>
+        <v>-0.8921</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1912,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1.045922923148897</v>
+        <v>-0.6862</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1921,7 +1909,7 @@
         <v>39</v>
       </c>
       <c r="M32" t="n">
-        <v>1.0459</v>
+        <v>-0.6862</v>
       </c>
       <c r="N32" t="n">
         <v>39</v>
@@ -1930,26 +1918,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2855</v>
+        <v>-1.0101</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1183683</v>
+        <v>-0.2591</v>
       </c>
       <c r="D33" t="n">
-        <v>0.05327843080140962</v>
+        <v>-0.8294</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4632</v>
+        <v>-1.0101</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4631709527687822</v>
+        <v>-1.0101</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1958,19 +1946,19 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4631709527687822</v>
+        <v>-0.777</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4632</v>
+        <v>-0.777</v>
       </c>
       <c r="N33" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -1980,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1989</v>
+        <v>-1.046</v>
       </c>
       <c r="C34" t="n">
-        <v>0.08246394</v>
+        <v>-0.2683</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03682519545734104</v>
+        <v>-0.8439</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3201</v>
+        <v>-1.046</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.320136321759349</v>
+        <v>-1.046</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -2004,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.320136321759349</v>
+        <v>-0.8046</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2013,7 +2001,7 @@
         <v>39</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3201</v>
+        <v>-0.8046</v>
       </c>
       <c r="N34" t="n">
         <v>39</v>
@@ -2022,26 +2010,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1974</v>
+        <v>-1.18</v>
       </c>
       <c r="C35" t="n">
-        <v>0.08184204</v>
+        <v>-0.3026</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03653601328924436</v>
+        <v>-0.8981</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3176</v>
+        <v>-1.18</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3176223441833139</v>
+        <v>-1.18</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2050,19 +2038,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3176223441833139</v>
+        <v>-0.9077</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3176</v>
+        <v>-0.9077</v>
       </c>
       <c r="N35" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
@@ -2072,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.2294</v>
+        <v>-1.2069</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.09510924</v>
+        <v>-0.3095</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.04258316258254657</v>
+        <v>-0.9089</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3702</v>
+        <v>-1.2069</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3701926593668412</v>
+        <v>-1.2069</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2096,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3701926593668412</v>
+        <v>-0.9284</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2105,7 +2093,7 @@
         <v>71</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3702</v>
+        <v>-0.9284</v>
       </c>
       <c r="N36" t="n">
         <v>71</v>
@@ -2114,26 +2102,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.5572</v>
+        <v>-1.3</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.23101512</v>
+        <v>-0.3334</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1066271294476398</v>
+        <v>-0.9465</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.927</v>
+        <v>-1.3</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9269527723394763</v>
+        <v>-1.3</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2142,44 +2130,44 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9269527723394763</v>
+        <v>-1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.927</v>
+        <v>-1</v>
       </c>
       <c r="N37" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.5916</v>
+        <v>-1.3</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.24527736</v>
+        <v>-0.3334</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1135658770289973</v>
+        <v>-0.9465</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9873</v>
+        <v>-1.3</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.9872741121375397</v>
+        <v>-1.3</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2188,65 +2176,65 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9872741121375397</v>
+        <v>-1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9873</v>
+        <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8495</v>
+        <v>-1.5078</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3522027</v>
+        <v>-0.3867</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.167017385790805</v>
+        <v>-1.0305</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4519</v>
+        <v>-1.5078</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-0.417</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.451949701634826</v>
+        <v>-1.0908</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-0.417</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>-0.417</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.451949701634826</v>
+        <v>-0.8391</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L39" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4519</v>
+        <v>-1.2561</v>
       </c>
       <c r="N39" t="n">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40">
@@ -2256,40 +2244,40 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4.3235</v>
+        <v>-2.3133</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.7925231</v>
+        <v>-0.5933</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.194801216289007</v>
+        <v>-1.3559</v>
       </c>
       <c r="E40" t="n">
-        <v>-10.3869</v>
+        <v>-2.3133</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-0.654</v>
       </c>
       <c r="G40" t="n">
-        <v>-10.386890330547</v>
+        <v>-1.6593</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>-0.654</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>-0.654</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.386890330547</v>
+        <v>-1.2764</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L40" t="n">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="M40" t="n">
-        <v>-10.3869</v>
+        <v>-1.9304</v>
       </c>
       <c r="N40" t="n">
         <v>167</v>
@@ -2302,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.5382</v>
+        <v>-2.5896</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.29613772</v>
+        <v>-0.6641</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.737208645393554</v>
+        <v>-1.4675</v>
       </c>
       <c r="E41" t="n">
-        <v>-15.1023</v>
+        <v>-2.5896</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-15.1022575429119</v>
+        <v>-2.5896</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2326,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.1022575429119</v>
+        <v>-1.992</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2335,7 +2323,7 @@
         <v>190</v>
       </c>
       <c r="M41" t="n">
-        <v>-15.1023</v>
+        <v>-1.992</v>
       </c>
       <c r="N41" t="n">
         <v>190</v>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9165513545279041</v>
+        <v>1.9614</v>
       </c>
       <c r="J2" t="n">
-        <v>18.33102709055808</v>
+        <v>39.228</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.45</v>
       </c>
       <c r="I3" t="n">
-        <v>0.356558273991202</v>
+        <v>1.0613</v>
       </c>
       <c r="J3" t="n">
-        <v>7.131165479824041</v>
+        <v>21.226</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2884940029337091</v>
+        <v>0.9305</v>
       </c>
       <c r="J4" t="n">
-        <v>5.769880058674182</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1916492126822428</v>
+        <v>-0.3303</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.832984253644857</v>
+        <v>-6.606</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.84</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3284734264979527</v>
+        <v>-0.6604</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.569468529959054</v>
+        <v>-13.208</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1608478553842286</v>
+        <v>0.1665</v>
       </c>
       <c r="J7" t="n">
-        <v>3.216957107684573</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.155073667410936</v>
+        <v>0.1442</v>
       </c>
       <c r="J8" t="n">
-        <v>3.10147334821872</v>
+        <v>2.884</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08187026387354437</v>
+        <v>-0.1504</v>
       </c>
       <c r="J9" t="n">
-        <v>1.637405277470887</v>
+        <v>-3.008</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01201237268538788</v>
+        <v>-0.4779</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2402474537077576</v>
+        <v>-9.558</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.48</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.13516863618741</v>
+        <v>-0.7631</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.703372723748201</v>
+        <v>-15.262</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3353805732503881</v>
+        <v>0.67</v>
       </c>
       <c r="J12" t="n">
-        <v>8.049133758009315</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1469778898147966</v>
+        <v>0.2279</v>
       </c>
       <c r="J13" t="n">
-        <v>3.527469355555118</v>
+        <v>5.4696</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>0.96</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07931596062052942</v>
+        <v>-0.1145</v>
       </c>
       <c r="J14" t="n">
-        <v>1.903583054892706</v>
+        <v>-2.748</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0459518469644572</v>
+        <v>-0.2279</v>
       </c>
       <c r="J15" t="n">
-        <v>1.102844327146973</v>
+        <v>-5.4696</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1198092616027665</v>
+        <v>-0.6214</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.875422278466395</v>
+        <v>-14.9136</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.37</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4416781084371473</v>
+        <v>0.5844</v>
       </c>
       <c r="J17" t="n">
-        <v>10.60027460249154</v>
+        <v>14.0256</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08810485586738365</v>
+        <v>0.0668</v>
       </c>
       <c r="J18" t="n">
-        <v>2.114516540817208</v>
+        <v>1.6032</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07830962535115149</v>
+        <v>0.045</v>
       </c>
       <c r="J19" t="n">
-        <v>1.879431008427636</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01748671550956583</v>
+        <v>-0.1202</v>
       </c>
       <c r="J20" t="n">
-        <v>0.41968117222958</v>
+        <v>-2.8848</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01748671550956583</v>
+        <v>-0.1202</v>
       </c>
       <c r="J21" t="n">
-        <v>0.41968117222958</v>
+        <v>-2.8848</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.72</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7553041674264132</v>
+        <v>1.6428</v>
       </c>
       <c r="J22" t="n">
-        <v>15.86138751595468</v>
+        <v>34.4988</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2352973500721233</v>
+        <v>0.7235</v>
       </c>
       <c r="J23" t="n">
-        <v>4.941244351514588</v>
+        <v>15.1935</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>1.21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.171877837012486</v>
+        <v>0.5669</v>
       </c>
       <c r="J24" t="n">
-        <v>3.609434577262206</v>
+        <v>11.9049</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>0.05003897768190978</v>
+        <v>0.2099</v>
       </c>
       <c r="J25" t="n">
-        <v>1.050818531320105</v>
+        <v>4.4079</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4241076876856286</v>
+        <v>-0.9971</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.9062614413982</v>
+        <v>-20.9391</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2621133336438347</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>5.504380006520528</v>
+        <v>10.9977</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.18</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2013141439624184</v>
+        <v>0.3715</v>
       </c>
       <c r="J28" t="n">
-        <v>4.227597023210786</v>
+        <v>7.8015</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>1.18</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2013141439624184</v>
+        <v>0.3715</v>
       </c>
       <c r="J29" t="n">
-        <v>4.227597023210786</v>
+        <v>7.8015</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.62</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1030758266054602</v>
+        <v>-0.6137</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.164592358714664</v>
+        <v>-12.8877</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.49</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1747835868586707</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.670455324032084</v>
+        <v>-16.1637</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.29</v>
       </c>
       <c r="I32" t="n">
-        <v>0.317352994895221</v>
+        <v>0.8005</v>
       </c>
       <c r="J32" t="n">
-        <v>6.981765887694862</v>
+        <v>17.611</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3055832638924444</v>
+        <v>0.7771</v>
       </c>
       <c r="J33" t="n">
-        <v>6.722831805633777</v>
+        <v>17.0962</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>1.27</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2938543379758437</v>
+        <v>0.7534</v>
       </c>
       <c r="J34" t="n">
-        <v>6.464795435468561</v>
+        <v>16.5748</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>1.19</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2032184664845326</v>
+        <v>0.5511</v>
       </c>
       <c r="J35" t="n">
-        <v>4.470806262659717</v>
+        <v>12.1242</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3545562135598543</v>
+        <v>-0.9653</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.800236698316795</v>
+        <v>-21.2366</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2085377555704856</v>
+        <v>0.331</v>
       </c>
       <c r="J37" t="n">
-        <v>4.587830622550682</v>
+        <v>7.282</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.07</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1695485443273176</v>
+        <v>0.2147</v>
       </c>
       <c r="J38" t="n">
-        <v>3.730067975200987</v>
+        <v>4.7234</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>0.93</v>
       </c>
       <c r="I39" t="n">
-        <v>0.092554535831086</v>
+        <v>-0.113</v>
       </c>
       <c r="J39" t="n">
-        <v>2.036199788283892</v>
+        <v>-2.486</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.79</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02393873786576571</v>
+        <v>-0.3703</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5266522330468456</v>
+        <v>-8.146599999999999</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.106866444034533</v>
+        <v>-0.6787</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.351061768759726</v>
+        <v>-14.9314</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.97</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1495671050146577</v>
+        <v>1.1756</v>
       </c>
       <c r="J42" t="n">
-        <v>3.140909205307811</v>
+        <v>24.6876</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.38</v>
       </c>
       <c r="I43" t="n">
-        <v>0.04923161020637508</v>
+        <v>0.5406</v>
       </c>
       <c r="J43" t="n">
-        <v>1.033863814333877</v>
+        <v>11.3526</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>1.17</v>
       </c>
       <c r="I44" t="n">
-        <v>0.01594660220661271</v>
+        <v>0.2291</v>
       </c>
       <c r="J44" t="n">
-        <v>0.3348786463388669</v>
+        <v>4.8111</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.91</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.03031952942362937</v>
+        <v>-0.2674</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.6367101178962168</v>
+        <v>-5.6154</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.87</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.03709394649170218</v>
+        <v>-0.3289</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.7789728763257459</v>
+        <v>-6.9069</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.62</v>
       </c>
       <c r="I47" t="n">
-        <v>0.07131513632802515</v>
+        <v>0.9298</v>
       </c>
       <c r="J47" t="n">
-        <v>1.497617862888528</v>
+        <v>19.5258</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.04145018004907861</v>
+        <v>0.4982</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8704537810306509</v>
+        <v>10.4622</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>0.67</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.007903698753919601</v>
+        <v>-0.5421</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.1659776738323116</v>
+        <v>-11.3841</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.57</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.01656129500068418</v>
+        <v>-0.6688</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.3477871950143677</v>
+        <v>-14.0448</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.44</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.02748179112972068</v>
+        <v>-0.8223</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.5771176137241343</v>
+        <v>-17.2683</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>0.86</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0170440741166892</v>
+        <v>-0.1624</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2897492599837164</v>
+        <v>-2.7608</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>0.85</v>
       </c>
       <c r="I53" t="n">
-        <v>0.01616651460769941</v>
+        <v>-0.179</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2748307483308901</v>
+        <v>-3.043</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>0.77</v>
       </c>
       <c r="I54" t="n">
-        <v>0.009535450951977957</v>
+        <v>-0.3124</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1621026661836253</v>
+        <v>-5.3108</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.66</v>
       </c>
       <c r="I55" t="n">
-        <v>0.001504877664114862</v>
+        <v>-0.5059</v>
       </c>
       <c r="J55" t="n">
-        <v>0.02558292028995265</v>
+        <v>-8.600300000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.006302932787387541</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.1071498573855882</v>
+        <v>-10.7372</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>2.07</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1560546638842333</v>
+        <v>2.0593</v>
       </c>
       <c r="J57" t="n">
-        <v>2.652929286031967</v>
+        <v>35.0081</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0263074007180985</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>0.4472258122076744</v>
+        <v>9.9314</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>1.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01256427337051537</v>
+        <v>0.3893</v>
       </c>
       <c r="J59" t="n">
-        <v>0.2135926472987613</v>
+        <v>6.6181</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.001978272142152029</v>
+        <v>0.2354</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0336306264165845</v>
+        <v>4.0018</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>1.07</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.006879759584240024</v>
+        <v>0.0959</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.1169559129320804</v>
+        <v>1.6303</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.03494604238017496</v>
+        <v>0.3824</v>
       </c>
       <c r="J62" t="n">
-        <v>0.9784891866448988</v>
+        <v>10.7072</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.02415901290216638</v>
+        <v>0.1869</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6764523612606587</v>
+        <v>5.2332</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0180050323091421</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>0.5041409046559788</v>
+        <v>0.2352</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>0.72</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.004118335953105196</v>
+        <v>-0.4773</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.1153134066869455</v>
+        <v>-13.3644</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.009502725753251461</v>
+        <v>-0.5572</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.2660763210910409</v>
+        <v>-15.6016</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.78</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1215144473206071</v>
+        <v>1.7368</v>
       </c>
       <c r="J67" t="n">
-        <v>3.402404524976998</v>
+        <v>48.6304</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>1.54</v>
       </c>
       <c r="I68" t="n">
-        <v>0.08147628194721118</v>
+        <v>1.2907</v>
       </c>
       <c r="J68" t="n">
-        <v>2.281335894521913</v>
+        <v>36.1396</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>1.22</v>
       </c>
       <c r="I69" t="n">
-        <v>0.02785226950868874</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>0.7798635462432848</v>
+        <v>15.736</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.04288000093308124</v>
+        <v>-0.7351</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.200640026126275</v>
+        <v>-20.5828</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0480198951439129</v>
+        <v>-0.8047</v>
       </c>
       <c r="J71" t="n">
-        <v>-1.344557064029561</v>
+        <v>-22.5316</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1526762150627107</v>
+        <v>0.4611</v>
       </c>
       <c r="J72" t="n">
-        <v>3.664229161505058</v>
+        <v>11.0664</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1413386176258892</v>
+        <v>0.4199</v>
       </c>
       <c r="J73" t="n">
-        <v>3.392126823021341</v>
+        <v>10.0776</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>1.14</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1080558287243703</v>
+        <v>0.2868</v>
       </c>
       <c r="J74" t="n">
-        <v>2.593339889384888</v>
+        <v>6.8832</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.008394178240804448</v>
+        <v>-0.3877</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.2014602777793068</v>
+        <v>-9.3048</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.06091852148140213</v>
+        <v>-0.5745</v>
       </c>
       <c r="J76" t="n">
-        <v>-1.462044515553651</v>
+        <v>-13.788</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4195373496204261</v>
+        <v>0.7498</v>
       </c>
       <c r="J77" t="n">
-        <v>10.06889639089023</v>
+        <v>17.9952</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.36</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2852103116013499</v>
+        <v>0.5595</v>
       </c>
       <c r="J78" t="n">
-        <v>6.845047478432398</v>
+        <v>13.428</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>0.99</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.002742553291006852</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.06582127898416446</v>
+        <v>-2.0304</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.91</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.06946976473807857</v>
+        <v>-0.2413</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.667274353713886</v>
+        <v>-5.7912</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1631552380124773</v>
+        <v>-0.4066</v>
       </c>
       <c r="J81" t="n">
-        <v>-3.915725712299456</v>
+        <v>-9.7584</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.74</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3725578571364646</v>
+        <v>1.5504</v>
       </c>
       <c r="J82" t="n">
-        <v>5.588367857046969</v>
+        <v>23.256</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.72</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3581457416241784</v>
+        <v>1.5139</v>
       </c>
       <c r="J83" t="n">
-        <v>5.372186124362676</v>
+        <v>22.7085</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.4</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1453508698413175</v>
+        <v>0.8355</v>
       </c>
       <c r="J84" t="n">
-        <v>2.180263047619762</v>
+        <v>12.5325</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>1.38</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1312272952869056</v>
+        <v>0.792</v>
       </c>
       <c r="J85" t="n">
-        <v>1.968409429303584</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>1.18</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.01606594196208673</v>
+        <v>0.3433</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.240989129431301</v>
+        <v>5.1495</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>0.9</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1221528283177252</v>
+        <v>-0.0259</v>
       </c>
       <c r="J87" t="n">
-        <v>1.832292424765878</v>
+        <v>-0.3885</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>0.75</v>
       </c>
       <c r="I88" t="n">
-        <v>0.05959243607723529</v>
+        <v>-0.2673</v>
       </c>
       <c r="J88" t="n">
-        <v>0.8938865411585294</v>
+        <v>-4.0095</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.6</v>
       </c>
       <c r="I89" t="n">
-        <v>0.004482347871265363</v>
+        <v>-0.5221</v>
       </c>
       <c r="J89" t="n">
-        <v>0.06723521806898045</v>
+        <v>-7.8315</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.45</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.05205218223386197</v>
+        <v>-0.7501</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.7807827335079296</v>
+        <v>-11.2515</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1008230905277128</v>
+        <v>-0.905</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.512346357915692</v>
+        <v>-13.575</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.79</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5247562302366573</v>
+        <v>1.7363</v>
       </c>
       <c r="J92" t="n">
-        <v>12.06939329544312</v>
+        <v>39.9349</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.39</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2354123582309317</v>
+        <v>0.9847</v>
       </c>
       <c r="J93" t="n">
-        <v>5.414484239311429</v>
+        <v>22.6481</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.106781472656219</v>
+        <v>0.5053</v>
       </c>
       <c r="J94" t="n">
-        <v>2.455973871093036</v>
+        <v>11.6219</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.02963347426362418</v>
+        <v>0.1987</v>
       </c>
       <c r="J95" t="n">
-        <v>0.6815699080633563</v>
+        <v>4.5701</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.62</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.312612909493081</v>
+        <v>-1.1264</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.190096918340863</v>
+        <v>-25.9072</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1445053767709094</v>
+        <v>0.3504</v>
       </c>
       <c r="J97" t="n">
-        <v>3.323623665730916</v>
+        <v>8.059200000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1403065278064879</v>
+        <v>0.3353</v>
       </c>
       <c r="J98" t="n">
-        <v>3.227050139549222</v>
+        <v>7.7119</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1360925835824328</v>
+        <v>0.3198</v>
       </c>
       <c r="J99" t="n">
-        <v>3.130129422395955</v>
+        <v>7.3554</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>0.68</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.04750676640971076</v>
+        <v>-0.5323</v>
       </c>
       <c r="J100" t="n">
-        <v>-1.092655627423347</v>
+        <v>-12.2429</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.51</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1178320421400658</v>
+        <v>-0.7432</v>
       </c>
       <c r="J101" t="n">
-        <v>-2.710136969221513</v>
+        <v>-17.0936</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>2.39</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7784042911086372</v>
+        <v>2.2187</v>
       </c>
       <c r="J102" t="n">
-        <v>14.01127723995547</v>
+        <v>39.9366</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.7</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3332413055995622</v>
+        <v>1.4898</v>
       </c>
       <c r="J103" t="n">
-        <v>5.998343500792119</v>
+        <v>26.8164</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.008178637317504345</v>
+        <v>0.3993</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.1472154717150782</v>
+        <v>7.1874</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1393548309578492</v>
+        <v>-0.096</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.508386957241285</v>
+        <v>-1.728</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.96</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1820293224385115</v>
+        <v>-0.3609</v>
       </c>
       <c r="J106" t="n">
-        <v>-3.276527803893207</v>
+        <v>-6.4962</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.37</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2491524420128313</v>
+        <v>0.6866</v>
       </c>
       <c r="J107" t="n">
-        <v>4.484743956230963</v>
+        <v>12.3588</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1049463143042185</v>
+        <v>0.131</v>
       </c>
       <c r="J108" t="n">
-        <v>1.889033657475933</v>
+        <v>2.358</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>0.72</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.001861243549176508</v>
+        <v>-0.4385</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.03350238388517715</v>
+        <v>-7.893</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.52</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0807707452036155</v>
+        <v>-0.709</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.453873413665079</v>
+        <v>-12.762</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.36</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1428514046314525</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-2.571325283366146</v>
+        <v>-16.1946</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.6</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2512810974025749</v>
+        <v>0.8413</v>
       </c>
       <c r="J112" t="n">
-        <v>6.030746337661798</v>
+        <v>20.1912</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.102537526505184</v>
+        <v>0.3307</v>
       </c>
       <c r="J113" t="n">
-        <v>2.460900636124417</v>
+        <v>7.9368</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>1.14</v>
       </c>
       <c r="I114" t="n">
-        <v>0.08582182063015041</v>
+        <v>0.251</v>
       </c>
       <c r="J114" t="n">
-        <v>2.05972369512361</v>
+        <v>6.024</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>0.99</v>
       </c>
       <c r="I115" t="n">
-        <v>0.04036651514920866</v>
+        <v>-0.0824</v>
       </c>
       <c r="J115" t="n">
-        <v>0.968796363581008</v>
+        <v>-1.9776</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0943012702385805</v>
+        <v>-0.6358</v>
       </c>
       <c r="J116" t="n">
-        <v>-2.263230485725932</v>
+        <v>-15.2592</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.24</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1959457146407256</v>
+        <v>0.417</v>
       </c>
       <c r="J117" t="n">
-        <v>4.702697151377415</v>
+        <v>10.008</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1165403698292252</v>
+        <v>0.2679</v>
       </c>
       <c r="J118" t="n">
-        <v>2.796968875901406</v>
+        <v>6.4296</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>1.04</v>
       </c>
       <c r="I119" t="n">
-        <v>0.05362991607951023</v>
+        <v>0.0704</v>
       </c>
       <c r="J119" t="n">
-        <v>1.287117985908246</v>
+        <v>1.6896</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I120" t="n">
-        <v>0.03945307074653324</v>
+        <v>0.025</v>
       </c>
       <c r="J120" t="n">
-        <v>0.9468736979167979</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.9</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.05579188973713685</v>
+        <v>-0.2468</v>
       </c>
       <c r="J121" t="n">
-        <v>-1.339005353691284</v>
+        <v>-5.9232</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.78</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4860526706040771</v>
+        <v>1.7044</v>
       </c>
       <c r="J122" t="n">
-        <v>9.721053412081542</v>
+        <v>34.088</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.74</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4588812854543497</v>
+        <v>1.6413</v>
       </c>
       <c r="J123" t="n">
-        <v>9.177625709086994</v>
+        <v>32.826</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.008740142529282291</v>
+        <v>0.1767</v>
       </c>
       <c r="J124" t="n">
-        <v>0.1748028505856458</v>
+        <v>3.534</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.89</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1373326169700919</v>
+        <v>-0.5228</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.746652339401837</v>
+        <v>-10.456</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1575074141175704</v>
+        <v>-0.6007</v>
       </c>
       <c r="J126" t="n">
-        <v>-3.150148282351407</v>
+        <v>-12.014</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.15</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1556011835890272</v>
+        <v>0.3602</v>
       </c>
       <c r="J127" t="n">
-        <v>3.112023671780545</v>
+        <v>7.204</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>0.85</v>
       </c>
       <c r="I128" t="n">
-        <v>0.03955165376333095</v>
+        <v>-0.2552</v>
       </c>
       <c r="J128" t="n">
-        <v>0.7910330752666189</v>
+        <v>-5.104</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>0.03955165376333095</v>
+        <v>-0.2552</v>
       </c>
       <c r="J129" t="n">
-        <v>0.7910330752666189</v>
+        <v>-5.104</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>0.78</v>
       </c>
       <c r="I130" t="n">
-        <v>0.01431853550274567</v>
+        <v>-0.3729</v>
       </c>
       <c r="J130" t="n">
-        <v>0.2863707100549134</v>
+        <v>-7.458</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.02559501600031766</v>
+        <v>-0.5168</v>
       </c>
       <c r="J131" t="n">
-        <v>-0.5119003200063532</v>
+        <v>-10.336</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>1.82</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4667679544399405</v>
+        <v>1.7349</v>
       </c>
       <c r="J132" t="n">
-        <v>8.868591134358869</v>
+        <v>32.9631</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>1.47</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2184239410932711</v>
+        <v>1.0931</v>
       </c>
       <c r="J133" t="n">
-        <v>4.150054880772151</v>
+        <v>20.7689</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1.46</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2112704179693104</v>
+        <v>1.0721</v>
       </c>
       <c r="J134" t="n">
-        <v>4.014137941416898</v>
+        <v>20.3699</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>1.09</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.04072176319182386</v>
+        <v>0.1541</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.7737135006446533</v>
+        <v>2.9279</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.214267057853939</v>
+        <v>-0.64</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.07107409922484</v>
+        <v>-12.16</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.102300247291958</v>
+        <v>0.2602</v>
       </c>
       <c r="J137" t="n">
-        <v>1.943704698547202</v>
+        <v>4.9438</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>0.04037669742142348</v>
+        <v>-0.1881</v>
       </c>
       <c r="J138" t="n">
-        <v>0.7671572510070461</v>
+        <v>-3.5739</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I139" t="n">
-        <v>0.02682098545977556</v>
+        <v>-0.3076</v>
       </c>
       <c r="J139" t="n">
-        <v>0.5095987237357356</v>
+        <v>-5.8444</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>0.02438251278780235</v>
+        <v>-0.3253</v>
       </c>
       <c r="J140" t="n">
-        <v>0.4632677429682446</v>
+        <v>-6.1807</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.03883064141789444</v>
+        <v>-0.6402</v>
       </c>
       <c r="J141" t="n">
-        <v>-0.7377821869399943</v>
+        <v>-12.1638</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.8</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4494650633589029</v>
+        <v>1.7077</v>
       </c>
       <c r="J142" t="n">
-        <v>8.989301267178059</v>
+        <v>34.154</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.5</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2360811621206143</v>
+        <v>1.1532</v>
       </c>
       <c r="J143" t="n">
-        <v>4.721623242412285</v>
+        <v>23.064</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>1.33</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1252617883997854</v>
+        <v>0.7558</v>
       </c>
       <c r="J144" t="n">
-        <v>2.505235767995707</v>
+        <v>15.116</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.01453565122021928</v>
+        <v>0.3636</v>
       </c>
       <c r="J145" t="n">
-        <v>0.2907130244043855</v>
+        <v>7.272</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1764331211471542</v>
+        <v>-0.4852</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.528662422943085</v>
+        <v>-9.704000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.21</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1382733115833747</v>
+        <v>0.4568</v>
       </c>
       <c r="J147" t="n">
-        <v>2.765466231667495</v>
+        <v>9.135999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>0.95</v>
       </c>
       <c r="I148" t="n">
-        <v>0.06004765698543883</v>
+        <v>-0.046</v>
       </c>
       <c r="J148" t="n">
-        <v>1.200953139708776</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>0.78</v>
       </c>
       <c r="I149" t="n">
-        <v>0.01637540241672324</v>
+        <v>-0.3641</v>
       </c>
       <c r="J149" t="n">
-        <v>0.3275080483344647</v>
+        <v>-7.282</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.009473120098819329</v>
+        <v>-0.497</v>
       </c>
       <c r="J150" t="n">
-        <v>-0.1894624019763866</v>
+        <v>-9.94</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.04488908876991526</v>
+        <v>-0.6554</v>
       </c>
       <c r="J151" t="n">
-        <v>-0.8977817753983053</v>
+        <v>-13.108</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.34</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1648074233122447</v>
+        <v>0.5923</v>
       </c>
       <c r="J152" t="n">
-        <v>3.955378159493874</v>
+        <v>14.2152</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.0865780438619336</v>
+        <v>0.1983</v>
       </c>
       <c r="J153" t="n">
-        <v>2.077873052686407</v>
+        <v>4.7592</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>0.87</v>
       </c>
       <c r="I154" t="n">
-        <v>0.03567388297066641</v>
+        <v>-0.258</v>
       </c>
       <c r="J154" t="n">
-        <v>0.8561731912959939</v>
+        <v>-6.192</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>0.01559705747699008</v>
+        <v>-0.3682</v>
       </c>
       <c r="J155" t="n">
-        <v>0.3743293794477618</v>
+        <v>-8.8368</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.62</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.03736179851022957</v>
+        <v>-0.6117</v>
       </c>
       <c r="J156" t="n">
-        <v>-0.8966831642455096</v>
+        <v>-14.6808</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.37</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3293225380167303</v>
+        <v>1.0169</v>
       </c>
       <c r="J157" t="n">
-        <v>7.903740912401528</v>
+        <v>24.4056</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>1.24</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2143603681260731</v>
+        <v>0.7208</v>
       </c>
       <c r="J158" t="n">
-        <v>5.144648835025755</v>
+        <v>17.2992</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>0.96</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.008289310572913836</v>
+        <v>-0.2452</v>
       </c>
       <c r="J159" t="n">
-        <v>-0.1989434537499321</v>
+        <v>-5.8848</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.02446303159300352</v>
+        <v>-0.3121</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.5871127582320844</v>
+        <v>-7.4904</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.08385970970211942</v>
+        <v>-0.516</v>
       </c>
       <c r="J161" t="n">
-        <v>-2.012633032850866</v>
+        <v>-12.384</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.34</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1747225667892472</v>
+        <v>0.523</v>
       </c>
       <c r="J162" t="n">
-        <v>4.018619036152686</v>
+        <v>12.029</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.27</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1336090162911868</v>
+        <v>0.4303</v>
       </c>
       <c r="J163" t="n">
-        <v>3.073007374697295</v>
+        <v>9.8969</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I164" t="n">
-        <v>0.05252860011177397</v>
+        <v>0.1685</v>
       </c>
       <c r="J164" t="n">
-        <v>1.208157802570801</v>
+        <v>3.8755</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>1.1</v>
       </c>
       <c r="I165" t="n">
-        <v>0.04731513985779178</v>
+        <v>0.1511</v>
       </c>
       <c r="J165" t="n">
-        <v>1.088248216729211</v>
+        <v>3.4753</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.04164723233580356</v>
+        <v>-0.1974</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.9578863437234818</v>
+        <v>-4.5402</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.23</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1283200064514212</v>
+        <v>0.4138</v>
       </c>
       <c r="J167" t="n">
-        <v>2.951360148382687</v>
+        <v>9.5174</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.08240330513464403</v>
+        <v>0.2476</v>
       </c>
       <c r="J168" t="n">
-        <v>1.895276018096813</v>
+        <v>5.6948</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>1.04</v>
       </c>
       <c r="I169" t="n">
-        <v>0.05218778036687872</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="J169" t="n">
-        <v>1.200318948438211</v>
+        <v>2.1574</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.99</v>
       </c>
       <c r="I170" t="n">
-        <v>0.03506305662448025</v>
+        <v>-0.0584</v>
       </c>
       <c r="J170" t="n">
-        <v>0.8064503023630458</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.04733665154098696</v>
+        <v>-0.3915</v>
       </c>
       <c r="J171" t="n">
-        <v>-1.0887429854427</v>
+        <v>-9.0045</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1417299052111936</v>
+        <v>0.5636</v>
       </c>
       <c r="J172" t="n">
-        <v>3.401517725068647</v>
+        <v>13.5264</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.07836918934455916</v>
+        <v>0.2522</v>
       </c>
       <c r="J173" t="n">
-        <v>1.88086054426942</v>
+        <v>6.0528</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.05993868073310434</v>
+        <v>0.1239</v>
       </c>
       <c r="J174" t="n">
-        <v>1.438528337594504</v>
+        <v>2.9736</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>0.01584483076151714</v>
+        <v>-0.2681</v>
       </c>
       <c r="J175" t="n">
-        <v>0.3802759382764113</v>
+        <v>-6.4344</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.02840280407050554</v>
+        <v>-0.4852</v>
       </c>
       <c r="J176" t="n">
-        <v>-0.6816672976921329</v>
+        <v>-11.6448</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.4</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2987624469822116</v>
+        <v>1.0489</v>
       </c>
       <c r="J177" t="n">
-        <v>7.170298727573078</v>
+        <v>25.1736</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2278296840248947</v>
+        <v>0.8739</v>
       </c>
       <c r="J178" t="n">
-        <v>5.467912416597473</v>
+        <v>20.9736</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>1.02</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.01087943697097921</v>
+        <v>0.0049</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.2611064873035009</v>
+        <v>0.1176</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>0.98</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.04425749544423276</v>
+        <v>-0.1988</v>
       </c>
       <c r="J180" t="n">
-        <v>-1.062179890661586</v>
+        <v>-4.7712</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.06156211530866809</v>
+        <v>-0.2721</v>
       </c>
       <c r="J181" t="n">
-        <v>-1.477490767408034</v>
+        <v>-6.5304</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.14</v>
       </c>
       <c r="I182" t="n">
-        <v>0.138941365959727</v>
+        <v>0.3741</v>
       </c>
       <c r="J182" t="n">
-        <v>2.362003221315359</v>
+        <v>6.3597</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>0.93</v>
       </c>
       <c r="I183" t="n">
-        <v>0.06754339092951019</v>
+        <v>-0.0623</v>
       </c>
       <c r="J183" t="n">
-        <v>1.148237645801673</v>
+        <v>-1.0591</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>0.77</v>
       </c>
       <c r="I184" t="n">
-        <v>0.02016332283531633</v>
+        <v>-0.355</v>
       </c>
       <c r="J184" t="n">
-        <v>0.3427764882003777</v>
+        <v>-6.035</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.61</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.03056522648754366</v>
+        <v>-0.5918</v>
       </c>
       <c r="J185" t="n">
-        <v>-0.5196088502882422</v>
+        <v>-10.0606</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.5</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.06703695835073301</v>
+        <v>-0.7326</v>
       </c>
       <c r="J186" t="n">
-        <v>-1.139628291962461</v>
+        <v>-12.4542</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.6</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2430706606924687</v>
+        <v>1.3563</v>
       </c>
       <c r="J187" t="n">
-        <v>4.132201231771967</v>
+        <v>23.0571</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1478833426398852</v>
+        <v>0.9684</v>
       </c>
       <c r="J188" t="n">
-        <v>2.514016824878048</v>
+        <v>16.4628</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.31</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1061332984295476</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="J189" t="n">
-        <v>1.804266073302308</v>
+        <v>12.1244</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>1.3</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1019012138609076</v>
+        <v>0.6878</v>
       </c>
       <c r="J190" t="n">
-        <v>1.732320635635429</v>
+        <v>11.6926</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>1.03</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.03424867907680523</v>
+        <v>-0.0287</v>
       </c>
       <c r="J191" t="n">
-        <v>-0.582227544305689</v>
+        <v>-0.4879</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.62</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3750497337904948</v>
+        <v>0.842</v>
       </c>
       <c r="J192" t="n">
-        <v>7.876044409600391</v>
+        <v>17.682</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.38</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2152576996022035</v>
+        <v>0.5649</v>
       </c>
       <c r="J193" t="n">
-        <v>4.520411691646274</v>
+        <v>11.8629</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.01086466507504923</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>-0.2281579665760338</v>
+        <v>-0.1785</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.06282629175907126</v>
+        <v>-0.2031</v>
       </c>
       <c r="J195" t="n">
-        <v>-1.319352126940496</v>
+        <v>-4.2651</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.06282629175907126</v>
+        <v>-0.2031</v>
       </c>
       <c r="J196" t="n">
-        <v>-1.319352126940496</v>
+        <v>-4.2651</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.09601820759681322</v>
+        <v>0.3257</v>
       </c>
       <c r="J197" t="n">
-        <v>2.016382359533078</v>
+        <v>6.8397</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.08</v>
       </c>
       <c r="I198" t="n">
-        <v>0.07829678186809852</v>
+        <v>0.2109</v>
       </c>
       <c r="J198" t="n">
-        <v>1.644232419230069</v>
+        <v>4.4289</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>1.04</v>
       </c>
       <c r="I199" t="n">
-        <v>0.06826471363808528</v>
+        <v>0.1347</v>
       </c>
       <c r="J199" t="n">
-        <v>1.433558986399791</v>
+        <v>2.8287</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.88</v>
       </c>
       <c r="I200" t="n">
-        <v>0.03302029371136535</v>
+        <v>-0.2463</v>
       </c>
       <c r="J200" t="n">
-        <v>0.6934261679386723</v>
+        <v>-5.1723</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.03331512080054364</v>
+        <v>-0.6141</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.6996175368114164</v>
+        <v>-12.8961</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>0.98</v>
       </c>
       <c r="I202" t="n">
-        <v>0.08518832192414988</v>
+        <v>0.0431</v>
       </c>
       <c r="J202" t="n">
-        <v>1.618578116558848</v>
+        <v>0.8189</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>0.06825071296017481</v>
+        <v>-0.0587</v>
       </c>
       <c r="J203" t="n">
-        <v>1.296763546243321</v>
+        <v>-1.1153</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>0.77</v>
       </c>
       <c r="I204" t="n">
-        <v>0.02036901450494278</v>
+        <v>-0.3495</v>
       </c>
       <c r="J204" t="n">
-        <v>0.3870112755939128</v>
+        <v>-6.6405</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.66</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.01320204290841909</v>
+        <v>-0.5208</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.2508388152599627</v>
+        <v>-9.895200000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.04295577005256403</v>
+        <v>-0.6423</v>
       </c>
       <c r="J206" t="n">
-        <v>-0.8161596309987165</v>
+        <v>-12.2037</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.68</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2745799311514616</v>
+        <v>1.497</v>
       </c>
       <c r="J207" t="n">
-        <v>5.217018691877771</v>
+        <v>28.443</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.68</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2745799311514616</v>
+        <v>1.497</v>
       </c>
       <c r="J208" t="n">
-        <v>5.217018691877771</v>
+        <v>28.443</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>1.33</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1082014450611929</v>
+        <v>0.7477</v>
       </c>
       <c r="J209" t="n">
-        <v>2.055827456162664</v>
+        <v>14.2063</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>1.17</v>
       </c>
       <c r="I210" t="n">
-        <v>0.02998286782090132</v>
+        <v>0.3599</v>
       </c>
       <c r="J210" t="n">
-        <v>0.5696744885971251</v>
+        <v>6.8381</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.9</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1084813323697345</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="J211" t="n">
-        <v>-2.061145315024956</v>
+        <v>-9.7774</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.05</v>
       </c>
       <c r="I212" t="n">
-        <v>0.08584125309031407</v>
+        <v>0.1709</v>
       </c>
       <c r="J212" t="n">
-        <v>2.060190074167537</v>
+        <v>4.1016</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.07939577805855949</v>
+        <v>0.1299</v>
       </c>
       <c r="J213" t="n">
-        <v>1.905498673405428</v>
+        <v>3.1176</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.07939577805855949</v>
+        <v>0.1299</v>
       </c>
       <c r="J214" t="n">
-        <v>1.905498673405428</v>
+        <v>3.1176</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.77</v>
       </c>
       <c r="I215" t="n">
-        <v>0.002701035048398685</v>
+        <v>-0.4048</v>
       </c>
       <c r="J215" t="n">
-        <v>0.06482484116156845</v>
+        <v>-9.715199999999999</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.02346159959658409</v>
+        <v>-0.516</v>
       </c>
       <c r="J216" t="n">
-        <v>-0.5630783903180181</v>
+        <v>-12.384</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.55</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3619248628773051</v>
+        <v>1.3459</v>
       </c>
       <c r="J217" t="n">
-        <v>8.686196709055324</v>
+        <v>32.3016</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.14</v>
       </c>
       <c r="I218" t="n">
-        <v>0.08648001493503035</v>
+        <v>0.387</v>
       </c>
       <c r="J218" t="n">
-        <v>2.075520358440729</v>
+        <v>9.288</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>0.04283866110125802</v>
+        <v>0.1715</v>
       </c>
       <c r="J219" t="n">
-        <v>1.028127866430192</v>
+        <v>4.116</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>1.04</v>
       </c>
       <c r="I220" t="n">
-        <v>0.02236802102835367</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J220" t="n">
-        <v>0.536832504680488</v>
+        <v>1.7376</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.04015033533930518</v>
+        <v>-0.3109</v>
       </c>
       <c r="J221" t="n">
-        <v>-0.9636080481433242</v>
+        <v>-7.4616</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.21</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1659691243339404</v>
+        <v>0.5073</v>
       </c>
       <c r="J222" t="n">
-        <v>2.821475113676987</v>
+        <v>8.6241</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>0.73</v>
       </c>
       <c r="I223" t="n">
-        <v>0.01487044135422032</v>
+        <v>-0.3722</v>
       </c>
       <c r="J223" t="n">
-        <v>0.2527975030217454</v>
+        <v>-6.3274</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.6</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.02140437541302695</v>
+        <v>-0.5851</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.3638743820214582</v>
+        <v>-9.9467</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.54</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.04031339448982146</v>
+        <v>-0.6663</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.6853277063269649</v>
+        <v>-11.3271</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.04031339448982146</v>
+        <v>-0.6663</v>
       </c>
       <c r="J226" t="n">
-        <v>-0.6853277063269649</v>
+        <v>-11.3271</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>2.35</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7105026108827786</v>
+        <v>2.181</v>
       </c>
       <c r="J227" t="n">
-        <v>12.07854438500724</v>
+        <v>37.077</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.59</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2299615468336603</v>
+        <v>1.2707</v>
       </c>
       <c r="J228" t="n">
-        <v>3.909346296172225</v>
+        <v>21.6019</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>1.31</v>
       </c>
       <c r="I229" t="n">
-        <v>0.05568033977259955</v>
+        <v>0.6429</v>
       </c>
       <c r="J229" t="n">
-        <v>0.9465657761341923</v>
+        <v>10.9293</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>1.21</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.01438540851444835</v>
+        <v>0.4169</v>
       </c>
       <c r="J230" t="n">
-        <v>-0.2445519447456219</v>
+        <v>7.0873</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.91</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2206584700474984</v>
+        <v>-0.5114</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.751193990807474</v>
+        <v>-8.6938</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8413/event_8413_evp_summary.xlsx
+++ b/database/event/8413/event_8413_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.4444</v>
       </c>
       <c r="D2" t="n">
-        <v>3.429</v>
+        <v>3.3533</v>
       </c>
       <c r="E2" t="n">
         <v>9.5311</v>
@@ -548,7 +548,7 @@
         <v>1.9431</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6394</v>
+        <v>2.5746</v>
       </c>
       <c r="E3" t="n">
         <v>7.5766</v>
@@ -594,7 +594,7 @@
         <v>1.6159</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1239</v>
+        <v>2.0662</v>
       </c>
       <c r="E4" t="n">
         <v>6.3006</v>
@@ -640,7 +640,7 @@
         <v>1.4073</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7953</v>
+        <v>1.7422</v>
       </c>
       <c r="E5" t="n">
         <v>5.4871</v>
@@ -686,7 +686,7 @@
         <v>1.353</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7098</v>
+        <v>1.6578</v>
       </c>
       <c r="E6" t="n">
         <v>5.2755</v>
@@ -732,7 +732,7 @@
         <v>1.0249</v>
       </c>
       <c r="D7" t="n">
-        <v>1.193</v>
+        <v>1.1482</v>
       </c>
       <c r="E7" t="n">
         <v>3.9962</v>
@@ -778,7 +778,7 @@
         <v>1.0196</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1847</v>
+        <v>1.14</v>
       </c>
       <c r="E8" t="n">
         <v>3.9757</v>
@@ -824,7 +824,7 @@
         <v>0.9732</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1117</v>
+        <v>1.0679</v>
       </c>
       <c r="E9" t="n">
         <v>3.7948</v>
@@ -870,7 +870,7 @@
         <v>0.7101</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6972</v>
+        <v>0.6592</v>
       </c>
       <c r="E10" t="n">
         <v>2.7689</v>
@@ -916,7 +916,7 @@
         <v>0.5432</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4343</v>
+        <v>0.3999</v>
       </c>
       <c r="E11" t="n">
         <v>2.1181</v>
@@ -962,7 +962,7 @@
         <v>0.5083</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3792</v>
+        <v>0.3456</v>
       </c>
       <c r="E12" t="n">
         <v>1.9818</v>
@@ -1008,7 +1008,7 @@
         <v>0.3822</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1807</v>
+        <v>0.1499</v>
       </c>
       <c r="E13" t="n">
         <v>1.4904</v>
@@ -1054,7 +1054,7 @@
         <v>0.3044</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0581</v>
+        <v>0.029</v>
       </c>
       <c r="E14" t="n">
         <v>1.1869</v>
@@ -1100,7 +1100,7 @@
         <v>0.2659</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0025</v>
+        <v>-0.0308</v>
       </c>
       <c r="E15" t="n">
         <v>1.0369</v>
@@ -1146,7 +1146,7 @@
         <v>0.2125</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0867</v>
+        <v>-0.1139</v>
       </c>
       <c r="E16" t="n">
         <v>0.8284</v>
@@ -1192,7 +1192,7 @@
         <v>0.1493</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1862</v>
+        <v>-0.212</v>
       </c>
       <c r="E17" t="n">
         <v>0.5822000000000001</v>
@@ -1238,7 +1238,7 @@
         <v>0.1363</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2067</v>
+        <v>-0.2322</v>
       </c>
       <c r="E18" t="n">
         <v>0.5313</v>
@@ -1284,7 +1284,7 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2836</v>
+        <v>-0.3081</v>
       </c>
       <c r="E19" t="n">
         <v>0.3409</v>
@@ -1330,7 +1330,7 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2838</v>
+        <v>-0.3082</v>
       </c>
       <c r="E20" t="n">
         <v>0.3406</v>
@@ -1376,7 +1376,7 @@
         <v>0.0439</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3523</v>
+        <v>-0.3758</v>
       </c>
       <c r="E21" t="n">
         <v>0.171</v>
@@ -1422,7 +1422,7 @@
         <v>0.0169</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3947</v>
+        <v>-0.4177</v>
       </c>
       <c r="E22" t="n">
         <v>0.0659</v>
@@ -1468,7 +1468,7 @@
         <v>-0.001</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.423</v>
+        <v>-0.4455</v>
       </c>
       <c r="E23" t="n">
         <v>-0.004</v>
@@ -1514,7 +1514,7 @@
         <v>-0.0086</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.435</v>
+        <v>-0.4573</v>
       </c>
       <c r="E24" t="n">
         <v>-0.0337</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0104</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4378</v>
+        <v>-0.4601</v>
       </c>
       <c r="E25" t="n">
         <v>-0.0406</v>
@@ -1606,7 +1606,7 @@
         <v>-0.1037</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5847</v>
+        <v>-0.6049</v>
       </c>
       <c r="E26" t="n">
         <v>-0.4042</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1045</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5859</v>
+        <v>-0.6062</v>
       </c>
       <c r="E27" t="n">
         <v>-0.4074</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1318</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6289</v>
+        <v>-0.6486</v>
       </c>
       <c r="E28" t="n">
         <v>-0.5138</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1652</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6815</v>
+        <v>-0.7005</v>
       </c>
       <c r="E29" t="n">
         <v>-0.644</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1788</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7030999999999999</v>
+        <v>-0.7217</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6973</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1841</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7114</v>
+        <v>-0.7299</v>
       </c>
       <c r="E31" t="n">
         <v>-0.7179</v>
@@ -1882,7 +1882,7 @@
         <v>-0.2288</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.7993</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8921</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2591</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8294</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="E33" t="n">
         <v>-1.0101</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2683</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8439</v>
+        <v>-0.8606</v>
       </c>
       <c r="E34" t="n">
         <v>-1.046</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3026</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8981</v>
+        <v>-0.914</v>
       </c>
       <c r="E35" t="n">
         <v>-1.18</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3095</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9089</v>
+        <v>-0.9247</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2069</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3334</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3334</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3867</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0305</v>
+        <v>-1.0446</v>
       </c>
       <c r="E39" t="n">
         <v>-1.5078</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5933</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3559</v>
+        <v>-1.3655</v>
       </c>
       <c r="E40" t="n">
         <v>-2.3133</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6641</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4675</v>
+        <v>-1.4756</v>
       </c>
       <c r="E41" t="n">
         <v>-2.5896</v>

--- a/database/event/8413/event_8413_evp_summary.xlsx
+++ b/database/event/8413/event_8413_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.5311</v>
+        <v>8.930999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4444</v>
+        <v>2.2905</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3533</v>
+        <v>3.3939</v>
       </c>
       <c r="E2" t="n">
-        <v>9.5311</v>
+        <v>8.930999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>9.5311</v>
+        <v>8.930999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3316</v>
+        <v>6.4005</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3316</v>
+        <v>6.4005</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.5766</v>
+        <v>7.4052</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9431</v>
+        <v>1.8992</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5746</v>
+        <v>2.7051</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5766</v>
+        <v>7.4052</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7.5766</v>
+        <v>7.4052</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8281</v>
+        <v>5.307</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8281</v>
+        <v>5.307</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3006</v>
+        <v>5.833</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6159</v>
+        <v>1.496</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0662</v>
+        <v>1.9953</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3006</v>
+        <v>5.833</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3006</v>
+        <v>5.833</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8466</v>
+        <v>4.1803</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>206</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8466</v>
+        <v>4.1803</v>
       </c>
       <c r="N4" t="n">
         <v>206</v>
@@ -630,26 +630,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4871</v>
+        <v>5.6982</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4073</v>
+        <v>1.4614</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7422</v>
+        <v>1.9344</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4871</v>
+        <v>5.6982</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4871</v>
+        <v>5.6982</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,44 +658,44 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2208</v>
+        <v>4.0837</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2208</v>
+        <v>4.0837</v>
       </c>
       <c r="N5" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2755</v>
+        <v>5.161</v>
       </c>
       <c r="C6" t="n">
-        <v>1.353</v>
+        <v>1.3236</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6578</v>
+        <v>1.6919</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2755</v>
+        <v>5.161</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2755</v>
+        <v>5.161</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,19 +704,19 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.0581</v>
+        <v>3.6987</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0581</v>
+        <v>3.6987</v>
       </c>
       <c r="N6" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9962</v>
+        <v>4.7668</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0249</v>
+        <v>1.2225</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1482</v>
+        <v>1.514</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9962</v>
+        <v>4.7668</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8824</v>
+        <v>1.8231</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1137</v>
+        <v>2.9436</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8824</v>
+        <v>1.8231</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8824</v>
+        <v>1.8231</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3952</v>
+        <v>2.1096</v>
       </c>
       <c r="K7" t="n">
         <v>66</v>
@@ -759,7 +759,7 @@
         <v>101</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2776</v>
+        <v>3.9327</v>
       </c>
       <c r="N7" t="n">
         <v>167</v>
@@ -768,26 +768,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9757</v>
+        <v>3.7589</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0196</v>
+        <v>0.964</v>
       </c>
       <c r="D8" t="n">
-        <v>1.14</v>
+        <v>1.0589</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9757</v>
+        <v>3.7589</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9757</v>
+        <v>3.7589</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,44 +796,44 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0582</v>
+        <v>2.6939</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0582</v>
+        <v>2.6939</v>
       </c>
       <c r="N8" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7948</v>
+        <v>3.2291</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9732</v>
+        <v>0.8282</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0679</v>
+        <v>0.8198</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7948</v>
+        <v>3.2291</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7948</v>
+        <v>3.2291</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,19 +842,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9191</v>
+        <v>2.3142</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9191</v>
+        <v>2.3142</v>
       </c>
       <c r="N9" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7689</v>
+        <v>2.6703</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7101</v>
+        <v>0.6848</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6592</v>
+        <v>0.5675</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7689</v>
+        <v>2.6703</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8764</v>
+        <v>1.1277</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8925</v>
+        <v>1.5426</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8764</v>
+        <v>1.1277</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8764</v>
+        <v>1.1277</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4558</v>
+        <v>1.1055</v>
       </c>
       <c r="K10" t="n">
         <v>66</v>
@@ -897,7 +897,7 @@
         <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3322</v>
+        <v>2.2332</v>
       </c>
       <c r="N10" t="n">
         <v>167</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1181</v>
+        <v>2.2134</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5432</v>
+        <v>0.5677</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3999</v>
+        <v>0.3612</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1181</v>
+        <v>2.2134</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2046</v>
+        <v>0.3665</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9135</v>
+        <v>1.8469</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2046</v>
+        <v>0.3665</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2046</v>
+        <v>0.3665</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4719</v>
+        <v>1.3236</v>
       </c>
       <c r="K11" t="n">
         <v>66</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6765</v>
+        <v>1.6901</v>
       </c>
       <c r="N11" t="n">
         <v>167</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9818</v>
+        <v>1.9896</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5083</v>
+        <v>0.5103</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3456</v>
+        <v>0.2602</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9818</v>
+        <v>1.9896</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2762</v>
+        <v>0.3102</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7056</v>
+        <v>1.6795</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2762</v>
+        <v>0.3102</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2762</v>
+        <v>0.3102</v>
       </c>
       <c r="J12" t="n">
-        <v>1.312</v>
+        <v>1.2036</v>
       </c>
       <c r="K12" t="n">
         <v>66</v>
@@ -989,7 +989,7 @@
         <v>133</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5882</v>
+        <v>1.5138</v>
       </c>
       <c r="N12" t="n">
         <v>199</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4904</v>
+        <v>1.4622</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3822</v>
+        <v>0.375</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1499</v>
+        <v>0.0221</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4904</v>
+        <v>1.4622</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4904</v>
+        <v>1.4622</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1465</v>
+        <v>1.0479</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1465</v>
+        <v>1.0479</v>
       </c>
       <c r="N13" t="n">
         <v>71</v>
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1869</v>
+        <v>1.2455</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3044</v>
+        <v>0.3194</v>
       </c>
       <c r="D14" t="n">
-        <v>0.029</v>
+        <v>-0.0757</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1869</v>
+        <v>1.2455</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1869</v>
+        <v>1.2455</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.913</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>0.913</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>71</v>
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0369</v>
+        <v>1.1597</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2659</v>
+        <v>0.2974</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0308</v>
+        <v>-0.1145</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0369</v>
+        <v>1.1597</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0369</v>
+        <v>1.1597</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7976</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>206</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7976</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>206</v>
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8284</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2125</v>
+        <v>0.2168</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1139</v>
+        <v>-0.2564</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8284</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8284</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6372</v>
+        <v>0.6058</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>41</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6372</v>
+        <v>0.6058</v>
       </c>
       <c r="N16" t="n">
         <v>41</v>
@@ -1182,127 +1182,127 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ryu</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5637</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1493</v>
+        <v>0.1446</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.212</v>
+        <v>-0.3835</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5637</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5214</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1036</v>
+        <v>0.5637</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5214</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5214</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8489</v>
+        <v>0.404</v>
       </c>
       <c r="K17" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3275</v>
+        <v>0.404</v>
       </c>
       <c r="N17" t="n">
-        <v>167</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>ryu</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5313</v>
+        <v>0.4628</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1363</v>
+        <v>0.1187</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2322</v>
+        <v>-0.4291</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5313</v>
+        <v>0.4628</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.3225</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5313</v>
+        <v>0.7853</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.3225</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.3225</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4087</v>
+        <v>0.5628</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L18" t="n">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4087</v>
+        <v>0.2403</v>
       </c>
       <c r="N18" t="n">
-        <v>57</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dziugss</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3409</v>
+        <v>0.3552</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0911</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3081</v>
+        <v>-0.4777</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3409</v>
+        <v>0.3552</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2742</v>
+        <v>0.0675</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0667</v>
+        <v>0.2877</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2742</v>
+        <v>0.0675</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2742</v>
+        <v>0.0675</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0513</v>
+        <v>0.2062</v>
       </c>
       <c r="K19" t="n">
         <v>66</v>
@@ -1311,7 +1311,7 @@
         <v>133</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3255</v>
+        <v>0.2737</v>
       </c>
       <c r="N19" t="n">
         <v>199</v>
@@ -1320,35 +1320,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3406</v>
+        <v>0.3483</v>
       </c>
       <c r="C20" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0893</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3082</v>
+        <v>-0.4808</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3406</v>
+        <v>0.3483</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0237</v>
+        <v>-0.3697</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3643</v>
+        <v>0.7179</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0237</v>
+        <v>-0.3697</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0237</v>
+        <v>-0.3697</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2802</v>
+        <v>0.5145</v>
       </c>
       <c r="K20" t="n">
         <v>66</v>
@@ -1357,7 +1357,7 @@
         <v>133</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2565</v>
+        <v>0.1448</v>
       </c>
       <c r="N20" t="n">
         <v>199</v>
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.171</v>
+        <v>0.3195</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0439</v>
+        <v>0.0819</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3758</v>
+        <v>-0.4938</v>
       </c>
       <c r="E21" t="n">
-        <v>0.171</v>
+        <v>0.3195</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.171</v>
+        <v>0.3195</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1315</v>
+        <v>0.229</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>39</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1315</v>
+        <v>0.229</v>
       </c>
       <c r="N21" t="n">
         <v>39</v>
@@ -1412,26 +1412,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0659</v>
+        <v>0.2188</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0169</v>
+        <v>0.0561</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4177</v>
+        <v>-0.5392</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0659</v>
+        <v>0.2188</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0659</v>
+        <v>0.2188</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,19 +1440,19 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0507</v>
+        <v>0.1568</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>57</v>
+        <v>206</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0507</v>
+        <v>0.1568</v>
       </c>
       <c r="N22" t="n">
-        <v>57</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23">
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.004</v>
+        <v>0.1192</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.001</v>
+        <v>0.0306</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4455</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.004</v>
+        <v>0.1192</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.004</v>
+        <v>0.1192</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0031</v>
+        <v>0.0854</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>71</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0031</v>
+        <v>0.0854</v>
       </c>
       <c r="N23" t="n">
         <v>71</v>
@@ -1504,118 +1504,118 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0337</v>
+        <v>0.0223</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0086</v>
+        <v>0.0057</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4573</v>
+        <v>-0.6279</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0337</v>
+        <v>0.0223</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4663</v>
+        <v>0.0223</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3587</v>
+        <v>0.016</v>
       </c>
       <c r="K24" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1413</v>
+        <v>0.016</v>
       </c>
       <c r="N24" t="n">
-        <v>199</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>dziugss</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0406</v>
+        <v>0.0061</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0104</v>
+        <v>0.0016</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4601</v>
+        <v>-0.6353</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0406</v>
+        <v>0.0061</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.2538</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0406</v>
+        <v>-0.2477</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.2538</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.2538</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0312</v>
+        <v>-0.1775</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L25" t="n">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0312</v>
+        <v>0.07630000000000003</v>
       </c>
       <c r="N25" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4042</v>
+        <v>-0.0772</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1037</v>
+        <v>-0.0198</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6049</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4042</v>
+        <v>-0.0772</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4042</v>
+        <v>-0.0772</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3109</v>
+        <v>-0.0553</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3109</v>
+        <v>-0.0553</v>
       </c>
       <c r="N26" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4074</v>
+        <v>-0.2235</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1045</v>
+        <v>-0.0573</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6062</v>
+        <v>-0.7389</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4074</v>
+        <v>-0.2235</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4074</v>
+        <v>-0.2235</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,19 +1670,19 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3134</v>
+        <v>-0.1602</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3134</v>
+        <v>-0.1602</v>
       </c>
       <c r="N27" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
@@ -1692,22 +1692,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5138</v>
+        <v>-0.2435</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1318</v>
+        <v>-0.0624</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6486</v>
+        <v>-0.7479</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5138</v>
+        <v>-0.2435</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5138</v>
+        <v>-0.2435</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3952</v>
+        <v>-0.1745</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>39</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3952</v>
+        <v>-0.1745</v>
       </c>
       <c r="N28" t="n">
         <v>39</v>
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.644</v>
+        <v>-0.4016</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1652</v>
+        <v>-0.103</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7005</v>
+        <v>-0.8193</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.644</v>
+        <v>-0.4016</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.644</v>
+        <v>-0.4016</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4954</v>
+        <v>-0.2878</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>41</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4954</v>
+        <v>-0.2878</v>
       </c>
       <c r="N29" t="n">
         <v>41</v>
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6973</v>
+        <v>-0.4702</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1788</v>
+        <v>-0.1206</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7217</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6973</v>
+        <v>-0.4702</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6973</v>
+        <v>-0.4702</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5364</v>
+        <v>-0.337</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>41</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5364</v>
+        <v>-0.337</v>
       </c>
       <c r="N30" t="n">
         <v>41</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7179</v>
+        <v>-0.5411</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1841</v>
+        <v>-0.1388</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7299</v>
+        <v>-0.8823</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7179</v>
+        <v>-0.5411</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.7179</v>
+        <v>-0.5411</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5522</v>
+        <v>-0.3878</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5522</v>
+        <v>-0.3878</v>
       </c>
       <c r="N31" t="n">
         <v>39</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8921</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2288</v>
+        <v>-0.1736</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7993</v>
+        <v>-0.9436</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8921</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8921</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6862</v>
+        <v>-0.4851</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>39</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6862</v>
+        <v>-0.4851</v>
       </c>
       <c r="N32" t="n">
         <v>39</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0101</v>
+        <v>-0.7415</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2591</v>
+        <v>-0.1902</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.9728</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0101</v>
+        <v>-0.7415</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.0101</v>
+        <v>-0.7415</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.777</v>
+        <v>-0.5314</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>41</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.777</v>
+        <v>-0.5314</v>
       </c>
       <c r="N33" t="n">
         <v>41</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.046</v>
+        <v>-0.7454</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2683</v>
+        <v>-0.1912</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8606</v>
+        <v>-0.9745</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.046</v>
+        <v>-0.7454</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.046</v>
+        <v>-0.7454</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8046</v>
+        <v>-0.5342</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>39</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8046</v>
+        <v>-0.5342</v>
       </c>
       <c r="N34" t="n">
         <v>39</v>
@@ -2010,26 +2010,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.18</v>
+        <v>-0.7577</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3026</v>
+        <v>-0.1943</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.914</v>
+        <v>-0.9801</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.18</v>
+        <v>-0.7577</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.18</v>
+        <v>-0.7577</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,44 +2038,44 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9077</v>
+        <v>-0.543</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9077</v>
+        <v>-0.543</v>
       </c>
       <c r="N35" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2069</v>
+        <v>-0.8517</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3095</v>
+        <v>-0.2184</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9247</v>
+        <v>-1.0225</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2069</v>
+        <v>-0.8517</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.2069</v>
+        <v>-0.8517</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,65 +2084,65 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9284</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9284</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3</v>
+        <v>-0.9567</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3334</v>
+        <v>-0.2454</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9618</v>
+        <v>-1.0699</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3</v>
+        <v>-0.9567</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-0.2328</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.3</v>
+        <v>-0.7239</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-0.2328</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>-0.2328</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>-0.5188</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L37" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="M37" t="n">
-        <v>-1</v>
+        <v>-0.7516</v>
       </c>
       <c r="N37" t="n">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38">
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3</v>
+        <v>-1.0167</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3334</v>
+        <v>-0.2607</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9618</v>
+        <v>-1.097</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3</v>
+        <v>-1.0167</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.3</v>
+        <v>-1.0167</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-1</v>
+        <v>-0.7286</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>41</v>
       </c>
       <c r="M38" t="n">
-        <v>-1</v>
+        <v>-0.7286</v>
       </c>
       <c r="N38" t="n">
         <v>41</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5078</v>
+        <v>-1.0361</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3867</v>
+        <v>-0.2657</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0446</v>
+        <v>-1.1058</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5078</v>
+        <v>-1.0361</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.417</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.0908</v>
+        <v>-1.0361</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.417</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.417</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8391</v>
+        <v>-0.7425</v>
       </c>
       <c r="K39" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2561</v>
+        <v>-0.7425</v>
       </c>
       <c r="N39" t="n">
-        <v>199</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.3133</v>
+        <v>-2.0639</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5933</v>
+        <v>-0.5293</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3655</v>
+        <v>-1.5698</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.3133</v>
+        <v>-2.0639</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.654</v>
+        <v>-0.4728</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.6593</v>
+        <v>-1.5911</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.654</v>
+        <v>-0.4728</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.654</v>
+        <v>-0.4728</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.2764</v>
+        <v>-1.1403</v>
       </c>
       <c r="K40" t="n">
         <v>66</v>
@@ -2277,7 +2277,7 @@
         <v>101</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9304</v>
+        <v>-1.6131</v>
       </c>
       <c r="N40" t="n">
         <v>167</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5896</v>
+        <v>-2.325</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6641</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4756</v>
+        <v>-1.6876</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5896</v>
+        <v>-2.325</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.5896</v>
+        <v>-2.325</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.992</v>
+        <v>-1.6662</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>190</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.992</v>
+        <v>-1.6662</v>
       </c>
       <c r="N41" t="n">
         <v>190</v>
@@ -2429,10 +2429,10 @@
         <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9614</v>
+        <v>1.6543</v>
       </c>
       <c r="J2" t="n">
-        <v>39.228</v>
+        <v>33.086</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.45</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0613</v>
+        <v>1.054</v>
       </c>
       <c r="J3" t="n">
-        <v>21.226</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9305</v>
+        <v>0.9599</v>
       </c>
       <c r="J4" t="n">
-        <v>18.61</v>
+        <v>19.198</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3303</v>
+        <v>-0.2452</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.606</v>
+        <v>-4.904</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.84</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6604</v>
+        <v>-0.5968</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.208</v>
+        <v>-11.936</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1665</v>
+        <v>0.1445</v>
       </c>
       <c r="J7" t="n">
-        <v>3.33</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1442</v>
+        <v>0.117</v>
       </c>
       <c r="J8" t="n">
-        <v>2.884</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1504</v>
+        <v>-0.1266</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.008</v>
+        <v>-2.532</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4779</v>
+        <v>-0.3139</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.558</v>
+        <v>-6.278</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.48</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7631</v>
+        <v>-0.5188</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.262</v>
+        <v>-10.376</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>0.67</v>
+        <v>0.6284</v>
       </c>
       <c r="J12" t="n">
-        <v>16.08</v>
+        <v>15.0816</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2279</v>
+        <v>0.1885</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4696</v>
+        <v>4.524</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.96</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1145</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.748</v>
+        <v>-1.5168</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2279</v>
+        <v>-0.1342</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.4696</v>
+        <v>-3.2208</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6214</v>
+        <v>-0.4109</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.9136</v>
+        <v>-9.861599999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.37</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5844</v>
+        <v>0.5043</v>
       </c>
       <c r="J17" t="n">
-        <v>14.0256</v>
+        <v>12.1032</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0668</v>
+        <v>0.0752</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6032</v>
+        <v>1.8048</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.045</v>
+        <v>0.0579</v>
       </c>
       <c r="J19" t="n">
-        <v>1.08</v>
+        <v>1.3896</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1202</v>
+        <v>-0.0575</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.8848</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1202</v>
+        <v>-0.0575</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.8848</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.72</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6428</v>
+        <v>1.419</v>
       </c>
       <c r="J22" t="n">
-        <v>34.4988</v>
+        <v>29.799</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7235</v>
+        <v>0.7256</v>
       </c>
       <c r="J23" t="n">
-        <v>15.1935</v>
+        <v>15.2376</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5669</v>
+        <v>0.5844</v>
       </c>
       <c r="J24" t="n">
-        <v>11.9049</v>
+        <v>12.2724</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2099</v>
+        <v>0.2754</v>
       </c>
       <c r="J25" t="n">
-        <v>4.4079</v>
+        <v>5.7834</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9971</v>
+        <v>-0.9715</v>
       </c>
       <c r="J26" t="n">
-        <v>-20.9391</v>
+        <v>-20.4015</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.6192</v>
       </c>
       <c r="J27" t="n">
-        <v>10.9977</v>
+        <v>13.0032</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.18</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3715</v>
+        <v>0.4177</v>
       </c>
       <c r="J28" t="n">
-        <v>7.8015</v>
+        <v>8.771699999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.18</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3715</v>
+        <v>0.4177</v>
       </c>
       <c r="J29" t="n">
-        <v>7.8015</v>
+        <v>8.771699999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.62</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6137</v>
+        <v>-0.4056</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.8877</v>
+        <v>-8.5176</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.49</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.5238</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.1637</v>
+        <v>-10.9998</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.29</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8005</v>
+        <v>0.7873</v>
       </c>
       <c r="J32" t="n">
-        <v>17.611</v>
+        <v>17.3206</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7771</v>
+        <v>0.7637</v>
       </c>
       <c r="J33" t="n">
-        <v>17.0962</v>
+        <v>16.8014</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.27</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7534</v>
+        <v>0.74</v>
       </c>
       <c r="J34" t="n">
-        <v>16.5748</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.19</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5511</v>
+        <v>0.5461</v>
       </c>
       <c r="J35" t="n">
-        <v>12.1242</v>
+        <v>12.0142</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9653</v>
+        <v>-0.9361</v>
       </c>
       <c r="J36" t="n">
-        <v>-21.2366</v>
+        <v>-20.5942</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.331</v>
+        <v>0.3604</v>
       </c>
       <c r="J37" t="n">
-        <v>7.282</v>
+        <v>7.9288</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.07</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2147</v>
+        <v>0.2127</v>
       </c>
       <c r="J38" t="n">
-        <v>4.7234</v>
+        <v>4.6794</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.93</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.113</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.486</v>
+        <v>-1.9998</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.79</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3703</v>
+        <v>-0.2366</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.146599999999999</v>
+        <v>-5.2052</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6787</v>
+        <v>-0.4546</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.9314</v>
+        <v>-10.0012</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.97</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1756</v>
+        <v>1.0575</v>
       </c>
       <c r="J42" t="n">
-        <v>24.6876</v>
+        <v>22.2075</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.38</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5406</v>
+        <v>0.4812</v>
       </c>
       <c r="J43" t="n">
-        <v>11.3526</v>
+        <v>10.1052</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.17</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2291</v>
+        <v>0.2391</v>
       </c>
       <c r="J44" t="n">
-        <v>4.8111</v>
+        <v>5.0211</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.91</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2674</v>
+        <v>-0.1496</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.6154</v>
+        <v>-3.1416</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.87</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3289</v>
+        <v>-0.1935</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.9069</v>
+        <v>-4.0635</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.62</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9298</v>
+        <v>0.92</v>
       </c>
       <c r="J47" t="n">
-        <v>19.5258</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4982</v>
+        <v>0.4463</v>
       </c>
       <c r="J48" t="n">
-        <v>10.4622</v>
+        <v>9.372299999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.67</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5421</v>
+        <v>-0.3541</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.3841</v>
+        <v>-7.4361</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.57</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6688</v>
+        <v>-0.4471</v>
       </c>
       <c r="J50" t="n">
-        <v>-14.0448</v>
+        <v>-9.389099999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.44</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8223</v>
+        <v>-0.5646</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.2683</v>
+        <v>-11.8566</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.86</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1624</v>
+        <v>-0.1447</v>
       </c>
       <c r="J52" t="n">
-        <v>-2.7608</v>
+        <v>-2.4599</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.85</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.179</v>
+        <v>-0.1557</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.043</v>
+        <v>-2.6469</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.77</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3124</v>
+        <v>-0.2379</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.3108</v>
+        <v>-4.0443</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.66</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5059</v>
+        <v>-0.3398</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.600300000000001</v>
+        <v>-5.7766</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.424</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.7372</v>
+        <v>-7.208</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.07</v>
       </c>
       <c r="I57" t="n">
-        <v>2.0593</v>
+        <v>1.7853</v>
       </c>
       <c r="J57" t="n">
-        <v>35.0081</v>
+        <v>30.3501</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.6763</v>
       </c>
       <c r="J58" t="n">
-        <v>9.9314</v>
+        <v>11.4971</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3893</v>
+        <v>0.4831</v>
       </c>
       <c r="J59" t="n">
-        <v>6.6181</v>
+        <v>8.2127</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2354</v>
+        <v>0.3257</v>
       </c>
       <c r="J60" t="n">
-        <v>4.0018</v>
+        <v>5.5369</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.07</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0959</v>
+        <v>0.1819</v>
       </c>
       <c r="J61" t="n">
-        <v>1.6303</v>
+        <v>3.0923</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3824</v>
+        <v>0.4292</v>
       </c>
       <c r="J62" t="n">
-        <v>10.7072</v>
+        <v>12.0176</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1869</v>
+        <v>0.1821</v>
       </c>
       <c r="J63" t="n">
-        <v>5.2332</v>
+        <v>5.0988</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0132</v>
       </c>
       <c r="J64" t="n">
-        <v>0.2352</v>
+        <v>-0.3696</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.72</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4773</v>
+        <v>-0.3079</v>
       </c>
       <c r="J65" t="n">
-        <v>-13.3644</v>
+        <v>-8.6212</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5572</v>
+        <v>-0.3648</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.6016</v>
+        <v>-10.2144</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.78</v>
       </c>
       <c r="I67" t="n">
-        <v>1.7368</v>
+        <v>1.4834</v>
       </c>
       <c r="J67" t="n">
-        <v>48.6304</v>
+        <v>41.5352</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.54</v>
       </c>
       <c r="I68" t="n">
-        <v>1.2907</v>
+        <v>1.1869</v>
       </c>
       <c r="J68" t="n">
-        <v>36.1396</v>
+        <v>33.2332</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.22</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.6041</v>
       </c>
       <c r="J69" t="n">
-        <v>15.736</v>
+        <v>16.9148</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7351</v>
+        <v>-0.6803</v>
       </c>
       <c r="J70" t="n">
-        <v>-20.5828</v>
+        <v>-19.0484</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8047</v>
+        <v>-0.7567</v>
       </c>
       <c r="J71" t="n">
-        <v>-22.5316</v>
+        <v>-21.1876</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4611</v>
+        <v>0.381</v>
       </c>
       <c r="J72" t="n">
-        <v>11.0664</v>
+        <v>9.144</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4199</v>
+        <v>0.357</v>
       </c>
       <c r="J73" t="n">
-        <v>10.0776</v>
+        <v>8.568</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.14</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2868</v>
+        <v>0.2455</v>
       </c>
       <c r="J74" t="n">
-        <v>6.8832</v>
+        <v>5.892</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3877</v>
+        <v>-0.2411</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.3048</v>
+        <v>-5.7864</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5745</v>
+        <v>-0.3758</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.788</v>
+        <v>-9.0192</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7498</v>
+        <v>0.5294</v>
       </c>
       <c r="J77" t="n">
-        <v>17.9952</v>
+        <v>12.7056</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.36</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5595</v>
+        <v>0.4221</v>
       </c>
       <c r="J78" t="n">
-        <v>13.428</v>
+        <v>10.1304</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.99</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-0.0315</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.0304</v>
+        <v>-0.756</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.91</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2413</v>
+        <v>-0.1356</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.7912</v>
+        <v>-3.2544</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4066</v>
+        <v>-0.2517</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.7584</v>
+        <v>-6.0408</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.74</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5504</v>
+        <v>1.0997</v>
       </c>
       <c r="J82" t="n">
-        <v>23.256</v>
+        <v>16.4955</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.72</v>
       </c>
       <c r="I83" t="n">
-        <v>1.5139</v>
+        <v>1.0767</v>
       </c>
       <c r="J83" t="n">
-        <v>22.7085</v>
+        <v>16.1505</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.4</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8355</v>
+        <v>0.7019</v>
       </c>
       <c r="J84" t="n">
-        <v>12.5325</v>
+        <v>10.5285</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.38</v>
       </c>
       <c r="I85" t="n">
-        <v>0.792</v>
+        <v>0.6768</v>
       </c>
       <c r="J85" t="n">
-        <v>11.88</v>
+        <v>10.152</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.18</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3433</v>
+        <v>0.4038</v>
       </c>
       <c r="J86" t="n">
-        <v>5.1495</v>
+        <v>6.057</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.9</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0259</v>
+        <v>-0.0539</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.3885</v>
+        <v>-0.8085</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.75</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2673</v>
+        <v>-0.2283</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.0095</v>
+        <v>-3.4245</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.6</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.5221</v>
+        <v>-0.3743</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.8315</v>
+        <v>-5.6145</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.45</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.7501</v>
+        <v>-0.5134</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.2515</v>
+        <v>-7.701</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.905</v>
+        <v>-0.6281</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.575</v>
+        <v>-9.4215</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.79</v>
       </c>
       <c r="I92" t="n">
-        <v>1.7363</v>
+        <v>1.2231</v>
       </c>
       <c r="J92" t="n">
-        <v>39.9349</v>
+        <v>28.1313</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.39</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9847</v>
+        <v>0.7214</v>
       </c>
       <c r="J93" t="n">
-        <v>22.6481</v>
+        <v>16.5922</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5053</v>
+        <v>0.4659</v>
       </c>
       <c r="J94" t="n">
-        <v>11.6219</v>
+        <v>10.7157</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1987</v>
+        <v>0.2697</v>
       </c>
       <c r="J95" t="n">
-        <v>4.5701</v>
+        <v>6.2031</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.62</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.1264</v>
+        <v>-1.1184</v>
       </c>
       <c r="J96" t="n">
-        <v>-25.9072</v>
+        <v>-25.7232</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3504</v>
+        <v>0.366</v>
       </c>
       <c r="J97" t="n">
-        <v>8.059200000000001</v>
+        <v>8.417999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3353</v>
+        <v>0.3544</v>
       </c>
       <c r="J98" t="n">
-        <v>7.7119</v>
+        <v>8.151199999999999</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3198</v>
+        <v>0.3417</v>
       </c>
       <c r="J99" t="n">
-        <v>7.3554</v>
+        <v>7.8591</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.68</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5323</v>
+        <v>-0.3467</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.2429</v>
+        <v>-7.9741</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.51</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7432</v>
+        <v>-0.5034</v>
       </c>
       <c r="J101" t="n">
-        <v>-17.0936</v>
+        <v>-11.5782</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>2.39</v>
       </c>
       <c r="I102" t="n">
-        <v>2.2187</v>
+        <v>1.8288</v>
       </c>
       <c r="J102" t="n">
-        <v>39.9366</v>
+        <v>32.9184</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.7</v>
       </c>
       <c r="I103" t="n">
-        <v>1.4898</v>
+        <v>1.0587</v>
       </c>
       <c r="J103" t="n">
-        <v>26.8164</v>
+        <v>19.0566</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3993</v>
+        <v>0.4369</v>
       </c>
       <c r="J104" t="n">
-        <v>7.1874</v>
+        <v>7.8642</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.096</v>
+        <v>-0.0102</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.728</v>
+        <v>-0.1836</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.96</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3609</v>
+        <v>-0.2737</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.4962</v>
+        <v>-4.9266</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.37</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6866</v>
+        <v>0.6417</v>
       </c>
       <c r="J107" t="n">
-        <v>12.3588</v>
+        <v>11.5506</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.131</v>
+        <v>0.0988</v>
       </c>
       <c r="J108" t="n">
-        <v>2.358</v>
+        <v>1.7784</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.72</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.4385</v>
+        <v>-0.291</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.893</v>
+        <v>-5.238</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.52</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.709</v>
+        <v>-0.4784</v>
       </c>
       <c r="J110" t="n">
-        <v>-12.762</v>
+        <v>-8.6112</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.36</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.6248</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.1946</v>
+        <v>-11.2464</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.6</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8413</v>
+        <v>0.6162</v>
       </c>
       <c r="J112" t="n">
-        <v>20.1912</v>
+        <v>14.7888</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3307</v>
+        <v>0.3002</v>
       </c>
       <c r="J113" t="n">
-        <v>7.9368</v>
+        <v>7.2048</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.14</v>
       </c>
       <c r="I114" t="n">
-        <v>0.251</v>
+        <v>0.2311</v>
       </c>
       <c r="J114" t="n">
-        <v>6.024</v>
+        <v>5.5464</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.99</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0824</v>
+        <v>-0.0307</v>
       </c>
       <c r="J115" t="n">
-        <v>-1.9776</v>
+        <v>-0.7368</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6358</v>
+        <v>-0.4214</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.2592</v>
+        <v>-10.1136</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.24</v>
       </c>
       <c r="I117" t="n">
-        <v>0.417</v>
+        <v>0.3418</v>
       </c>
       <c r="J117" t="n">
-        <v>10.008</v>
+        <v>8.203200000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2679</v>
+        <v>0.2202</v>
       </c>
       <c r="J118" t="n">
-        <v>6.4296</v>
+        <v>5.2848</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.04</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0704</v>
+        <v>0.076</v>
       </c>
       <c r="J119" t="n">
-        <v>1.6896</v>
+        <v>1.824</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I120" t="n">
-        <v>0.025</v>
+        <v>0.0405</v>
       </c>
       <c r="J120" t="n">
-        <v>0.6</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.9</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2468</v>
+        <v>-0.1417</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.9232</v>
+        <v>-3.4008</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.78</v>
       </c>
       <c r="I122" t="n">
-        <v>1.7044</v>
+        <v>1.1943</v>
       </c>
       <c r="J122" t="n">
-        <v>34.088</v>
+        <v>23.886</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.74</v>
       </c>
       <c r="I123" t="n">
-        <v>1.6413</v>
+        <v>1.1463</v>
       </c>
       <c r="J123" t="n">
-        <v>32.826</v>
+        <v>22.926</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1767</v>
+        <v>0.2569</v>
       </c>
       <c r="J124" t="n">
-        <v>3.534</v>
+        <v>5.138</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.89</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5228</v>
+        <v>-0.4494</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.456</v>
+        <v>-8.988</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6007</v>
+        <v>-0.5329</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.014</v>
+        <v>-10.658</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.15</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3602</v>
+        <v>0.3707</v>
       </c>
       <c r="J127" t="n">
-        <v>7.204</v>
+        <v>7.414</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.85</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2552</v>
+        <v>-0.1724</v>
       </c>
       <c r="J128" t="n">
-        <v>-5.104</v>
+        <v>-3.448</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2552</v>
+        <v>-0.1724</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.104</v>
+        <v>-3.448</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.78</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3729</v>
+        <v>-0.2418</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.458</v>
+        <v>-4.836</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5168</v>
+        <v>-0.3382</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.336</v>
+        <v>-6.764</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.82</v>
       </c>
       <c r="I132" t="n">
-        <v>1.7349</v>
+        <v>1.2235</v>
       </c>
       <c r="J132" t="n">
-        <v>32.9631</v>
+        <v>23.2465</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.47</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0931</v>
+        <v>0.8025</v>
       </c>
       <c r="J133" t="n">
-        <v>20.7689</v>
+        <v>15.2475</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.46</v>
       </c>
       <c r="I134" t="n">
-        <v>1.0721</v>
+        <v>0.7901</v>
       </c>
       <c r="J134" t="n">
-        <v>20.3699</v>
+        <v>15.0119</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.09</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1541</v>
+        <v>0.2417</v>
       </c>
       <c r="J135" t="n">
-        <v>2.9279</v>
+        <v>4.5923</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.64</v>
+        <v>-0.5743</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.16</v>
+        <v>-10.9117</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2602</v>
+        <v>0.2636</v>
       </c>
       <c r="J137" t="n">
-        <v>4.9438</v>
+        <v>5.0084</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1881</v>
+        <v>-0.1488</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.5739</v>
+        <v>-2.8272</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3076</v>
+        <v>-0.2085</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.8444</v>
+        <v>-3.9615</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3253</v>
+        <v>-0.2181</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.1807</v>
+        <v>-4.1439</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6402</v>
+        <v>-0.4273</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.1638</v>
+        <v>-8.1187</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.8</v>
       </c>
       <c r="I142" t="n">
-        <v>1.7077</v>
+        <v>1.199</v>
       </c>
       <c r="J142" t="n">
-        <v>34.154</v>
+        <v>23.98</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.5</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1532</v>
+        <v>0.8389</v>
       </c>
       <c r="J143" t="n">
-        <v>23.064</v>
+        <v>16.778</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.33</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7558</v>
+        <v>0.6276</v>
       </c>
       <c r="J144" t="n">
-        <v>15.116</v>
+        <v>12.552</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3636</v>
+        <v>0.4067</v>
       </c>
       <c r="J145" t="n">
-        <v>7.272</v>
+        <v>8.134</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4852</v>
+        <v>-0.4072</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.704000000000001</v>
+        <v>-8.144</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.21</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4568</v>
+        <v>0.4471</v>
       </c>
       <c r="J147" t="n">
-        <v>9.135999999999999</v>
+        <v>8.942</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.95</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.046</v>
+        <v>-0.0578</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.92</v>
+        <v>-1.156</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.78</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3641</v>
+        <v>-0.239</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.282</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.497</v>
+        <v>-0.3257</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.94</v>
+        <v>-6.514</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6554</v>
+        <v>-0.4381</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.108</v>
+        <v>-8.762</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.34</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5923</v>
+        <v>0.5572</v>
       </c>
       <c r="J152" t="n">
-        <v>14.2152</v>
+        <v>13.3728</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1983</v>
+        <v>0.1991</v>
       </c>
       <c r="J153" t="n">
-        <v>4.7592</v>
+        <v>4.7784</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.87</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.258</v>
+        <v>-0.16</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.192</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3682</v>
+        <v>-0.2318</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.8368</v>
+        <v>-5.5632</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.62</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6117</v>
+        <v>-0.4042</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.6808</v>
+        <v>-9.700799999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.37</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0169</v>
+        <v>0.728</v>
       </c>
       <c r="J157" t="n">
-        <v>24.4056</v>
+        <v>17.472</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.24</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7208</v>
+        <v>0.5443</v>
       </c>
       <c r="J158" t="n">
-        <v>17.2992</v>
+        <v>13.0632</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.96</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2452</v>
+        <v>-0.1844</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.8848</v>
+        <v>-4.4256</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3121</v>
+        <v>-0.2498</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.4904</v>
+        <v>-5.9952</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.516</v>
+        <v>-0.4556</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.384</v>
+        <v>-10.9344</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.34</v>
       </c>
       <c r="I162" t="n">
-        <v>0.523</v>
+        <v>0.4042</v>
       </c>
       <c r="J162" t="n">
-        <v>12.029</v>
+        <v>9.2966</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.27</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4303</v>
+        <v>0.3558</v>
       </c>
       <c r="J163" t="n">
-        <v>9.8969</v>
+        <v>8.183400000000001</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1685</v>
+        <v>0.1715</v>
       </c>
       <c r="J164" t="n">
-        <v>3.8755</v>
+        <v>3.9445</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.1</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1511</v>
+        <v>0.1576</v>
       </c>
       <c r="J165" t="n">
-        <v>3.4753</v>
+        <v>3.6248</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1974</v>
+        <v>-0.104</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.5402</v>
+        <v>-2.392</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.23</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4138</v>
+        <v>0.3544</v>
       </c>
       <c r="J167" t="n">
-        <v>9.5174</v>
+        <v>8.151199999999999</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2476</v>
+        <v>0.2125</v>
       </c>
       <c r="J168" t="n">
-        <v>5.6948</v>
+        <v>4.8875</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.04</v>
       </c>
       <c r="I169" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J169" t="n">
-        <v>2.1574</v>
+        <v>1.9458</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.99</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0584</v>
+        <v>-0.0236</v>
       </c>
       <c r="J170" t="n">
-        <v>-1.3432</v>
+        <v>-0.5427999999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3915</v>
+        <v>-0.2431</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.0045</v>
+        <v>-5.5913</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5636</v>
+        <v>0.5359</v>
       </c>
       <c r="J172" t="n">
-        <v>13.5264</v>
+        <v>12.8616</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2522</v>
+        <v>0.2805</v>
       </c>
       <c r="J173" t="n">
-        <v>6.0528</v>
+        <v>6.732</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1239</v>
+        <v>0.1349</v>
       </c>
       <c r="J174" t="n">
-        <v>2.9736</v>
+        <v>3.2376</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2681</v>
+        <v>-0.1588</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.4344</v>
+        <v>-3.8112</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4852</v>
+        <v>-0.3103</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.6448</v>
+        <v>-7.4472</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.4</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0489</v>
+        <v>0.7527</v>
       </c>
       <c r="J177" t="n">
-        <v>25.1736</v>
+        <v>18.0648</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8739</v>
+        <v>0.6442</v>
       </c>
       <c r="J178" t="n">
-        <v>20.9736</v>
+        <v>15.4608</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.02</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0049</v>
+        <v>0.0635</v>
       </c>
       <c r="J179" t="n">
-        <v>0.1176</v>
+        <v>1.524</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.98</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1988</v>
+        <v>-0.1282</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.7712</v>
+        <v>-3.0768</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2721</v>
+        <v>-0.2005</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.5304</v>
+        <v>-4.812</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.14</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3741</v>
+        <v>0.3809</v>
       </c>
       <c r="J182" t="n">
-        <v>6.3597</v>
+        <v>6.4753</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.93</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0623</v>
+        <v>-0.0735</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.0591</v>
+        <v>-1.2495</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.77</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.355</v>
+        <v>-0.2427</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.035</v>
+        <v>-4.1259</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.61</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5918</v>
+        <v>-0.3939</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.0606</v>
+        <v>-6.6963</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.5</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7326</v>
+        <v>-0.4961</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.4542</v>
+        <v>-8.4337</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.6</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3563</v>
+        <v>0.9633</v>
       </c>
       <c r="J187" t="n">
-        <v>23.0571</v>
+        <v>16.3761</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.9684</v>
+        <v>0.7288</v>
       </c>
       <c r="J188" t="n">
-        <v>16.4628</v>
+        <v>12.3896</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.31</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.6032</v>
       </c>
       <c r="J189" t="n">
-        <v>12.1244</v>
+        <v>10.2544</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.3</v>
       </c>
       <c r="I190" t="n">
-        <v>0.6878</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>11.6926</v>
+        <v>10.0334</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.03</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0287</v>
+        <v>0.0534</v>
       </c>
       <c r="J191" t="n">
-        <v>-0.4879</v>
+        <v>0.9078000000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.62</v>
       </c>
       <c r="I192" t="n">
-        <v>0.842</v>
+        <v>0.5839</v>
       </c>
       <c r="J192" t="n">
-        <v>17.682</v>
+        <v>12.2619</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.38</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5649</v>
+        <v>0.4283</v>
       </c>
       <c r="J193" t="n">
-        <v>11.8629</v>
+        <v>8.994300000000001</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="J194" t="n">
-        <v>-0.1785</v>
+        <v>0.5523</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2031</v>
+        <v>-0.1068</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.2651</v>
+        <v>-2.2428</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2031</v>
+        <v>-0.1068</v>
       </c>
       <c r="J196" t="n">
-        <v>-4.2651</v>
+        <v>-2.2428</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3257</v>
+        <v>0.275</v>
       </c>
       <c r="J197" t="n">
-        <v>6.8397</v>
+        <v>5.775</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.08</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2109</v>
+        <v>0.1659</v>
       </c>
       <c r="J198" t="n">
-        <v>4.4289</v>
+        <v>3.4839</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.04</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1347</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>2.8287</v>
+        <v>2.0286</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.88</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2463</v>
+        <v>-0.1509</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.1723</v>
+        <v>-3.1689</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6141</v>
+        <v>-0.4059</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.8961</v>
+        <v>-8.523899999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.98</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0431</v>
+        <v>-0.0032</v>
       </c>
       <c r="J202" t="n">
-        <v>0.8189</v>
+        <v>-0.0608</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0587</v>
+        <v>-0.0718</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.1153</v>
+        <v>-1.3642</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.77</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3495</v>
+        <v>-0.2418</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.6405</v>
+        <v>-4.5942</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.66</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5208</v>
+        <v>-0.3458</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.895200000000001</v>
+        <v>-6.5702</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6423</v>
+        <v>-0.4301</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.2037</v>
+        <v>-8.171900000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.68</v>
       </c>
       <c r="I207" t="n">
-        <v>1.497</v>
+        <v>1.0549</v>
       </c>
       <c r="J207" t="n">
-        <v>28.443</v>
+        <v>20.0431</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.68</v>
       </c>
       <c r="I208" t="n">
-        <v>1.497</v>
+        <v>1.0549</v>
       </c>
       <c r="J208" t="n">
-        <v>28.443</v>
+        <v>20.0431</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.33</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7477</v>
+        <v>0.6268</v>
       </c>
       <c r="J209" t="n">
-        <v>14.2063</v>
+        <v>11.9092</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.17</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3599</v>
+        <v>0.4054</v>
       </c>
       <c r="J210" t="n">
-        <v>6.8381</v>
+        <v>7.7026</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.9</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.4384</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.7774</v>
+        <v>-8.329599999999999</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.05</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1709</v>
+        <v>0.1614</v>
       </c>
       <c r="J212" t="n">
-        <v>4.1016</v>
+        <v>3.8736</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1299</v>
+        <v>0.1122</v>
       </c>
       <c r="J213" t="n">
-        <v>3.1176</v>
+        <v>2.6928</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1299</v>
+        <v>0.1122</v>
       </c>
       <c r="J214" t="n">
-        <v>3.1176</v>
+        <v>2.6928</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.77</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4048</v>
+        <v>-0.2583</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.715199999999999</v>
+        <v>-6.1992</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.516</v>
+        <v>-0.3355</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.384</v>
+        <v>-8.052</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.55</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3459</v>
+        <v>0.9454</v>
       </c>
       <c r="J217" t="n">
-        <v>32.3016</v>
+        <v>22.6896</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.14</v>
       </c>
       <c r="I218" t="n">
-        <v>0.387</v>
+        <v>0.3852</v>
       </c>
       <c r="J218" t="n">
-        <v>9.288</v>
+        <v>9.2448</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1715</v>
+        <v>0.227</v>
       </c>
       <c r="J219" t="n">
-        <v>4.116</v>
+        <v>5.448</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.04</v>
       </c>
       <c r="I220" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.1317</v>
       </c>
       <c r="J220" t="n">
-        <v>1.7376</v>
+        <v>3.1608</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3109</v>
+        <v>-0.2376</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.4616</v>
+        <v>-5.7024</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.21</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5073</v>
+        <v>0.4936</v>
       </c>
       <c r="J222" t="n">
-        <v>8.6241</v>
+        <v>8.3912</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.73</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.3722</v>
+        <v>-0.2731</v>
       </c>
       <c r="J223" t="n">
-        <v>-6.3274</v>
+        <v>-4.6427</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.6</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.5851</v>
+        <v>-0.3931</v>
       </c>
       <c r="J224" t="n">
-        <v>-9.9467</v>
+        <v>-6.6827</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.54</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.6663</v>
+        <v>-0.4492</v>
       </c>
       <c r="J225" t="n">
-        <v>-11.3271</v>
+        <v>-7.6364</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6663</v>
+        <v>-0.4492</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.3271</v>
+        <v>-7.6364</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>2.35</v>
       </c>
       <c r="I227" t="n">
-        <v>2.181</v>
+        <v>1.7791</v>
       </c>
       <c r="J227" t="n">
-        <v>37.077</v>
+        <v>30.2447</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.59</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2707</v>
+        <v>0.9276</v>
       </c>
       <c r="J228" t="n">
-        <v>21.6019</v>
+        <v>15.7692</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.31</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6429</v>
+        <v>0.5873</v>
       </c>
       <c r="J229" t="n">
-        <v>10.9293</v>
+        <v>9.9841</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.21</v>
       </c>
       <c r="I230" t="n">
-        <v>0.4169</v>
+        <v>0.449</v>
       </c>
       <c r="J230" t="n">
-        <v>7.0873</v>
+        <v>7.633</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.91</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5114</v>
+        <v>-0.4335</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.6938</v>
+        <v>-7.3695</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8413/event_8413_evp_summary.xlsx
+++ b/database/event/8413/event_8413_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.930999999999999</v>
+        <v>8.6227</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2905</v>
+        <v>2.2114</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3939</v>
+        <v>3.301</v>
       </c>
       <c r="E2" t="n">
-        <v>8.930999999999999</v>
+        <v>8.6227</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.930999999999999</v>
+        <v>8.6227</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4005</v>
+        <v>6.778</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>6.4005</v>
+        <v>6.778</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4052</v>
+        <v>7.4062</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8992</v>
+        <v>1.8994</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7051</v>
+        <v>2.7473</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4052</v>
+        <v>7.4062</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7.4052</v>
+        <v>7.4062</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5.307</v>
+        <v>5.8218</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>5.307</v>
+        <v>5.8218</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.833</v>
+        <v>5.6788</v>
       </c>
       <c r="C4" t="n">
-        <v>1.496</v>
+        <v>1.4564</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9953</v>
+        <v>1.9609</v>
       </c>
       <c r="E4" t="n">
-        <v>5.833</v>
+        <v>5.6788</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.833</v>
+        <v>5.6788</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1803</v>
+        <v>4.464</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>206</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1803</v>
+        <v>4.464</v>
       </c>
       <c r="N4" t="n">
         <v>206</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6982</v>
+        <v>5.3666</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4614</v>
+        <v>1.3763</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9344</v>
+        <v>1.8188</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6982</v>
+        <v>5.3666</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6982</v>
+        <v>5.3666</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0837</v>
+        <v>4.2185</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>190</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0837</v>
+        <v>4.2185</v>
       </c>
       <c r="N5" t="n">
         <v>190</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.161</v>
+        <v>5.2074</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3236</v>
+        <v>1.3355</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6919</v>
+        <v>1.7463</v>
       </c>
       <c r="E6" t="n">
-        <v>5.161</v>
+        <v>5.2074</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5.161</v>
+        <v>5.2074</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6987</v>
+        <v>4.0933</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>206</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6987</v>
+        <v>4.0933</v>
       </c>
       <c r="N6" t="n">
         <v>206</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7668</v>
+        <v>4.9051</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2225</v>
+        <v>1.258</v>
       </c>
       <c r="D7" t="n">
-        <v>1.514</v>
+        <v>1.6087</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7668</v>
+        <v>4.9051</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8231</v>
+        <v>1.9012</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9436</v>
+        <v>3.0039</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8231</v>
+        <v>1.9012</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8231</v>
+        <v>1.9012</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1096</v>
+        <v>2.3613</v>
       </c>
       <c r="K7" t="n">
         <v>66</v>
@@ -759,7 +759,7 @@
         <v>101</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9327</v>
+        <v>4.2625</v>
       </c>
       <c r="N7" t="n">
         <v>167</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7589</v>
+        <v>3.796</v>
       </c>
       <c r="C8" t="n">
-        <v>0.964</v>
+        <v>0.9735</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0589</v>
+        <v>1.1038</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7589</v>
+        <v>3.796</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7589</v>
+        <v>3.796</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6939</v>
+        <v>2.9839</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>206</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6939</v>
+        <v>2.9839</v>
       </c>
       <c r="N8" t="n">
         <v>206</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2291</v>
+        <v>3.5356</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8282</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8198</v>
+        <v>0.9853</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2291</v>
+        <v>3.5356</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2291</v>
+        <v>3.5356</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3142</v>
+        <v>2.7792</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>190</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3142</v>
+        <v>2.7792</v>
       </c>
       <c r="N9" t="n">
         <v>190</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6703</v>
+        <v>2.7239</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6848</v>
+        <v>0.6986</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5675</v>
+        <v>0.6158</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6703</v>
+        <v>2.7239</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1277</v>
+        <v>1.1228</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5426</v>
+        <v>1.6011</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1277</v>
+        <v>1.1228</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1277</v>
+        <v>1.1228</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1055</v>
+        <v>1.2586</v>
       </c>
       <c r="K10" t="n">
         <v>66</v>
@@ -897,7 +897,7 @@
         <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2332</v>
+        <v>2.3814</v>
       </c>
       <c r="N10" t="n">
         <v>167</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2134</v>
+        <v>2.2713</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5677</v>
+        <v>0.5825</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3612</v>
+        <v>0.4097</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2134</v>
+        <v>2.2713</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3665</v>
+        <v>0.3502</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8469</v>
+        <v>1.9211</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3665</v>
+        <v>0.3502</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3665</v>
+        <v>0.3502</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3236</v>
+        <v>1.5101</v>
       </c>
       <c r="K11" t="n">
         <v>66</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6901</v>
+        <v>1.8603</v>
       </c>
       <c r="N11" t="n">
         <v>167</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9896</v>
+        <v>1.9741</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5103</v>
+        <v>0.5063</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2602</v>
+        <v>0.2744</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9896</v>
+        <v>1.9741</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3102</v>
+        <v>0.2942</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6795</v>
+        <v>1.6799</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3102</v>
+        <v>0.2942</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3102</v>
+        <v>0.2942</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2036</v>
+        <v>1.3205</v>
       </c>
       <c r="K12" t="n">
         <v>66</v>
@@ -989,7 +989,7 @@
         <v>133</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5138</v>
+        <v>1.6147</v>
       </c>
       <c r="N12" t="n">
         <v>199</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4622</v>
+        <v>1.458</v>
       </c>
       <c r="C13" t="n">
-        <v>0.375</v>
+        <v>0.3739</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0221</v>
+        <v>0.0395</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4622</v>
+        <v>1.458</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4622</v>
+        <v>1.458</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0479</v>
+        <v>1.1461</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0479</v>
+        <v>1.1461</v>
       </c>
       <c r="N13" t="n">
         <v>71</v>
@@ -1044,26 +1044,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2455</v>
+        <v>1.3013</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3194</v>
+        <v>0.3337</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0757</v>
+        <v>-0.0318</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2455</v>
+        <v>1.3013</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2455</v>
+        <v>1.3013</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8925999999999999</v>
+        <v>1.0229</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8925999999999999</v>
+        <v>1.0229</v>
       </c>
       <c r="N14" t="n">
-        <v>71</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1597</v>
+        <v>1.2395</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2974</v>
+        <v>0.3179</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1145</v>
+        <v>-0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1597</v>
+        <v>1.2395</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1597</v>
+        <v>1.2395</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,19 +1118,19 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>206</v>
+        <v>71</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>206</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8181</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2168</v>
+        <v>0.2098</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2564</v>
+        <v>-0.2518</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8181</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8181</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6058</v>
+        <v>0.6431</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>41</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6058</v>
+        <v>0.6431</v>
       </c>
       <c r="N16" t="n">
         <v>41</v>
@@ -1182,173 +1182,173 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>ryu</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5637</v>
+        <v>0.5659</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1446</v>
+        <v>0.1451</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3835</v>
+        <v>-0.3666</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5637</v>
+        <v>0.5659</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.3046</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5637</v>
+        <v>0.8704</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0.3046</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.3046</v>
       </c>
       <c r="J17" t="n">
-        <v>0.404</v>
+        <v>0.6842</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L17" t="n">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="M17" t="n">
-        <v>0.404</v>
+        <v>0.3796</v>
       </c>
       <c r="N17" t="n">
-        <v>57</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ryu</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4628</v>
+        <v>0.5272</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1187</v>
+        <v>0.1352</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4291</v>
+        <v>-0.3842</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4628</v>
+        <v>0.5272</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3225</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7853</v>
+        <v>0.5272</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3225</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3225</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5628</v>
+        <v>0.4144</v>
       </c>
       <c r="K18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2403</v>
+        <v>0.4144</v>
       </c>
       <c r="N18" t="n">
-        <v>167</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3552</v>
+        <v>0.5206</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0911</v>
+        <v>0.1335</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4777</v>
+        <v>-0.3872</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3552</v>
+        <v>0.5206</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2877</v>
+        <v>0.5206</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2062</v>
+        <v>0.4092</v>
       </c>
       <c r="K19" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2737</v>
+        <v>0.4092</v>
       </c>
       <c r="N19" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3483</v>
+        <v>0.4154</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0893</v>
+        <v>0.1065</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4808</v>
+        <v>-0.4351</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3483</v>
+        <v>0.4154</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3697</v>
+        <v>0.0488</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7179</v>
+        <v>0.3666</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3697</v>
+        <v>0.0488</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3697</v>
+        <v>0.0488</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5145</v>
+        <v>0.2882</v>
       </c>
       <c r="K20" t="n">
         <v>66</v>
@@ -1357,7 +1357,7 @@
         <v>133</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1448</v>
+        <v>0.337</v>
       </c>
       <c r="N20" t="n">
         <v>199</v>
@@ -1366,72 +1366,72 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3195</v>
+        <v>0.3951</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0819</v>
+        <v>0.1013</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4938</v>
+        <v>-0.4443</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3195</v>
+        <v>0.3951</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0.3903</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3195</v>
+        <v>0.7854</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-0.3903</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.3903</v>
       </c>
       <c r="J21" t="n">
-        <v>0.229</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L21" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="M21" t="n">
-        <v>0.229</v>
+        <v>0.2271</v>
       </c>
       <c r="N21" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2188</v>
+        <v>0.3166</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0561</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5392</v>
+        <v>-0.4801</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2188</v>
+        <v>0.3166</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2188</v>
+        <v>0.3166</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,19 +1440,19 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1568</v>
+        <v>0.2489</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>206</v>
+        <v>39</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1568</v>
+        <v>0.2489</v>
       </c>
       <c r="N22" t="n">
-        <v>206</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1192</v>
+        <v>0.1398</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0306</v>
+        <v>0.0359</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.5606</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1192</v>
+        <v>0.1398</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1192</v>
+        <v>0.1398</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0854</v>
+        <v>0.1099</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>71</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0854</v>
+        <v>0.1099</v>
       </c>
       <c r="N23" t="n">
         <v>71</v>
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0223</v>
+        <v>0.0941</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0057</v>
+        <v>0.0241</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6279</v>
+        <v>-0.5814</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0223</v>
+        <v>0.0941</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0223</v>
+        <v>0.0941</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.016</v>
+        <v>0.074</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>57</v>
       </c>
       <c r="M24" t="n">
-        <v>0.016</v>
+        <v>0.074</v>
       </c>
       <c r="N24" t="n">
         <v>57</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0061</v>
+        <v>0.094</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0016</v>
+        <v>0.0241</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6353</v>
+        <v>-0.5814</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0061</v>
+        <v>0.094</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2538</v>
+        <v>0.2506</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2477</v>
+        <v>-0.1566</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2538</v>
+        <v>0.2506</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2538</v>
+        <v>0.2506</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1775</v>
+        <v>-0.1231</v>
       </c>
       <c r="K25" t="n">
         <v>66</v>
@@ -1587,7 +1587,7 @@
         <v>133</v>
       </c>
       <c r="M25" t="n">
-        <v>0.07630000000000003</v>
+        <v>0.1275</v>
       </c>
       <c r="N25" t="n">
         <v>199</v>
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0772</v>
+        <v>-0.0911</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0198</v>
+        <v>-0.0234</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6657</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0772</v>
+        <v>-0.0911</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0772</v>
+        <v>-0.0911</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0553</v>
+        <v>-0.0716</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>71</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0553</v>
+        <v>-0.0716</v>
       </c>
       <c r="N26" t="n">
         <v>71</v>
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2235</v>
+        <v>-0.1749</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0573</v>
+        <v>-0.0449</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7389</v>
+        <v>-0.7038</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2235</v>
+        <v>-0.1749</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2235</v>
+        <v>-0.1749</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.1602</v>
+        <v>-0.1375</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>57</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1602</v>
+        <v>-0.1375</v>
       </c>
       <c r="N27" t="n">
         <v>57</v>
@@ -1692,22 +1692,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2435</v>
+        <v>-0.2462</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0624</v>
+        <v>-0.0631</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7479</v>
+        <v>-0.7363</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2435</v>
+        <v>-0.2462</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2435</v>
+        <v>-0.2462</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1745</v>
+        <v>-0.1935</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>39</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1745</v>
+        <v>-0.1935</v>
       </c>
       <c r="N28" t="n">
         <v>39</v>
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4016</v>
+        <v>-0.3791</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.103</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8193</v>
+        <v>-0.7968</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4016</v>
+        <v>-0.3791</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4016</v>
+        <v>-0.3791</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2878</v>
+        <v>-0.298</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>41</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2878</v>
+        <v>-0.298</v>
       </c>
       <c r="N29" t="n">
         <v>41</v>
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4702</v>
+        <v>-0.4417</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1206</v>
+        <v>-0.1133</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.8253</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4702</v>
+        <v>-0.4417</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4702</v>
+        <v>-0.4417</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.337</v>
+        <v>-0.3472</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>41</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.337</v>
+        <v>-0.3472</v>
       </c>
       <c r="N30" t="n">
         <v>41</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5411</v>
+        <v>-0.5381</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1388</v>
+        <v>-0.138</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8823</v>
+        <v>-0.8692</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5411</v>
+        <v>-0.5381</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5411</v>
+        <v>-0.5381</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3878</v>
+        <v>-0.423</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3878</v>
+        <v>-0.423</v>
       </c>
       <c r="N31" t="n">
         <v>39</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6499</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1736</v>
+        <v>-0.1667</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9436</v>
+        <v>-0.9201</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6499</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6499</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4851</v>
+        <v>-0.5109</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>39</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4851</v>
+        <v>-0.5109</v>
       </c>
       <c r="N32" t="n">
         <v>39</v>
@@ -1918,26 +1918,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7415</v>
+        <v>-0.697</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1902</v>
+        <v>-0.1788</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9728</v>
+        <v>-0.9415</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7415</v>
+        <v>-0.697</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7415</v>
+        <v>-0.697</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,44 +1946,44 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5314</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5314</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7454</v>
+        <v>-0.7209</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1912</v>
+        <v>-0.1849</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9745</v>
+        <v>-0.9524</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7454</v>
+        <v>-0.7209</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.7454</v>
+        <v>-0.7209</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,44 +1992,44 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.5342</v>
+        <v>-0.5667</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5342</v>
+        <v>-0.5667</v>
       </c>
       <c r="N34" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7577</v>
+        <v>-0.7222</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1943</v>
+        <v>-0.1852</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9801</v>
+        <v>-0.953</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7577</v>
+        <v>-0.7222</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7577</v>
+        <v>-0.7222</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,19 +2038,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.543</v>
+        <v>-0.5677</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.543</v>
+        <v>-0.5677</v>
       </c>
       <c r="N35" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36">
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8517</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2184</v>
+        <v>-0.2111</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0225</v>
+        <v>-0.9989</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8517</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8517</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.647</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>57</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.647</v>
       </c>
       <c r="N36" t="n">
         <v>57</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9567</v>
+        <v>-0.8924</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2454</v>
+        <v>-0.2289</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0699</v>
+        <v>-1.0304</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9567</v>
+        <v>-0.8924</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.2328</v>
+        <v>-0.2379</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7239</v>
+        <v>-0.6545</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2328</v>
+        <v>-0.2379</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2328</v>
+        <v>-0.2379</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5188</v>
+        <v>-0.5145</v>
       </c>
       <c r="K37" t="n">
         <v>66</v>
@@ -2139,7 +2139,7 @@
         <v>133</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7516</v>
+        <v>-0.7524</v>
       </c>
       <c r="N37" t="n">
         <v>199</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0167</v>
+        <v>-0.9638</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2607</v>
+        <v>-0.2472</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.097</v>
+        <v>-1.0629</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0167</v>
+        <v>-0.9638</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.0167</v>
+        <v>-0.9638</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7286</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>41</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7286</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>41</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0361</v>
+        <v>-0.9952</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2657</v>
+        <v>-0.2552</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1058</v>
+        <v>-1.0772</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0361</v>
+        <v>-0.9952</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.0361</v>
+        <v>-0.9952</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7425</v>
+        <v>-0.7823</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>57</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7425</v>
+        <v>-0.7823</v>
       </c>
       <c r="N39" t="n">
         <v>57</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0639</v>
+        <v>-1.8093</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5293</v>
+        <v>-0.464</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5698</v>
+        <v>-1.4478</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0639</v>
+        <v>-1.8093</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.4728</v>
+        <v>-0.4396</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.5911</v>
+        <v>-1.3697</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4728</v>
+        <v>-0.4396</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4728</v>
+        <v>-0.4396</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.1403</v>
+        <v>-1.0767</v>
       </c>
       <c r="K40" t="n">
         <v>66</v>
@@ -2277,7 +2277,7 @@
         <v>101</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6131</v>
+        <v>-1.5163</v>
       </c>
       <c r="N40" t="n">
         <v>167</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.325</v>
+        <v>-1.8614</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.4774</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6876</v>
+        <v>-1.4716</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.325</v>
+        <v>-1.8614</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.325</v>
+        <v>-1.8614</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.6662</v>
+        <v>-1.4632</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>190</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6662</v>
+        <v>-1.4632</v>
       </c>
       <c r="N41" t="n">
         <v>190</v>
@@ -2429,10 +2429,10 @@
         <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6543</v>
+        <v>1.7917</v>
       </c>
       <c r="J2" t="n">
-        <v>33.086</v>
+        <v>35.834</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.45</v>
       </c>
       <c r="I3" t="n">
-        <v>1.054</v>
+        <v>1.0191</v>
       </c>
       <c r="J3" t="n">
-        <v>21.08</v>
+        <v>20.382</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9599</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>19.198</v>
+        <v>18.156</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2452</v>
+        <v>-0.2251</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.904</v>
+        <v>-4.502</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.84</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5968</v>
+        <v>-0.5503</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.936</v>
+        <v>-11.006</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1445</v>
+        <v>0.1383</v>
       </c>
       <c r="J7" t="n">
-        <v>2.89</v>
+        <v>2.766</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.117</v>
+        <v>0.1104</v>
       </c>
       <c r="J8" t="n">
-        <v>2.34</v>
+        <v>2.208</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1266</v>
+        <v>-0.1439</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.532</v>
+        <v>-2.878</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3139</v>
+        <v>-0.3302</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.278</v>
+        <v>-6.604</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.48</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5188</v>
+        <v>-0.5252</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.376</v>
+        <v>-10.504</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6284</v>
+        <v>0.6118</v>
       </c>
       <c r="J12" t="n">
-        <v>15.0816</v>
+        <v>14.6832</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1885</v>
+        <v>0.1978</v>
       </c>
       <c r="J13" t="n">
-        <v>4.524</v>
+        <v>4.7472</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.96</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0725</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.5168</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1342</v>
+        <v>-0.1469</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.2208</v>
+        <v>-3.5256</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4109</v>
+        <v>-0.4197</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.861599999999999</v>
+        <v>-10.0728</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.37</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5043</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>12.1032</v>
+        <v>12.2064</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0752</v>
+        <v>0.0871</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8048</v>
+        <v>2.0904</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0579</v>
+        <v>0.0688</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3896</v>
+        <v>1.6512</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0575</v>
+        <v>-0.064</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.38</v>
+        <v>-1.536</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0575</v>
+        <v>-0.064</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.38</v>
+        <v>-1.536</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.72</v>
       </c>
       <c r="I22" t="n">
-        <v>1.419</v>
+        <v>1.5287</v>
       </c>
       <c r="J22" t="n">
-        <v>29.799</v>
+        <v>32.1027</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7256</v>
+        <v>0.6928</v>
       </c>
       <c r="J23" t="n">
-        <v>15.2376</v>
+        <v>14.5488</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5844</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>12.2724</v>
+        <v>11.907</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2754</v>
+        <v>0.2848</v>
       </c>
       <c r="J25" t="n">
-        <v>5.7834</v>
+        <v>5.9808</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9715</v>
+        <v>-0.886</v>
       </c>
       <c r="J26" t="n">
-        <v>-20.4015</v>
+        <v>-18.606</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6192</v>
+        <v>0.5959</v>
       </c>
       <c r="J27" t="n">
-        <v>13.0032</v>
+        <v>12.5139</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.18</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4177</v>
+        <v>0.4111</v>
       </c>
       <c r="J28" t="n">
-        <v>8.771699999999999</v>
+        <v>8.633100000000001</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.18</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4177</v>
+        <v>0.4111</v>
       </c>
       <c r="J29" t="n">
-        <v>8.771699999999999</v>
+        <v>8.633100000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.62</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4056</v>
+        <v>-0.4155</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.5176</v>
+        <v>-8.7255</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.49</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5238</v>
+        <v>-0.5278</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.9998</v>
+        <v>-11.0838</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.29</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7873</v>
+        <v>0.7444</v>
       </c>
       <c r="J32" t="n">
-        <v>17.3206</v>
+        <v>16.3768</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7637</v>
+        <v>0.7236</v>
       </c>
       <c r="J33" t="n">
-        <v>16.8014</v>
+        <v>15.9192</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.27</v>
       </c>
       <c r="I34" t="n">
-        <v>0.74</v>
+        <v>0.7027</v>
       </c>
       <c r="J34" t="n">
-        <v>16.28</v>
+        <v>15.4594</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.19</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5461</v>
+        <v>0.5303</v>
       </c>
       <c r="J35" t="n">
-        <v>12.0142</v>
+        <v>11.6666</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9361</v>
+        <v>-0.857</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.5942</v>
+        <v>-18.854</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3604</v>
+        <v>0.3534</v>
       </c>
       <c r="J37" t="n">
-        <v>7.9288</v>
+        <v>7.7748</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.07</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2127</v>
+        <v>0.2128</v>
       </c>
       <c r="J38" t="n">
-        <v>4.6794</v>
+        <v>4.6816</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.93</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.1046</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.9998</v>
+        <v>-2.3012</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.79</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2366</v>
+        <v>-0.2526</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.2052</v>
+        <v>-5.5572</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4546</v>
+        <v>-0.4632</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.0012</v>
+        <v>-10.1904</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.97</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0575</v>
+        <v>1.0457</v>
       </c>
       <c r="J42" t="n">
-        <v>22.2075</v>
+        <v>21.9597</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.38</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4812</v>
+        <v>0.4931</v>
       </c>
       <c r="J43" t="n">
-        <v>10.1052</v>
+        <v>10.3551</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.17</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2391</v>
+        <v>0.2585</v>
       </c>
       <c r="J44" t="n">
-        <v>5.0211</v>
+        <v>5.4285</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.91</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1496</v>
+        <v>-0.1562</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.1416</v>
+        <v>-3.2802</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.87</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1935</v>
+        <v>-0.201</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.0635</v>
+        <v>-4.221</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.62</v>
       </c>
       <c r="I47" t="n">
-        <v>0.92</v>
+        <v>0.8703</v>
       </c>
       <c r="J47" t="n">
-        <v>19.32</v>
+        <v>18.2763</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4463</v>
+        <v>0.4388</v>
       </c>
       <c r="J48" t="n">
-        <v>9.372299999999999</v>
+        <v>9.2148</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.67</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3541</v>
+        <v>-0.3669</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.4361</v>
+        <v>-7.7049</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.57</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4471</v>
+        <v>-0.4558</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.389099999999999</v>
+        <v>-9.5718</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.44</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5646</v>
+        <v>-0.5668</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.8566</v>
+        <v>-11.9028</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.86</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1447</v>
+        <v>-0.1657</v>
       </c>
       <c r="J52" t="n">
-        <v>-2.4599</v>
+        <v>-2.8169</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.85</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1557</v>
+        <v>-0.1767</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.6469</v>
+        <v>-3.0039</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.77</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2379</v>
+        <v>-0.2579</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.0443</v>
+        <v>-4.3843</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.66</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3398</v>
+        <v>-0.3574</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.7766</v>
+        <v>-6.0758</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.424</v>
+        <v>-0.4377</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.208</v>
+        <v>-7.4409</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.07</v>
       </c>
       <c r="I57" t="n">
-        <v>1.7853</v>
+        <v>1.7889</v>
       </c>
       <c r="J57" t="n">
-        <v>30.3501</v>
+        <v>30.4113</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6763</v>
+        <v>0.6545</v>
       </c>
       <c r="J58" t="n">
-        <v>11.4971</v>
+        <v>11.1265</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4831</v>
+        <v>0.4818</v>
       </c>
       <c r="J59" t="n">
-        <v>8.2127</v>
+        <v>8.1906</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3257</v>
+        <v>0.3388</v>
       </c>
       <c r="J60" t="n">
-        <v>5.5369</v>
+        <v>5.7596</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.07</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1819</v>
+        <v>0.2056</v>
       </c>
       <c r="J61" t="n">
-        <v>3.0923</v>
+        <v>3.4952</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4292</v>
+        <v>0.4195</v>
       </c>
       <c r="J62" t="n">
-        <v>12.0176</v>
+        <v>11.746</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1821</v>
+        <v>0.1849</v>
       </c>
       <c r="J63" t="n">
-        <v>5.0988</v>
+        <v>5.1772</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0132</v>
+        <v>-0.0196</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.3696</v>
+        <v>-0.5488</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.72</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3079</v>
+        <v>-0.3218</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.6212</v>
+        <v>-9.010400000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3648</v>
+        <v>-0.3769</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.2144</v>
+        <v>-10.5532</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.78</v>
       </c>
       <c r="I67" t="n">
-        <v>1.4834</v>
+        <v>1.468</v>
       </c>
       <c r="J67" t="n">
-        <v>41.5352</v>
+        <v>41.104</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.54</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1869</v>
+        <v>1.154</v>
       </c>
       <c r="J68" t="n">
-        <v>33.2332</v>
+        <v>32.312</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.22</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6041</v>
+        <v>0.5855</v>
       </c>
       <c r="J69" t="n">
-        <v>16.9148</v>
+        <v>16.394</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6803</v>
+        <v>-0.629</v>
       </c>
       <c r="J70" t="n">
-        <v>-19.0484</v>
+        <v>-17.612</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7567</v>
+        <v>-0.6968</v>
       </c>
       <c r="J71" t="n">
-        <v>-21.1876</v>
+        <v>-19.5104</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.381</v>
+        <v>0.4136</v>
       </c>
       <c r="J72" t="n">
-        <v>9.144</v>
+        <v>9.926399999999999</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>0.357</v>
+        <v>0.3758</v>
       </c>
       <c r="J73" t="n">
-        <v>8.568</v>
+        <v>9.0192</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.14</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2455</v>
+        <v>0.2542</v>
       </c>
       <c r="J74" t="n">
-        <v>5.892</v>
+        <v>6.1008</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2411</v>
+        <v>-0.254</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.7864</v>
+        <v>-6.096</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3758</v>
+        <v>-0.3856</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.0192</v>
+        <v>-9.2544</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5294</v>
+        <v>0.603</v>
       </c>
       <c r="J77" t="n">
-        <v>12.7056</v>
+        <v>14.472</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.36</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4221</v>
+        <v>0.477</v>
       </c>
       <c r="J78" t="n">
-        <v>10.1304</v>
+        <v>11.448</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.99</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0315</v>
+        <v>-0.0336</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.756</v>
+        <v>-0.8064</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.91</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1356</v>
+        <v>-0.1452</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.2544</v>
+        <v>-3.4848</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2517</v>
+        <v>-0.2623</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.0408</v>
+        <v>-6.2952</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.74</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0997</v>
+        <v>1.2154</v>
       </c>
       <c r="J82" t="n">
-        <v>16.4955</v>
+        <v>18.231</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.72</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0767</v>
+        <v>1.191</v>
       </c>
       <c r="J83" t="n">
-        <v>16.1505</v>
+        <v>17.865</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.4</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7019</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>10.5285</v>
+        <v>11.787</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.38</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6768</v>
+        <v>0.7582</v>
       </c>
       <c r="J85" t="n">
-        <v>10.152</v>
+        <v>11.373</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.18</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4038</v>
+        <v>0.4539</v>
       </c>
       <c r="J86" t="n">
-        <v>6.057</v>
+        <v>6.8085</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.9</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0539</v>
+        <v>-0.0842</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.8085</v>
+        <v>-1.263</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.75</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2283</v>
+        <v>-0.2544</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.4245</v>
+        <v>-3.816</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.6</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3743</v>
+        <v>-0.3943</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.6145</v>
+        <v>-5.9145</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.45</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5134</v>
+        <v>-0.525</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.701</v>
+        <v>-7.875</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6281</v>
+        <v>-0.6308</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.4215</v>
+        <v>-9.462</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.79</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2231</v>
+        <v>1.3346</v>
       </c>
       <c r="J92" t="n">
-        <v>28.1313</v>
+        <v>30.6958</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.39</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7214</v>
+        <v>0.7996</v>
       </c>
       <c r="J93" t="n">
-        <v>16.5922</v>
+        <v>18.3908</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4659</v>
+        <v>0.5162</v>
       </c>
       <c r="J94" t="n">
-        <v>10.7157</v>
+        <v>11.8726</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2697</v>
+        <v>0.2808</v>
       </c>
       <c r="J95" t="n">
-        <v>6.2031</v>
+        <v>6.4584</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.62</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.1184</v>
+        <v>-1.0124</v>
       </c>
       <c r="J96" t="n">
-        <v>-25.7232</v>
+        <v>-23.2852</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.366</v>
+        <v>0.3818</v>
       </c>
       <c r="J97" t="n">
-        <v>8.417999999999999</v>
+        <v>8.7814</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3544</v>
+        <v>0.3635</v>
       </c>
       <c r="J98" t="n">
-        <v>8.151199999999999</v>
+        <v>8.3605</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3417</v>
+        <v>0.3449</v>
       </c>
       <c r="J99" t="n">
-        <v>7.8591</v>
+        <v>7.9327</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.68</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3467</v>
+        <v>-0.3593</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.9741</v>
+        <v>-8.2639</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.51</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5034</v>
+        <v>-0.5089</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.5782</v>
+        <v>-11.7047</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>2.39</v>
       </c>
       <c r="I102" t="n">
-        <v>1.8288</v>
+        <v>1.9744</v>
       </c>
       <c r="J102" t="n">
-        <v>32.9184</v>
+        <v>35.5392</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.7</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0587</v>
+        <v>1.1709</v>
       </c>
       <c r="J103" t="n">
-        <v>19.0566</v>
+        <v>21.0762</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4369</v>
+        <v>0.4911</v>
       </c>
       <c r="J104" t="n">
-        <v>7.8642</v>
+        <v>8.8398</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0102</v>
+        <v>0.0273</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.1836</v>
+        <v>0.4914</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.96</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2737</v>
+        <v>-0.2452</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.9266</v>
+        <v>-4.4136</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.37</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6417</v>
+        <v>0.7016</v>
       </c>
       <c r="J107" t="n">
-        <v>11.5506</v>
+        <v>12.6288</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0988</v>
+        <v>0.0878</v>
       </c>
       <c r="J108" t="n">
-        <v>1.7784</v>
+        <v>1.5804</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.72</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.291</v>
+        <v>-0.3087</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.238</v>
+        <v>-5.5566</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.52</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4784</v>
+        <v>-0.4878</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.6112</v>
+        <v>-8.7804</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.36</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6248</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.2464</v>
+        <v>-11.241</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.6</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6162</v>
+        <v>0.6947</v>
       </c>
       <c r="J112" t="n">
-        <v>14.7888</v>
+        <v>16.6728</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3002</v>
+        <v>0.3104</v>
       </c>
       <c r="J113" t="n">
-        <v>7.2048</v>
+        <v>7.4496</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.14</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2311</v>
+        <v>0.2435</v>
       </c>
       <c r="J114" t="n">
-        <v>5.5464</v>
+        <v>5.844</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.99</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0307</v>
+        <v>-0.033</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.7368</v>
+        <v>-0.792</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4214</v>
+        <v>-0.4279</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.1136</v>
+        <v>-10.2696</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.24</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3418</v>
+        <v>0.3606</v>
       </c>
       <c r="J117" t="n">
-        <v>8.203200000000001</v>
+        <v>8.654400000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2202</v>
+        <v>0.2349</v>
       </c>
       <c r="J118" t="n">
-        <v>5.2848</v>
+        <v>5.6376</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.04</v>
       </c>
       <c r="I119" t="n">
-        <v>0.076</v>
+        <v>0.0877</v>
       </c>
       <c r="J119" t="n">
-        <v>1.824</v>
+        <v>2.1048</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0405</v>
+        <v>0.0497</v>
       </c>
       <c r="J120" t="n">
-        <v>0.972</v>
+        <v>1.1928</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.9</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1417</v>
+        <v>-0.1528</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.4008</v>
+        <v>-3.6672</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.78</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1943</v>
+        <v>1.3071</v>
       </c>
       <c r="J122" t="n">
-        <v>23.886</v>
+        <v>26.142</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.74</v>
       </c>
       <c r="I123" t="n">
-        <v>1.1463</v>
+        <v>1.2565</v>
       </c>
       <c r="J123" t="n">
-        <v>22.926</v>
+        <v>25.13</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2569</v>
+        <v>0.2719</v>
       </c>
       <c r="J124" t="n">
-        <v>5.138</v>
+        <v>5.438</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.89</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4494</v>
+        <v>-0.4186</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.988</v>
+        <v>-8.372</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5329</v>
+        <v>-0.4946</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.658</v>
+        <v>-9.891999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.15</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3707</v>
+        <v>0.3838</v>
       </c>
       <c r="J127" t="n">
-        <v>7.414</v>
+        <v>7.676</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.85</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1724</v>
+        <v>-0.1895</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.448</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1724</v>
+        <v>-0.1895</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.448</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.78</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2418</v>
+        <v>-0.2588</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.836</v>
+        <v>-5.176</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3382</v>
+        <v>-0.3527</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.764</v>
+        <v>-7.054</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.82</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2235</v>
+        <v>1.3408</v>
       </c>
       <c r="J132" t="n">
-        <v>23.2465</v>
+        <v>25.4752</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.47</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8025</v>
+        <v>0.8922</v>
       </c>
       <c r="J133" t="n">
-        <v>15.2475</v>
+        <v>16.9518</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.46</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7901</v>
+        <v>0.8787</v>
       </c>
       <c r="J134" t="n">
-        <v>15.0119</v>
+        <v>16.6953</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.09</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2417</v>
+        <v>0.2613</v>
       </c>
       <c r="J135" t="n">
-        <v>4.5923</v>
+        <v>4.9647</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5743</v>
+        <v>-0.5292</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.9117</v>
+        <v>-10.0548</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2636</v>
+        <v>0.2553</v>
       </c>
       <c r="J137" t="n">
-        <v>5.0084</v>
+        <v>4.8507</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1488</v>
+        <v>-0.1664</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.8272</v>
+        <v>-3.1616</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2085</v>
+        <v>-0.2266</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.9615</v>
+        <v>-4.3054</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2181</v>
+        <v>-0.2362</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.1439</v>
+        <v>-4.4878</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4273</v>
+        <v>-0.4387</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.1187</v>
+        <v>-8.3353</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.8</v>
       </c>
       <c r="I142" t="n">
-        <v>1.199</v>
+        <v>1.3152</v>
       </c>
       <c r="J142" t="n">
-        <v>23.98</v>
+        <v>26.304</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.5</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8389</v>
+        <v>0.9317</v>
       </c>
       <c r="J143" t="n">
-        <v>16.778</v>
+        <v>18.634</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.33</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6276</v>
+        <v>0.7005</v>
       </c>
       <c r="J144" t="n">
-        <v>12.552</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4067</v>
+        <v>0.4525</v>
       </c>
       <c r="J145" t="n">
-        <v>8.134</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4072</v>
+        <v>-0.3764</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.144</v>
+        <v>-7.528</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.21</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4471</v>
+        <v>0.4851</v>
       </c>
       <c r="J147" t="n">
-        <v>8.942</v>
+        <v>9.702</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.95</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0578</v>
+        <v>-0.0722</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.156</v>
+        <v>-1.444</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.78</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.239</v>
+        <v>-0.2566</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.78</v>
+        <v>-5.132</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3257</v>
+        <v>-0.3411</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.514</v>
+        <v>-6.822</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4381</v>
+        <v>-0.4488</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.762</v>
+        <v>-8.976000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.34</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5572</v>
+        <v>0.6168</v>
       </c>
       <c r="J152" t="n">
-        <v>13.3728</v>
+        <v>14.8032</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1991</v>
+        <v>0.2029</v>
       </c>
       <c r="J153" t="n">
-        <v>4.7784</v>
+        <v>4.8696</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.87</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.16</v>
+        <v>-0.1749</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.84</v>
+        <v>-4.1976</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2318</v>
+        <v>-0.2468</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.5632</v>
+        <v>-5.9232</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.62</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4042</v>
+        <v>-0.4144</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.700799999999999</v>
+        <v>-9.945600000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.37</v>
       </c>
       <c r="I157" t="n">
-        <v>0.728</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>17.472</v>
+        <v>19.1976</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.24</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5443</v>
+        <v>0.5987</v>
       </c>
       <c r="J158" t="n">
-        <v>13.0632</v>
+        <v>14.3688</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.96</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1844</v>
+        <v>-0.1826</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.4256</v>
+        <v>-4.3824</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2498</v>
+        <v>-0.2448</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.9952</v>
+        <v>-5.8752</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4556</v>
+        <v>-0.4347</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.9344</v>
+        <v>-10.4328</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.34</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4042</v>
+        <v>0.4562</v>
       </c>
       <c r="J162" t="n">
-        <v>9.2966</v>
+        <v>10.4926</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.27</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3558</v>
+        <v>0.3846</v>
       </c>
       <c r="J163" t="n">
-        <v>8.183400000000001</v>
+        <v>8.845800000000001</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1715</v>
+        <v>0.1884</v>
       </c>
       <c r="J164" t="n">
-        <v>3.9445</v>
+        <v>4.3332</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.1</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1576</v>
+        <v>0.1743</v>
       </c>
       <c r="J165" t="n">
-        <v>3.6248</v>
+        <v>4.0089</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.104</v>
+        <v>-0.1113</v>
       </c>
       <c r="J166" t="n">
-        <v>-2.392</v>
+        <v>-2.5599</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.23</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3544</v>
+        <v>0.3726</v>
       </c>
       <c r="J167" t="n">
-        <v>8.151199999999999</v>
+        <v>8.569800000000001</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2125</v>
+        <v>0.2229</v>
       </c>
       <c r="J168" t="n">
-        <v>4.8875</v>
+        <v>5.1267</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.04</v>
       </c>
       <c r="I169" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0945</v>
       </c>
       <c r="J169" t="n">
-        <v>1.9458</v>
+        <v>2.1735</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.99</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0236</v>
+        <v>-0.0275</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.6325</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2431</v>
+        <v>-0.2556</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.5913</v>
+        <v>-5.8788</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5359</v>
+        <v>0.5971</v>
       </c>
       <c r="J172" t="n">
-        <v>12.8616</v>
+        <v>14.3304</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2805</v>
+        <v>0.2865</v>
       </c>
       <c r="J173" t="n">
-        <v>6.732</v>
+        <v>6.876</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1349</v>
+        <v>0.1447</v>
       </c>
       <c r="J174" t="n">
-        <v>3.2376</v>
+        <v>3.4728</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1588</v>
+        <v>-0.1714</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.8112</v>
+        <v>-4.1136</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3103</v>
+        <v>-0.3219</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.4472</v>
+        <v>-7.7256</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.4</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7527</v>
+        <v>0.8299</v>
       </c>
       <c r="J177" t="n">
-        <v>18.0648</v>
+        <v>19.9176</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6442</v>
+        <v>0.7117</v>
       </c>
       <c r="J178" t="n">
-        <v>15.4608</v>
+        <v>17.0808</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.02</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0635</v>
+        <v>0.0789</v>
       </c>
       <c r="J179" t="n">
-        <v>1.524</v>
+        <v>1.8936</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.98</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1282</v>
+        <v>-0.1234</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.0768</v>
+        <v>-2.9616</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2005</v>
+        <v>-0.1938</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.812</v>
+        <v>-4.6512</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.14</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3809</v>
+        <v>0.3927</v>
       </c>
       <c r="J182" t="n">
-        <v>6.4753</v>
+        <v>6.6759</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.93</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0735</v>
+        <v>-0.0911</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.2495</v>
+        <v>-1.5487</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.77</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2427</v>
+        <v>-0.2615</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.1259</v>
+        <v>-4.4455</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.61</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3939</v>
+        <v>-0.4079</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.6963</v>
+        <v>-6.9343</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.5</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4961</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.4337</v>
+        <v>-8.576499999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.6</v>
       </c>
       <c r="I187" t="n">
-        <v>0.9633</v>
+        <v>1.0648</v>
       </c>
       <c r="J187" t="n">
-        <v>16.3761</v>
+        <v>18.1016</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7288</v>
+        <v>0.8118</v>
       </c>
       <c r="J188" t="n">
-        <v>12.3896</v>
+        <v>13.8006</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.31</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6032</v>
+        <v>0.673</v>
       </c>
       <c r="J189" t="n">
-        <v>10.2544</v>
+        <v>11.441</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.3</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.6586</v>
       </c>
       <c r="J190" t="n">
-        <v>10.0334</v>
+        <v>11.1962</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.03</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0534</v>
+        <v>0.0824</v>
       </c>
       <c r="J191" t="n">
-        <v>0.9078000000000001</v>
+        <v>1.4008</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.62</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5839</v>
+        <v>0.6682</v>
       </c>
       <c r="J192" t="n">
-        <v>12.2619</v>
+        <v>14.0322</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.38</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4283</v>
+        <v>0.486</v>
       </c>
       <c r="J193" t="n">
-        <v>8.994300000000001</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0263</v>
+        <v>0.039</v>
       </c>
       <c r="J194" t="n">
-        <v>0.5523</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1068</v>
+        <v>-0.1135</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.2428</v>
+        <v>-2.3835</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1068</v>
+        <v>-0.1135</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.2428</v>
+        <v>-2.3835</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.275</v>
+        <v>0.2794</v>
       </c>
       <c r="J197" t="n">
-        <v>5.775</v>
+        <v>5.8674</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.08</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1659</v>
+        <v>0.1731</v>
       </c>
       <c r="J198" t="n">
-        <v>3.4839</v>
+        <v>3.6351</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.04</v>
       </c>
       <c r="I199" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.1033</v>
       </c>
       <c r="J199" t="n">
-        <v>2.0286</v>
+        <v>2.1693</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.88</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1509</v>
+        <v>-0.1653</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.1689</v>
+        <v>-3.4713</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4059</v>
+        <v>-0.4157</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.523899999999999</v>
+        <v>-8.729699999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.98</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0032</v>
+        <v>-0.0173</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.0608</v>
+        <v>-0.3287</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0718</v>
+        <v>-0.0897</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.3642</v>
+        <v>-1.7043</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.77</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2418</v>
+        <v>-0.2609</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.5942</v>
+        <v>-4.9571</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.66</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3458</v>
+        <v>-0.362</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.5702</v>
+        <v>-6.878</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4301</v>
+        <v>-0.4424</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.171900000000001</v>
+        <v>-8.4056</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.68</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0549</v>
+        <v>1.1632</v>
       </c>
       <c r="J207" t="n">
-        <v>20.0431</v>
+        <v>22.1008</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.68</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0549</v>
+        <v>1.1632</v>
       </c>
       <c r="J208" t="n">
-        <v>20.0431</v>
+        <v>22.1008</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.33</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6268</v>
+        <v>0.6998</v>
       </c>
       <c r="J209" t="n">
-        <v>11.9092</v>
+        <v>13.2962</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.17</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4054</v>
+        <v>0.4513</v>
       </c>
       <c r="J210" t="n">
-        <v>7.7026</v>
+        <v>8.5747</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.9</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4384</v>
+        <v>-0.4047</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.329599999999999</v>
+        <v>-7.6893</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.05</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1614</v>
+        <v>0.1639</v>
       </c>
       <c r="J212" t="n">
-        <v>3.8736</v>
+        <v>3.9336</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1122</v>
+        <v>0.1147</v>
       </c>
       <c r="J213" t="n">
-        <v>2.6928</v>
+        <v>2.7528</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1122</v>
+        <v>0.1147</v>
       </c>
       <c r="J214" t="n">
-        <v>2.6928</v>
+        <v>2.7528</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.77</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2583</v>
+        <v>-0.2736</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.1992</v>
+        <v>-6.5664</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3355</v>
+        <v>-0.3488</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.052</v>
+        <v>-8.3712</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.55</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9454</v>
+        <v>1.0375</v>
       </c>
       <c r="J217" t="n">
-        <v>22.6896</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.14</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3852</v>
+        <v>0.4158</v>
       </c>
       <c r="J218" t="n">
-        <v>9.2448</v>
+        <v>9.979200000000001</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>0.227</v>
+        <v>0.237</v>
       </c>
       <c r="J219" t="n">
-        <v>5.448</v>
+        <v>5.688</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.04</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1317</v>
+        <v>0.1465</v>
       </c>
       <c r="J220" t="n">
-        <v>3.1608</v>
+        <v>3.516</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2376</v>
+        <v>-0.2283</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.7024</v>
+        <v>-5.4792</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.21</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4936</v>
+        <v>0.5284</v>
       </c>
       <c r="J222" t="n">
-        <v>8.3912</v>
+        <v>8.982799999999999</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.73</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2731</v>
+        <v>-0.2931</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.6427</v>
+        <v>-4.9827</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.6</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3931</v>
+        <v>-0.4088</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.6827</v>
+        <v>-6.9496</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.54</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4492</v>
+        <v>-0.4619</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.6364</v>
+        <v>-7.8523</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4492</v>
+        <v>-0.4619</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.6364</v>
+        <v>-7.8523</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>2.35</v>
       </c>
       <c r="I227" t="n">
-        <v>1.7791</v>
+        <v>1.9241</v>
       </c>
       <c r="J227" t="n">
-        <v>30.2447</v>
+        <v>32.7097</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.59</v>
       </c>
       <c r="I228" t="n">
-        <v>0.9276</v>
+        <v>1.0312</v>
       </c>
       <c r="J228" t="n">
-        <v>15.7692</v>
+        <v>17.5304</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.31</v>
       </c>
       <c r="I229" t="n">
-        <v>0.5873</v>
+        <v>0.6593</v>
       </c>
       <c r="J229" t="n">
-        <v>9.9841</v>
+        <v>11.2081</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.21</v>
       </c>
       <c r="I230" t="n">
-        <v>0.449</v>
+        <v>0.5053</v>
       </c>
       <c r="J230" t="n">
-        <v>7.633</v>
+        <v>8.5901</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.91</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4335</v>
+        <v>-0.3949</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.3695</v>
+        <v>-6.7133</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8413/event_8413_evp_summary.xlsx
+++ b/database/event/8413/event_8413_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.6227</v>
+        <v>8.8475</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2114</v>
+        <v>2.2691</v>
       </c>
       <c r="D2" t="n">
-        <v>3.301</v>
+        <v>3.3382</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6227</v>
+        <v>8.8475</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.6227</v>
+        <v>8.6128</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.778</v>
+        <v>6.7702</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>6.778</v>
+        <v>6.7702</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4062</v>
+        <v>7.5177</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8994</v>
+        <v>1.928</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7473</v>
+        <v>2.7442</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4062</v>
+        <v>7.5177</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7.4062</v>
+        <v>7.4065</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8218</v>
+        <v>5.822</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8218</v>
+        <v>5.822</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6788</v>
+        <v>5.768</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4564</v>
+        <v>1.4793</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9609</v>
+        <v>1.9626</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6788</v>
+        <v>5.768</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6788</v>
+        <v>5.6792</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4.464</v>
+        <v>4.4642</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>206</v>
       </c>
       <c r="M4" t="n">
-        <v>4.464</v>
+        <v>4.4642</v>
       </c>
       <c r="N4" t="n">
         <v>206</v>
@@ -630,26 +630,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3666</v>
+        <v>5.348</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3763</v>
+        <v>1.3716</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8188</v>
+        <v>1.775</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3666</v>
+        <v>5.348</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3666</v>
+        <v>5.1947</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,44 +658,44 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2185</v>
+        <v>4.0834</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2185</v>
+        <v>4.0834</v>
       </c>
       <c r="N5" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2074</v>
+        <v>5.3322</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3355</v>
+        <v>1.3675</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7463</v>
+        <v>1.768</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2074</v>
+        <v>5.3322</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2074</v>
+        <v>5.3668</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,19 +704,19 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.0933</v>
+        <v>4.2187</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0933</v>
+        <v>4.2187</v>
       </c>
       <c r="N6" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9051</v>
+        <v>5.1945</v>
       </c>
       <c r="C7" t="n">
-        <v>1.258</v>
+        <v>1.3322</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6087</v>
+        <v>1.7064</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9051</v>
+        <v>5.1945</v>
       </c>
       <c r="F7" t="n">
         <v>1.9012</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0039</v>
+        <v>3.0147</v>
       </c>
       <c r="H7" t="n">
         <v>1.9012</v>
@@ -750,7 +750,7 @@
         <v>1.9012</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3613</v>
+        <v>2.3698</v>
       </c>
       <c r="K7" t="n">
         <v>66</v>
@@ -759,7 +759,7 @@
         <v>101</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2625</v>
+        <v>4.271</v>
       </c>
       <c r="N7" t="n">
         <v>167</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.796</v>
+        <v>3.6734</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9735</v>
+        <v>0.9421</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1038</v>
+        <v>1.027</v>
       </c>
       <c r="E8" t="n">
-        <v>3.796</v>
+        <v>3.6734</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.796</v>
+        <v>3.7962</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9839</v>
+        <v>2.9841</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>206</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9839</v>
+        <v>2.9841</v>
       </c>
       <c r="N8" t="n">
         <v>206</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5356</v>
+        <v>3.6621</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.9392</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9853</v>
+        <v>1.022</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5356</v>
+        <v>3.6621</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5356</v>
+        <v>3.5358</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7792</v>
+        <v>2.7794</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>190</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7792</v>
+        <v>2.7794</v>
       </c>
       <c r="N9" t="n">
         <v>190</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7239</v>
+        <v>2.877</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6986</v>
+        <v>0.7379</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6158</v>
+        <v>0.6713</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7239</v>
+        <v>2.877</v>
       </c>
       <c r="F10" t="n">
         <v>1.1228</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6011</v>
+        <v>1.6002</v>
       </c>
       <c r="H10" t="n">
         <v>1.1228</v>
@@ -888,7 +888,7 @@
         <v>1.1228</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2586</v>
+        <v>1.2579</v>
       </c>
       <c r="K10" t="n">
         <v>66</v>
@@ -897,7 +897,7 @@
         <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3814</v>
+        <v>2.3807</v>
       </c>
       <c r="N10" t="n">
         <v>167</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2713</v>
+        <v>2.3092</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5825</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4097</v>
+        <v>0.4176</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2713</v>
+        <v>2.3092</v>
       </c>
       <c r="F11" t="n">
         <v>0.3502</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9211</v>
+        <v>1.9207</v>
       </c>
       <c r="H11" t="n">
         <v>0.3502</v>
@@ -934,7 +934,7 @@
         <v>0.3502</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5101</v>
+        <v>1.5098</v>
       </c>
       <c r="K11" t="n">
         <v>66</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8603</v>
+        <v>1.86</v>
       </c>
       <c r="N11" t="n">
         <v>167</v>
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9741</v>
+        <v>2.0648</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5063</v>
+        <v>0.5296</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2744</v>
+        <v>0.3085</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9741</v>
+        <v>2.0648</v>
       </c>
       <c r="F12" t="n">
         <v>0.2942</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6799</v>
+        <v>1.6941</v>
       </c>
       <c r="H12" t="n">
         <v>0.2942</v>
@@ -980,7 +980,7 @@
         <v>0.2942</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3205</v>
+        <v>1.3317</v>
       </c>
       <c r="K12" t="n">
         <v>66</v>
@@ -989,7 +989,7 @@
         <v>133</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6147</v>
+        <v>1.6259</v>
       </c>
       <c r="N12" t="n">
         <v>199</v>
@@ -998,26 +998,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.458</v>
+        <v>1.5514</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3739</v>
+        <v>0.3979</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0395</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.458</v>
+        <v>1.5514</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.458</v>
+        <v>1.2538</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1461</v>
+        <v>0.9856</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1461</v>
+        <v>0.9856</v>
       </c>
       <c r="N13" t="n">
         <v>71</v>
@@ -1044,26 +1044,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3013</v>
+        <v>1.4841</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3337</v>
+        <v>0.3806</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0318</v>
+        <v>0.0491</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3013</v>
+        <v>1.4841</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3013</v>
+        <v>1.4436</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0229</v>
+        <v>1.1348</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>206</v>
+        <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0229</v>
+        <v>1.1348</v>
       </c>
       <c r="N14" t="n">
-        <v>206</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2395</v>
+        <v>1.3151</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3179</v>
+        <v>0.3373</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>-0.0264</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2395</v>
+        <v>1.3151</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2395</v>
+        <v>1.3017</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9743000000000001</v>
+        <v>1.0232</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9743000000000001</v>
+        <v>1.0232</v>
       </c>
       <c r="N15" t="n">
-        <v>71</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8181</v>
+        <v>0.9601</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2098</v>
+        <v>0.2462</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2518</v>
+        <v>-0.185</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8181</v>
+        <v>0.9601</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8181</v>
+        <v>0.3166</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,65 +1164,65 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6431</v>
+        <v>0.2489</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6431</v>
+        <v>0.2489</v>
       </c>
       <c r="N16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ryu</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5659</v>
+        <v>0.8953</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1451</v>
+        <v>0.2296</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3666</v>
+        <v>-0.2139</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5659</v>
+        <v>0.8953</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3046</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8704</v>
+        <v>0.8176</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3046</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3046</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6842</v>
+        <v>0.6427</v>
       </c>
       <c r="K17" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3796</v>
+        <v>0.6427</v>
       </c>
       <c r="N17" t="n">
-        <v>167</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5272</v>
+        <v>0.6224</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1352</v>
+        <v>0.1596</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3842</v>
+        <v>-0.3358</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5272</v>
+        <v>0.6224</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>ryu</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5206</v>
+        <v>0.507</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1335</v>
+        <v>0.13</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3872</v>
+        <v>-0.3874</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5206</v>
+        <v>0.507</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0.3046</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5206</v>
+        <v>0.8698</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0.3046</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.3046</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4092</v>
+        <v>0.6837</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L19" t="n">
-        <v>206</v>
+        <v>101</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4092</v>
+        <v>0.3791</v>
       </c>
       <c r="N19" t="n">
-        <v>206</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20">
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4154</v>
+        <v>0.4503</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1065</v>
+        <v>0.1155</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4351</v>
+        <v>-0.4127</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4154</v>
+        <v>0.4503</v>
       </c>
       <c r="F20" t="n">
         <v>0.0488</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3666</v>
+        <v>0.3657</v>
       </c>
       <c r="H20" t="n">
         <v>0.0488</v>
@@ -1348,7 +1348,7 @@
         <v>0.0488</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2882</v>
+        <v>0.2875</v>
       </c>
       <c r="K20" t="n">
         <v>66</v>
@@ -1357,7 +1357,7 @@
         <v>133</v>
       </c>
       <c r="M20" t="n">
-        <v>0.337</v>
+        <v>0.3363</v>
       </c>
       <c r="N20" t="n">
         <v>199</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3951</v>
+        <v>0.3685</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1013</v>
+        <v>0.0945</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4443</v>
+        <v>-0.4492</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3951</v>
+        <v>0.3685</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3903</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7854</v>
+        <v>0.5208</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3903</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3903</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.4094</v>
       </c>
       <c r="K21" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2271</v>
+        <v>0.4094</v>
       </c>
       <c r="N21" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3166</v>
+        <v>0.3553</v>
       </c>
       <c r="C22" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0911</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4801</v>
+        <v>-0.4551</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3166</v>
+        <v>0.3553</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0.3903</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3166</v>
+        <v>0.7852</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.3903</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.3903</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2489</v>
+        <v>0.6172</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L22" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2489</v>
+        <v>0.2269</v>
       </c>
       <c r="N22" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23">
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1398</v>
+        <v>0.3026</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0359</v>
+        <v>0.0776</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5606</v>
+        <v>-0.4787</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1398</v>
+        <v>0.3026</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0941</v>
+        <v>0.2935</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0241</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5814</v>
+        <v>-0.4827</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0941</v>
+        <v>0.2935</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.094</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0241</v>
+        <v>0.0216</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5814</v>
+        <v>-0.5763</v>
       </c>
       <c r="E25" t="n">
-        <v>0.094</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="F25" t="n">
         <v>0.2506</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1566</v>
+        <v>-0.1569</v>
       </c>
       <c r="H25" t="n">
         <v>0.2506</v>
@@ -1578,7 +1578,7 @@
         <v>0.2506</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1231</v>
+        <v>-0.1233</v>
       </c>
       <c r="K25" t="n">
         <v>66</v>
@@ -1587,7 +1587,7 @@
         <v>133</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1275</v>
+        <v>0.1273</v>
       </c>
       <c r="N25" t="n">
         <v>199</v>
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0911</v>
+        <v>-0.1152</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0234</v>
+        <v>-0.0295</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6657</v>
+        <v>-0.6653</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0911</v>
+        <v>-0.1152</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0911</v>
+        <v>-0.0912</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0716</v>
+        <v>-0.0717</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>71</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0716</v>
+        <v>-0.0717</v>
       </c>
       <c r="N26" t="n">
         <v>71</v>
@@ -1642,26 +1642,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1749</v>
+        <v>-0.2811</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0449</v>
+        <v>-0.0721</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7038</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1749</v>
+        <v>-0.2811</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1749</v>
+        <v>-0.4422</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.1375</v>
+        <v>-0.3476</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1375</v>
+        <v>-0.3476</v>
       </c>
       <c r="N27" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2462</v>
+        <v>-0.3619</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0631</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7363</v>
+        <v>-0.7755</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2462</v>
+        <v>-0.3619</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2462</v>
+        <v>-0.1749</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,19 +1716,19 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1935</v>
+        <v>-0.1375</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1935</v>
+        <v>-0.1375</v>
       </c>
       <c r="N28" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3791</v>
+        <v>-0.5059</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1297</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7968</v>
+        <v>-0.8398</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3791</v>
+        <v>-0.5059</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3791</v>
+        <v>-0.3506</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.298</v>
+        <v>-0.2756</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>41</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.298</v>
+        <v>-0.2756</v>
       </c>
       <c r="N29" t="n">
         <v>41</v>
@@ -1780,26 +1780,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4417</v>
+        <v>-0.5313</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1133</v>
+        <v>-0.1363</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8253</v>
+        <v>-0.8511</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4417</v>
+        <v>-0.5313</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4417</v>
+        <v>-0.2462</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,19 +1808,19 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3472</v>
+        <v>-0.1935</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3472</v>
+        <v>-0.1935</v>
       </c>
       <c r="N30" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5381</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.138</v>
+        <v>-0.1653</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8692</v>
+        <v>-0.9018</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5381</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1872,26 +1872,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6499</v>
+        <v>-0.7408</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1667</v>
+        <v>-0.19</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9201</v>
+        <v>-0.9447</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6499</v>
+        <v>-0.7408</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6499</v>
+        <v>-0.7212</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,44 +1900,44 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5109</v>
+        <v>-0.5669</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5109</v>
+        <v>-0.5669</v>
       </c>
       <c r="N32" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.697</v>
+        <v>-0.8487</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1788</v>
+        <v>-0.2177</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9415</v>
+        <v>-0.9929</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.697</v>
+        <v>-0.8487</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.697</v>
+        <v>-0.7222</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,44 +1946,44 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5677</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5677</v>
       </c>
       <c r="N33" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7209</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1849</v>
+        <v>-0.2336</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9524</v>
+        <v>-1.0207</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7209</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.7209</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,90 +1992,90 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.5667</v>
+        <v>-0.647</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5667</v>
+        <v>-0.647</v>
       </c>
       <c r="N34" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7222</v>
+        <v>-0.9169</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1852</v>
+        <v>-0.2352</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.953</v>
+        <v>-1.0234</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7222</v>
+        <v>-0.9169</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-0.2379</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7222</v>
+        <v>-0.6548</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-0.2379</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>-0.2379</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5677</v>
+        <v>-0.5147</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L35" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5677</v>
+        <v>-0.7526</v>
       </c>
       <c r="N35" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.9371</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2111</v>
+        <v>-0.2403</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9989</v>
+        <v>-1.0324</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.9371</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.697</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,90 +2084,90 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.647</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.647</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8924</v>
+        <v>-0.9885</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2289</v>
+        <v>-0.2535</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0304</v>
+        <v>-1.0554</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8924</v>
+        <v>-0.9885</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.2379</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6545</v>
+        <v>-0.6499</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2379</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2379</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5145</v>
+        <v>-0.5109</v>
       </c>
       <c r="K37" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7524</v>
+        <v>-0.5109</v>
       </c>
       <c r="N37" t="n">
-        <v>199</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9638</v>
+        <v>-1.0741</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2472</v>
+        <v>-0.2755</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0629</v>
+        <v>-1.0936</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9638</v>
+        <v>-1.0741</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.9638</v>
+        <v>-0.9952</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,44 +2176,44 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.7823</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.7823</v>
       </c>
       <c r="N38" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9952</v>
+        <v>-1.2236</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2552</v>
+        <v>-0.3138</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0772</v>
+        <v>-1.1604</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9952</v>
+        <v>-1.2236</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9952</v>
+        <v>-0.964</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,111 +2222,111 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7823</v>
+        <v>-0.7578</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7823</v>
+        <v>-0.7578</v>
       </c>
       <c r="N39" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8093</v>
+        <v>-2.1386</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.464</v>
+        <v>-0.5485</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4478</v>
+        <v>-1.5691</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8093</v>
+        <v>-2.1386</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.4396</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.3697</v>
+        <v>-1.8612</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4396</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4396</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.0767</v>
+        <v>-1.463</v>
       </c>
       <c r="K40" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5163</v>
+        <v>-1.463</v>
       </c>
       <c r="N40" t="n">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8614</v>
+        <v>-2.1702</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4774</v>
+        <v>-0.5566</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4716</v>
+        <v>-1.5832</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8614</v>
+        <v>-2.1702</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-0.4396</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.8614</v>
+        <v>-1.3697</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>-0.4396</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>-0.4396</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.4632</v>
+        <v>-1.0767</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L41" t="n">
-        <v>190</v>
+        <v>101</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4632</v>
+        <v>-1.5163</v>
       </c>
       <c r="N41" t="n">
-        <v>190</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -5629,10 +5629,10 @@
         <v>1.74</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2154</v>
+        <v>1.2157</v>
       </c>
       <c r="J82" t="n">
-        <v>18.231</v>
+        <v>18.2355</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.72</v>
       </c>
       <c r="I83" t="n">
-        <v>1.191</v>
+        <v>1.1913</v>
       </c>
       <c r="J83" t="n">
-        <v>17.865</v>
+        <v>17.8695</v>
       </c>
     </row>
     <row r="84">
@@ -5706,13 +5706,13 @@
         <v>15</v>
       </c>
       <c r="H84" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7723</v>
       </c>
       <c r="J84" t="n">
-        <v>11.787</v>
+        <v>11.5845</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.38</v>
       </c>
       <c r="I85" t="n">
-        <v>0.7582</v>
+        <v>0.7584</v>
       </c>
       <c r="J85" t="n">
-        <v>11.373</v>
+        <v>11.376</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.18</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4539</v>
+        <v>0.4541</v>
       </c>
       <c r="J86" t="n">
-        <v>6.8085</v>
+        <v>6.8115</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.9</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0842</v>
+        <v>-0.0849</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.263</v>
+        <v>-1.2735</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.75</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2544</v>
+        <v>-0.2549</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.816</v>
+        <v>-3.8235</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.6</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3943</v>
+        <v>-0.3945</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.9145</v>
+        <v>-5.9175</v>
       </c>
     </row>
     <row r="90">
@@ -5946,13 +5946,13 @@
         <v>15</v>
       </c>
       <c r="H90" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.525</v>
+        <v>-0.5165</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.875</v>
+        <v>-7.7475</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6308</v>
+        <v>-0.6311</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.462</v>
+        <v>-9.4665</v>
       </c>
     </row>
     <row r="92">
@@ -6626,13 +6626,13 @@
         <v>18</v>
       </c>
       <c r="H107" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7016</v>
+        <v>0.7128</v>
       </c>
       <c r="J107" t="n">
-        <v>12.6288</v>
+        <v>12.8304</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0878</v>
+        <v>0.0871</v>
       </c>
       <c r="J108" t="n">
-        <v>1.5804</v>
+        <v>1.5678</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.72</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3087</v>
+        <v>-0.3089</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.5566</v>
+        <v>-5.5602</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.52</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4878</v>
+        <v>-0.488</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.7804</v>
+        <v>-8.784000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.36</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.6247</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.241</v>
+        <v>-11.2446</v>
       </c>
     </row>
     <row r="112">
@@ -8426,13 +8426,13 @@
         <v>24</v>
       </c>
       <c r="H152" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6168</v>
+        <v>0.6057</v>
       </c>
       <c r="J152" t="n">
-        <v>14.8032</v>
+        <v>14.5368</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2029</v>
+        <v>0.2033</v>
       </c>
       <c r="J153" t="n">
-        <v>4.8696</v>
+        <v>4.8792</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.87</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1749</v>
+        <v>-0.1747</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.1976</v>
+        <v>-4.1928</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2468</v>
+        <v>-0.2466</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.9232</v>
+        <v>-5.9184</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.62</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4144</v>
+        <v>-0.4142</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.945600000000001</v>
+        <v>-9.940799999999999</v>
       </c>
     </row>
     <row r="157">
@@ -9226,13 +9226,13 @@
         <v>24</v>
       </c>
       <c r="H172" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5971</v>
+        <v>0.608</v>
       </c>
       <c r="J172" t="n">
-        <v>14.3304</v>
+        <v>14.592</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2865</v>
+        <v>0.2862</v>
       </c>
       <c r="J173" t="n">
-        <v>6.876</v>
+        <v>6.8688</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1447</v>
+        <v>0.1445</v>
       </c>
       <c r="J174" t="n">
-        <v>3.4728</v>
+        <v>3.468</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1714</v>
+        <v>-0.1716</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.1136</v>
+        <v>-4.1184</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3219</v>
+        <v>-0.3221</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.7256</v>
+        <v>-7.7304</v>
       </c>
     </row>
     <row r="177">
@@ -10826,13 +10826,13 @@
         <v>24</v>
       </c>
       <c r="H212" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1639</v>
+        <v>0.1863</v>
       </c>
       <c r="J212" t="n">
-        <v>3.9336</v>
+        <v>4.4712</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1147</v>
+        <v>0.1143</v>
       </c>
       <c r="J213" t="n">
-        <v>2.7528</v>
+        <v>2.7432</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1147</v>
+        <v>0.1143</v>
       </c>
       <c r="J214" t="n">
-        <v>2.7528</v>
+        <v>2.7432</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.77</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2736</v>
+        <v>-0.2738</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.5664</v>
+        <v>-6.5712</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3488</v>
+        <v>-0.349</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.3712</v>
+        <v>-8.375999999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11426,13 +11426,13 @@
         <v>17</v>
       </c>
       <c r="H227" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="I227" t="n">
-        <v>1.9241</v>
+        <v>1.9136</v>
       </c>
       <c r="J227" t="n">
-        <v>32.7097</v>
+        <v>32.5312</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.59</v>
       </c>
       <c r="I228" t="n">
-        <v>1.0312</v>
+        <v>1.0314</v>
       </c>
       <c r="J228" t="n">
-        <v>17.5304</v>
+        <v>17.5338</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.31</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6593</v>
+        <v>0.6595</v>
       </c>
       <c r="J229" t="n">
-        <v>11.2081</v>
+        <v>11.2115</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.21</v>
       </c>
       <c r="I230" t="n">
-        <v>0.5053</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="J230" t="n">
-        <v>8.5901</v>
+        <v>8.593500000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.91</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3949</v>
+        <v>-0.3947</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.7133</v>
+        <v>-6.7099</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8413/event_8413_evp_summary.xlsx
+++ b/database/event/8413/event_8413_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.8475</v>
+        <v>8.6769</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2691</v>
+        <v>2.2253</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3382</v>
+        <v>3.347</v>
       </c>
       <c r="E2" t="n">
-        <v>8.8475</v>
+        <v>8.6769</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.6128</v>
+        <v>8.4422</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7702</v>
+        <v>6.6746</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7702</v>
+        <v>6.6746</v>
       </c>
       <c r="N2" t="n">
         <v>190</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.5177</v>
+        <v>7.5649</v>
       </c>
       <c r="C3" t="n">
-        <v>1.928</v>
+        <v>1.9401</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7442</v>
+        <v>2.8404</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5177</v>
+        <v>7.5649</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7.4065</v>
+        <v>7.4537</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5.822</v>
+        <v>5.893</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="M3" t="n">
-        <v>5.822</v>
+        <v>5.893</v>
       </c>
       <c r="N3" t="n">
         <v>190</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.768</v>
+        <v>5.5799</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4793</v>
+        <v>1.4311</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9626</v>
+        <v>1.9361</v>
       </c>
       <c r="E4" t="n">
-        <v>5.768</v>
+        <v>5.5799</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6792</v>
+        <v>5.4911</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4642</v>
+        <v>4.3413</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>206</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4642</v>
+        <v>4.3413</v>
       </c>
       <c r="N4" t="n">
         <v>206</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.348</v>
+        <v>5.2158</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3716</v>
+        <v>1.3377</v>
       </c>
       <c r="D5" t="n">
-        <v>1.775</v>
+        <v>1.7703</v>
       </c>
       <c r="E5" t="n">
-        <v>5.348</v>
+        <v>5.2158</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1947</v>
+        <v>5.0625</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0834</v>
+        <v>4.0025</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>206</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0834</v>
+        <v>4.0025</v>
       </c>
       <c r="N5" t="n">
         <v>206</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3322</v>
+        <v>5.1833</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3675</v>
+        <v>1.3293</v>
       </c>
       <c r="D6" t="n">
-        <v>1.768</v>
+        <v>1.7555</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3322</v>
+        <v>5.1833</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5.3668</v>
+        <v>5.2179</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2187</v>
+        <v>4.1254</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>190</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2187</v>
+        <v>4.1254</v>
       </c>
       <c r="N6" t="n">
         <v>190</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.1945</v>
+        <v>5.1696</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3322</v>
+        <v>1.3258</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7064</v>
+        <v>1.7492</v>
       </c>
       <c r="E7" t="n">
-        <v>5.1945</v>
+        <v>5.1696</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9012</v>
+        <v>1.9387</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0147</v>
+        <v>2.9523</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9012</v>
+        <v>1.9387</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9012</v>
+        <v>1.9387</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3698</v>
+        <v>2.3341</v>
       </c>
       <c r="K7" t="n">
         <v>66</v>
@@ -759,7 +759,7 @@
         <v>101</v>
       </c>
       <c r="M7" t="n">
-        <v>4.271</v>
+        <v>4.2728</v>
       </c>
       <c r="N7" t="n">
         <v>167</v>
@@ -768,26 +768,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6734</v>
+        <v>3.7301</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9421</v>
+        <v>0.9566</v>
       </c>
       <c r="D8" t="n">
-        <v>1.027</v>
+        <v>1.0935</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6734</v>
+        <v>3.7301</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7962</v>
+        <v>3.6038</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,44 +796,44 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9841</v>
+        <v>2.8492</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9841</v>
+        <v>2.8492</v>
       </c>
       <c r="N8" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6621</v>
+        <v>3.4714</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9392</v>
+        <v>0.8903</v>
       </c>
       <c r="D9" t="n">
-        <v>1.022</v>
+        <v>0.9756</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6621</v>
+        <v>3.4714</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5358</v>
+        <v>3.5942</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,19 +842,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7794</v>
+        <v>2.8416</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7794</v>
+        <v>2.8416</v>
       </c>
       <c r="N9" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.877</v>
+        <v>2.7863</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7379</v>
+        <v>0.7146</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6713</v>
+        <v>0.6635</v>
       </c>
       <c r="E10" t="n">
-        <v>2.877</v>
+        <v>2.7863</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1228</v>
+        <v>1.1252</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6002</v>
+        <v>1.5071</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1228</v>
+        <v>1.1252</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1228</v>
+        <v>1.1252</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2579</v>
+        <v>1.1916</v>
       </c>
       <c r="K10" t="n">
         <v>66</v>
@@ -897,7 +897,7 @@
         <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3807</v>
+        <v>2.3168</v>
       </c>
       <c r="N10" t="n">
         <v>167</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3092</v>
+        <v>2.0817</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.5339</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4176</v>
+        <v>0.3425</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3092</v>
+        <v>2.0817</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3502</v>
+        <v>0.3258</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9207</v>
+        <v>1.7176</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3502</v>
+        <v>0.3258</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3502</v>
+        <v>0.3258</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5098</v>
+        <v>1.3579</v>
       </c>
       <c r="K11" t="n">
         <v>66</v>
@@ -943,7 +943,7 @@
         <v>101</v>
       </c>
       <c r="M11" t="n">
-        <v>1.86</v>
+        <v>1.6837</v>
       </c>
       <c r="N11" t="n">
         <v>167</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0648</v>
+        <v>1.9822</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5296</v>
+        <v>0.5084</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3085</v>
+        <v>0.2972</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0648</v>
+        <v>1.9822</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2942</v>
+        <v>0.2764</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6941</v>
+        <v>1.6294</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2942</v>
+        <v>0.2764</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2942</v>
+        <v>0.2764</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3317</v>
+        <v>1.2882</v>
       </c>
       <c r="K12" t="n">
         <v>66</v>
@@ -989,7 +989,7 @@
         <v>133</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6259</v>
+        <v>1.5646</v>
       </c>
       <c r="N12" t="n">
         <v>199</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5514</v>
+        <v>1.3999</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3979</v>
+        <v>0.359</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0319</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5514</v>
+        <v>1.3999</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2538</v>
+        <v>1.1023</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9856</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9856</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>71</v>
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4841</v>
+        <v>1.3146</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3806</v>
+        <v>0.3371</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0491</v>
+        <v>-0.0069</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4841</v>
+        <v>1.3146</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4436</v>
+        <v>1.2741</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1348</v>
+        <v>1.0073</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1348</v>
+        <v>1.0073</v>
       </c>
       <c r="N14" t="n">
         <v>71</v>
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3151</v>
+        <v>1.2178</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3373</v>
+        <v>0.3123</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0264</v>
+        <v>-0.051</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3151</v>
+        <v>1.2178</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3017</v>
+        <v>1.2044</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0232</v>
+        <v>0.9522</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>206</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0232</v>
+        <v>0.9522</v>
       </c>
       <c r="N15" t="n">
         <v>206</v>
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9601</v>
+        <v>0.9347</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2462</v>
+        <v>0.2397</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.185</v>
+        <v>-0.18</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9601</v>
+        <v>0.9347</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3166</v>
+        <v>0.2912</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2489</v>
+        <v>0.2302</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>39</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2489</v>
+        <v>0.2302</v>
       </c>
       <c r="N16" t="n">
         <v>39</v>
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8953</v>
+        <v>0.8371</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2296</v>
+        <v>0.2147</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2139</v>
+        <v>-0.2244</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8953</v>
+        <v>0.8371</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8176</v>
+        <v>0.7594</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6427</v>
+        <v>0.6004</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>41</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6427</v>
+        <v>0.6004</v>
       </c>
       <c r="N17" t="n">
         <v>41</v>
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6224</v>
+        <v>0.551</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1596</v>
+        <v>0.1413</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3358</v>
+        <v>-0.3548</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6224</v>
+        <v>0.551</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5272</v>
+        <v>0.4558</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4144</v>
+        <v>0.3604</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4144</v>
+        <v>0.3604</v>
       </c>
       <c r="N18" t="n">
         <v>57</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.507</v>
+        <v>0.5105</v>
       </c>
       <c r="C19" t="n">
-        <v>0.13</v>
+        <v>0.1309</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3874</v>
+        <v>-0.3732</v>
       </c>
       <c r="E19" t="n">
-        <v>0.507</v>
+        <v>0.5105</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3046</v>
+        <v>-0.3078</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8698</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3046</v>
+        <v>-0.3078</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3046</v>
+        <v>-0.3078</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6837</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>66</v>
@@ -1311,7 +1311,7 @@
         <v>101</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3791</v>
+        <v>0.3851999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>167</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4503</v>
+        <v>0.4247</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1155</v>
+        <v>0.1089</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4127</v>
+        <v>-0.4123</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4503</v>
+        <v>0.4247</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0488</v>
+        <v>0.0378</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3657</v>
+        <v>0.3511</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0488</v>
+        <v>0.0378</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0488</v>
+        <v>0.0378</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2875</v>
+        <v>0.2776</v>
       </c>
       <c r="K20" t="n">
         <v>66</v>
@@ -1357,7 +1357,7 @@
         <v>133</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3363</v>
+        <v>0.3154</v>
       </c>
       <c r="N20" t="n">
         <v>199</v>
@@ -1366,26 +1366,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3685</v>
+        <v>0.2766</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0945</v>
+        <v>0.0709</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4492</v>
+        <v>-0.4798</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3685</v>
+        <v>0.2766</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5208</v>
+        <v>0.1138</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,90 +1394,90 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4094</v>
+        <v>0.09</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>206</v>
+        <v>71</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4094</v>
+        <v>0.09</v>
       </c>
       <c r="N21" t="n">
-        <v>206</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3553</v>
+        <v>0.276</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0911</v>
+        <v>0.0708</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4551</v>
+        <v>-0.4801</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3553</v>
+        <v>0.276</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3903</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7852</v>
+        <v>0.4283</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3903</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3903</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6172</v>
+        <v>0.3386</v>
       </c>
       <c r="K22" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2269</v>
+        <v>0.3386</v>
       </c>
       <c r="N22" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3026</v>
+        <v>0.2564</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0776</v>
+        <v>0.0658</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4787</v>
+        <v>-0.489</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3026</v>
+        <v>0.2564</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1398</v>
+        <v>0.057</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,65 +1486,65 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1099</v>
+        <v>0.0451</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1099</v>
+        <v>0.0451</v>
       </c>
       <c r="N23" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2935</v>
+        <v>0.2095</v>
       </c>
       <c r="C24" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0537</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4827</v>
+        <v>-0.5104</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2935</v>
+        <v>0.2095</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-0.3646</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0941</v>
+        <v>0.6136</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-0.3646</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-0.3646</v>
       </c>
       <c r="J24" t="n">
-        <v>0.074</v>
+        <v>0.4851</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L24" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="M24" t="n">
-        <v>0.074</v>
+        <v>0.1205</v>
       </c>
       <c r="N24" t="n">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0216</v>
+        <v>0.0228</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5763</v>
+        <v>-0.5653</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2506</v>
+        <v>0.2038</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1569</v>
+        <v>-0.1052</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2506</v>
+        <v>0.2038</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2506</v>
+        <v>0.2038</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1233</v>
+        <v>-0.0832</v>
       </c>
       <c r="K25" t="n">
         <v>66</v>
@@ -1587,7 +1587,7 @@
         <v>133</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1273</v>
+        <v>0.1206</v>
       </c>
       <c r="N25" t="n">
         <v>199</v>
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1152</v>
+        <v>-0.1291</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0295</v>
+        <v>-0.0331</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6653</v>
+        <v>-0.6646</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1152</v>
+        <v>-0.1291</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0912</v>
+        <v>-0.1051</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0717</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>71</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0717</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>71</v>
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2811</v>
+        <v>-0.3085</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0721</v>
+        <v>-0.0791</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.7463</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2811</v>
+        <v>-0.3085</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4422</v>
+        <v>-0.4696</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3476</v>
+        <v>-0.3713</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>41</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3476</v>
+        <v>-0.3713</v>
       </c>
       <c r="N27" t="n">
         <v>41</v>
@@ -1692,22 +1692,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3619</v>
+        <v>-0.3865</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7755</v>
+        <v>-0.7819</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3619</v>
+        <v>-0.3865</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1749</v>
+        <v>-0.1995</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1375</v>
+        <v>-0.1577</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>57</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1375</v>
+        <v>-0.1577</v>
       </c>
       <c r="N28" t="n">
         <v>57</v>
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5059</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1297</v>
+        <v>-0.1403</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8398</v>
+        <v>-0.8549</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5059</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3506</v>
+        <v>-0.3916</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2756</v>
+        <v>-0.3096</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>41</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2756</v>
+        <v>-0.3096</v>
       </c>
       <c r="N29" t="n">
         <v>41</v>
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5313</v>
+        <v>-0.5764</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1363</v>
+        <v>-0.1478</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8511</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5313</v>
+        <v>-0.5764</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2462</v>
+        <v>-0.2913</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1935</v>
+        <v>-0.2303</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>39</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1935</v>
+        <v>-0.2303</v>
       </c>
       <c r="N30" t="n">
         <v>39</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.5968</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1653</v>
+        <v>-0.1531</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9018</v>
+        <v>-0.8777</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.5968</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5381</v>
+        <v>-0.4902</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.423</v>
+        <v>-0.3876</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.423</v>
+        <v>-0.3876</v>
       </c>
       <c r="N31" t="n">
         <v>39</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7408</v>
+        <v>-0.6936</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.19</v>
+        <v>-0.1779</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9447</v>
+        <v>-0.9218</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7408</v>
+        <v>-0.6936</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7212</v>
+        <v>-0.674</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5669</v>
+        <v>-0.5329</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>41</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5669</v>
+        <v>-0.5329</v>
       </c>
       <c r="N32" t="n">
         <v>41</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8487</v>
+        <v>-0.8015</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2177</v>
+        <v>-0.2056</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9929</v>
+        <v>-0.9709</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8487</v>
+        <v>-0.8015</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7222</v>
+        <v>-0.675</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5677</v>
+        <v>-0.5337</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>39</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5677</v>
+        <v>-0.5337</v>
       </c>
       <c r="N33" t="n">
         <v>39</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.8125</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2336</v>
+        <v>-0.2084</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0207</v>
+        <v>-0.9759</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.8125</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-0.2478</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.5405</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>-0.2478</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>-0.2478</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.647</v>
+        <v>-0.4273</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L34" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.647</v>
+        <v>-0.6751</v>
       </c>
       <c r="N34" t="n">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9169</v>
+        <v>-0.8568</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2352</v>
+        <v>-0.2197</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0234</v>
+        <v>-0.9961</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9169</v>
+        <v>-0.8568</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2379</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.6548</v>
+        <v>-0.7691</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2379</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2379</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5147</v>
+        <v>-0.6081</v>
       </c>
       <c r="K35" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7526</v>
+        <v>-0.6081</v>
       </c>
       <c r="N35" t="n">
-        <v>199</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9371</v>
+        <v>-0.9507</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2403</v>
+        <v>-0.2438</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0324</v>
+        <v>-1.0389</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9371</v>
+        <v>-0.9507</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.697</v>
+        <v>-0.7106</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5618</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>71</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5618</v>
       </c>
       <c r="N36" t="n">
         <v>71</v>
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9885</v>
+        <v>-0.9598</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2535</v>
+        <v>-0.2462</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0554</v>
+        <v>-1.043</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9885</v>
+        <v>-0.9598</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6499</v>
+        <v>-0.6212</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5109</v>
+        <v>-0.4911</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>39</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5109</v>
+        <v>-0.4911</v>
       </c>
       <c r="N37" t="n">
         <v>39</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0741</v>
+        <v>-1.0107</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2755</v>
+        <v>-0.2592</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0936</v>
+        <v>-1.0662</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0741</v>
+        <v>-1.0107</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.9952</v>
+        <v>-0.9318</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7823</v>
+        <v>-0.7367</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7823</v>
+        <v>-0.7367</v>
       </c>
       <c r="N38" t="n">
         <v>57</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2236</v>
+        <v>-1.1856</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3138</v>
+        <v>-0.3041</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1604</v>
+        <v>-1.1459</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2236</v>
+        <v>-1.1856</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.964</v>
+        <v>-0.926</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7578</v>
+        <v>-0.7321</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>41</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7578</v>
+        <v>-0.7321</v>
       </c>
       <c r="N39" t="n">
         <v>41</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1386</v>
+        <v>-1.9942</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5485</v>
+        <v>-0.5114</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5691</v>
+        <v>-1.5142</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.1386</v>
+        <v>-1.9942</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.8612</v>
+        <v>-1.7168</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.463</v>
+        <v>-1.3573</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>190</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.463</v>
+        <v>-1.3573</v>
       </c>
       <c r="N40" t="n">
         <v>190</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1702</v>
+        <v>-2.1135</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5566</v>
+        <v>-0.542</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5832</v>
+        <v>-1.5686</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.1702</v>
+        <v>-2.1135</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.4396</v>
+        <v>-0.4353</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.3697</v>
+        <v>-1.3173</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.4396</v>
+        <v>-0.4353</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4396</v>
+        <v>-0.4353</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.0767</v>
+        <v>-1.0415</v>
       </c>
       <c r="K41" t="n">
         <v>66</v>
@@ -2323,7 +2323,7 @@
         <v>101</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5163</v>
+        <v>-1.4768</v>
       </c>
       <c r="N41" t="n">
         <v>167</v>
@@ -2429,10 +2429,10 @@
         <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7917</v>
+        <v>1.8344</v>
       </c>
       <c r="J2" t="n">
-        <v>35.834</v>
+        <v>36.688</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.45</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0191</v>
+        <v>1.0161</v>
       </c>
       <c r="J3" t="n">
-        <v>20.382</v>
+        <v>20.322</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>18.156</v>
+        <v>17.914</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2251</v>
+        <v>-0.1929</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.502</v>
+        <v>-3.858</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.84</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5503</v>
+        <v>-0.516</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.006</v>
+        <v>-10.32</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1383</v>
+        <v>0.1081</v>
       </c>
       <c r="J7" t="n">
-        <v>2.766</v>
+        <v>2.162</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1104</v>
+        <v>0.0847</v>
       </c>
       <c r="J8" t="n">
-        <v>2.208</v>
+        <v>1.694</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1439</v>
+        <v>-0.128</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.878</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3302</v>
+        <v>-0.314</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.604</v>
+        <v>-6.28</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.48</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5252</v>
+        <v>-0.5281</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.504</v>
+        <v>-10.562</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6118</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>14.6832</v>
+        <v>15.3744</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1978</v>
+        <v>0.1811</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7472</v>
+        <v>4.3464</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.96</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0725</v>
+        <v>-0.0582</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.74</v>
+        <v>-1.3968</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1469</v>
+        <v>-0.1273</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.5256</v>
+        <v>-3.0552</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4197</v>
+        <v>-0.4115</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.0728</v>
+        <v>-9.875999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.37</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.4401</v>
       </c>
       <c r="J17" t="n">
-        <v>12.2064</v>
+        <v>10.5624</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0871</v>
+        <v>0.0635</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0904</v>
+        <v>1.524</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0688</v>
+        <v>0.0492</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6512</v>
+        <v>1.1808</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.064</v>
+        <v>-0.0501</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.536</v>
+        <v>-1.2024</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.064</v>
+        <v>-0.0501</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.536</v>
+        <v>-1.2024</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.72</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5287</v>
+        <v>1.5623</v>
       </c>
       <c r="J22" t="n">
-        <v>32.1027</v>
+        <v>32.8083</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6928</v>
+        <v>0.6625</v>
       </c>
       <c r="J23" t="n">
-        <v>14.5488</v>
+        <v>13.9125</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5329</v>
       </c>
       <c r="J24" t="n">
-        <v>11.907</v>
+        <v>11.1909</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.09</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2848</v>
+        <v>0.2527</v>
       </c>
       <c r="J25" t="n">
-        <v>5.9808</v>
+        <v>5.3067</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.886</v>
+        <v>-0.8742</v>
       </c>
       <c r="J26" t="n">
-        <v>-18.606</v>
+        <v>-18.3582</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5959</v>
+        <v>0.5386</v>
       </c>
       <c r="J27" t="n">
-        <v>12.5139</v>
+        <v>11.3106</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.18</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4111</v>
+        <v>0.3548</v>
       </c>
       <c r="J28" t="n">
-        <v>8.633100000000001</v>
+        <v>7.4508</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.18</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4111</v>
+        <v>0.3548</v>
       </c>
       <c r="J29" t="n">
-        <v>8.633100000000001</v>
+        <v>7.4508</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.62</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4155</v>
+        <v>-0.4064</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.7255</v>
+        <v>-8.5344</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.49</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5278</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.0838</v>
+        <v>-11.1888</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.29</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7444</v>
+        <v>0.7148</v>
       </c>
       <c r="J32" t="n">
-        <v>16.3768</v>
+        <v>15.7256</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7236</v>
+        <v>0.6929</v>
       </c>
       <c r="J33" t="n">
-        <v>15.9192</v>
+        <v>15.2438</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.27</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7027</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>15.4594</v>
+        <v>14.7598</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.19</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5303</v>
+        <v>0.493</v>
       </c>
       <c r="J35" t="n">
-        <v>11.6666</v>
+        <v>10.846</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.857</v>
+        <v>-0.8407</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.854</v>
+        <v>-18.4954</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3534</v>
+        <v>0.3007</v>
       </c>
       <c r="J37" t="n">
-        <v>7.7748</v>
+        <v>6.6154</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.07</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2128</v>
+        <v>0.1703</v>
       </c>
       <c r="J38" t="n">
-        <v>4.6816</v>
+        <v>3.7466</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.93</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1046</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.3012</v>
+        <v>-1.9668</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.79</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2526</v>
+        <v>-0.2331</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.5572</v>
+        <v>-5.1282</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4632</v>
+        <v>-0.4588</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.1904</v>
+        <v>-10.0936</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.97</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0457</v>
+        <v>1.0006</v>
       </c>
       <c r="J42" t="n">
-        <v>21.9597</v>
+        <v>21.0126</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.38</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4931</v>
+        <v>0.4264</v>
       </c>
       <c r="J43" t="n">
-        <v>10.3551</v>
+        <v>8.9544</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.17</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2585</v>
+        <v>0.2118</v>
       </c>
       <c r="J44" t="n">
-        <v>5.4285</v>
+        <v>4.4478</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.91</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1562</v>
+        <v>-0.1375</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.2802</v>
+        <v>-2.8875</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.87</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.201</v>
+        <v>-0.182</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.221</v>
+        <v>-3.822</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.62</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8703</v>
+        <v>0.9654</v>
       </c>
       <c r="J47" t="n">
-        <v>18.2763</v>
+        <v>20.2734</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4388</v>
+        <v>0.4432</v>
       </c>
       <c r="J48" t="n">
-        <v>9.2148</v>
+        <v>9.3072</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.67</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3669</v>
+        <v>-0.353</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.7049</v>
+        <v>-7.413</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.57</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4558</v>
+        <v>-0.4507</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.5718</v>
+        <v>-9.464700000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.44</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5668</v>
+        <v>-0.5772</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.9028</v>
+        <v>-12.1212</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.86</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1657</v>
+        <v>-0.1501</v>
       </c>
       <c r="J52" t="n">
-        <v>-2.8169</v>
+        <v>-2.5517</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.85</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1767</v>
+        <v>-0.1611</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.0039</v>
+        <v>-2.7387</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.77</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2579</v>
+        <v>-0.2423</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.3843</v>
+        <v>-4.1191</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.66</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3574</v>
+        <v>-0.3435</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.0758</v>
+        <v>-5.8395</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4377</v>
+        <v>-0.4295</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.4409</v>
+        <v>-7.3015</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.07</v>
       </c>
       <c r="I57" t="n">
-        <v>1.7889</v>
+        <v>1.8499</v>
       </c>
       <c r="J57" t="n">
-        <v>30.4113</v>
+        <v>31.4483</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6545</v>
+        <v>0.6299</v>
       </c>
       <c r="J58" t="n">
-        <v>11.1265</v>
+        <v>10.7083</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4818</v>
+        <v>0.4514</v>
       </c>
       <c r="J59" t="n">
-        <v>8.1906</v>
+        <v>7.6738</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3388</v>
+        <v>0.3069</v>
       </c>
       <c r="J60" t="n">
-        <v>5.7596</v>
+        <v>5.2173</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.07</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2056</v>
+        <v>0.1761</v>
       </c>
       <c r="J61" t="n">
-        <v>3.4952</v>
+        <v>2.9937</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4195</v>
+        <v>0.3637</v>
       </c>
       <c r="J62" t="n">
-        <v>11.746</v>
+        <v>10.1836</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1849</v>
+        <v>0.1452</v>
       </c>
       <c r="J63" t="n">
-        <v>5.1772</v>
+        <v>4.0656</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.99</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0196</v>
+        <v>-0.0145</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.5488</v>
+        <v>-0.406</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.72</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3218</v>
+        <v>-0.3049</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.010400000000001</v>
+        <v>-8.5372</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3769</v>
+        <v>-0.3639</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.5532</v>
+        <v>-10.1892</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.78</v>
       </c>
       <c r="I67" t="n">
-        <v>1.468</v>
+        <v>1.5003</v>
       </c>
       <c r="J67" t="n">
-        <v>41.104</v>
+        <v>42.0084</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.54</v>
       </c>
       <c r="I68" t="n">
-        <v>1.154</v>
+        <v>1.1671</v>
       </c>
       <c r="J68" t="n">
-        <v>32.312</v>
+        <v>32.6788</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.22</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5855</v>
+        <v>0.5532</v>
       </c>
       <c r="J69" t="n">
-        <v>16.394</v>
+        <v>15.4896</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.629</v>
+        <v>-0.596</v>
       </c>
       <c r="J70" t="n">
-        <v>-17.612</v>
+        <v>-16.688</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6968</v>
+        <v>-0.6683</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.5104</v>
+        <v>-18.7124</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4136</v>
+        <v>0.4126</v>
       </c>
       <c r="J72" t="n">
-        <v>9.926399999999999</v>
+        <v>9.9024</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.23</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3758</v>
+        <v>0.3701</v>
       </c>
       <c r="J73" t="n">
-        <v>9.0192</v>
+        <v>8.882400000000001</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.14</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2542</v>
+        <v>0.2395</v>
       </c>
       <c r="J74" t="n">
-        <v>6.1008</v>
+        <v>5.748</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.254</v>
+        <v>-0.2343</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.096</v>
+        <v>-5.6232</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3856</v>
+        <v>-0.3742</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.2544</v>
+        <v>-8.9808</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>0.603</v>
+        <v>0.5661</v>
       </c>
       <c r="J77" t="n">
-        <v>14.472</v>
+        <v>13.5864</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.36</v>
       </c>
       <c r="I78" t="n">
-        <v>0.477</v>
+        <v>0.4226</v>
       </c>
       <c r="J78" t="n">
-        <v>11.448</v>
+        <v>10.1424</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.99</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0336</v>
+        <v>-0.0245</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.8064</v>
+        <v>-0.588</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.91</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1452</v>
+        <v>-0.1255</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.4848</v>
+        <v>-3.012</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2623</v>
+        <v>-0.2435</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.2952</v>
+        <v>-5.844</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.74</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2157</v>
+        <v>1.2139</v>
       </c>
       <c r="J82" t="n">
-        <v>18.2355</v>
+        <v>18.2085</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.72</v>
       </c>
       <c r="I83" t="n">
-        <v>1.1913</v>
+        <v>1.1884</v>
       </c>
       <c r="J83" t="n">
-        <v>17.8695</v>
+        <v>17.826</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.39</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7723</v>
+        <v>0.7654</v>
       </c>
       <c r="J84" t="n">
-        <v>11.5845</v>
+        <v>11.481</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.38</v>
       </c>
       <c r="I85" t="n">
-        <v>0.7584</v>
+        <v>0.7518</v>
       </c>
       <c r="J85" t="n">
-        <v>11.376</v>
+        <v>11.277</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.18</v>
       </c>
       <c r="I86" t="n">
-        <v>0.4541</v>
+        <v>0.4302</v>
       </c>
       <c r="J86" t="n">
-        <v>6.8115</v>
+        <v>6.453</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.9</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0849</v>
+        <v>-0.0624</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.2735</v>
+        <v>-0.9360000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.75</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2549</v>
+        <v>-0.2412</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.8235</v>
+        <v>-3.618</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.6</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3945</v>
+        <v>-0.3862</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.9175</v>
+        <v>-5.793</v>
       </c>
     </row>
     <row r="90">
@@ -5989,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6311</v>
+        <v>-0.6478</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.4665</v>
+        <v>-9.717000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.79</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3346</v>
+        <v>1.3427</v>
       </c>
       <c r="J92" t="n">
-        <v>30.6958</v>
+        <v>30.8821</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.39</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7996</v>
+        <v>0.7843</v>
       </c>
       <c r="J93" t="n">
-        <v>18.3908</v>
+        <v>18.0389</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5162</v>
+        <v>0.5071</v>
       </c>
       <c r="J94" t="n">
-        <v>11.8726</v>
+        <v>11.6633</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2808</v>
+        <v>0.2492</v>
       </c>
       <c r="J95" t="n">
-        <v>6.4584</v>
+        <v>5.7316</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.62</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.0124</v>
+        <v>-1.0166</v>
       </c>
       <c r="J96" t="n">
-        <v>-23.2852</v>
+        <v>-23.3818</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3818</v>
+        <v>0.327</v>
       </c>
       <c r="J97" t="n">
-        <v>8.7814</v>
+        <v>7.521</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3635</v>
+        <v>0.3095</v>
       </c>
       <c r="J98" t="n">
-        <v>8.3605</v>
+        <v>7.1185</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3449</v>
+        <v>0.2918</v>
       </c>
       <c r="J99" t="n">
-        <v>7.9327</v>
+        <v>6.7114</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.68</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3593</v>
+        <v>-0.3449</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.2639</v>
+        <v>-7.9327</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.51</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5089</v>
+        <v>-0.5108</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.7047</v>
+        <v>-11.7484</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>2.39</v>
       </c>
       <c r="I102" t="n">
-        <v>1.9744</v>
+        <v>2.0495</v>
       </c>
       <c r="J102" t="n">
-        <v>35.5392</v>
+        <v>36.891</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.7</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1709</v>
+        <v>1.1666</v>
       </c>
       <c r="J103" t="n">
-        <v>21.0762</v>
+        <v>20.9988</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4911</v>
+        <v>0.4805</v>
       </c>
       <c r="J104" t="n">
-        <v>8.8398</v>
+        <v>8.648999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0273</v>
+        <v>0.0074</v>
       </c>
       <c r="J105" t="n">
-        <v>0.4914</v>
+        <v>0.1332</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.96</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2452</v>
+        <v>-0.2168</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.4136</v>
+        <v>-3.9024</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.38</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7128</v>
+        <v>0.6948</v>
       </c>
       <c r="J107" t="n">
-        <v>12.8304</v>
+        <v>12.5064</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0871</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>1.5678</v>
+        <v>1.2258</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.72</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3089</v>
+        <v>-0.2921</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.5602</v>
+        <v>-5.2578</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.52</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.488</v>
+        <v>-0.4856</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.784000000000001</v>
+        <v>-8.7408</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.36</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6247</v>
+        <v>-0.6434</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.2446</v>
+        <v>-11.5812</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.6</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6947</v>
+        <v>0.7381</v>
       </c>
       <c r="J112" t="n">
-        <v>16.6728</v>
+        <v>17.7144</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3104</v>
+        <v>0.3005</v>
       </c>
       <c r="J113" t="n">
-        <v>7.4496</v>
+        <v>7.212</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.14</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2435</v>
+        <v>0.2304</v>
       </c>
       <c r="J114" t="n">
-        <v>5.844</v>
+        <v>5.5296</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.99</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.033</v>
+        <v>-0.024</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.792</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.62</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4279</v>
+        <v>-0.422</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.2696</v>
+        <v>-10.128</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.24</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3606</v>
+        <v>0.2999</v>
       </c>
       <c r="J117" t="n">
-        <v>8.654400000000001</v>
+        <v>7.1976</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.14</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2349</v>
+        <v>0.1868</v>
       </c>
       <c r="J118" t="n">
-        <v>5.6376</v>
+        <v>4.4832</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.04</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0877</v>
+        <v>0.0639</v>
       </c>
       <c r="J119" t="n">
-        <v>2.1048</v>
+        <v>1.5336</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0497</v>
+        <v>0.0345</v>
       </c>
       <c r="J120" t="n">
-        <v>1.1928</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.9</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1528</v>
+        <v>-0.1327</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.6672</v>
+        <v>-3.1848</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.78</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3071</v>
+        <v>1.3112</v>
       </c>
       <c r="J122" t="n">
-        <v>26.142</v>
+        <v>26.224</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.74</v>
       </c>
       <c r="I123" t="n">
-        <v>1.2565</v>
+        <v>1.2569</v>
       </c>
       <c r="J123" t="n">
-        <v>25.13</v>
+        <v>25.138</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2719</v>
+        <v>0.2409</v>
       </c>
       <c r="J124" t="n">
-        <v>5.438</v>
+        <v>4.818</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.89</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4186</v>
+        <v>-0.3795</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.372</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4946</v>
+        <v>-0.4569</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.891999999999999</v>
+        <v>-9.138</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.15</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3838</v>
+        <v>0.3316</v>
       </c>
       <c r="J127" t="n">
-        <v>7.676</v>
+        <v>6.632</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.85</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1895</v>
+        <v>-0.171</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.79</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1895</v>
+        <v>-0.171</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.79</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.78</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2588</v>
+        <v>-0.2398</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.176</v>
+        <v>-4.796</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3527</v>
+        <v>-0.3376</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.054</v>
+        <v>-6.752</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.82</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3408</v>
+        <v>1.3464</v>
       </c>
       <c r="J132" t="n">
-        <v>25.4752</v>
+        <v>25.5816</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.47</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8922</v>
+        <v>0.8793</v>
       </c>
       <c r="J133" t="n">
-        <v>16.9518</v>
+        <v>16.7067</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.46</v>
       </c>
       <c r="I134" t="n">
-        <v>0.8787</v>
+        <v>0.8659</v>
       </c>
       <c r="J134" t="n">
-        <v>16.6953</v>
+        <v>16.4521</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.09</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2613</v>
+        <v>0.2302</v>
       </c>
       <c r="J135" t="n">
-        <v>4.9647</v>
+        <v>4.3738</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5292</v>
+        <v>-0.4946</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.0548</v>
+        <v>-9.397399999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.08</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2553</v>
+        <v>0.2118</v>
       </c>
       <c r="J137" t="n">
-        <v>4.8507</v>
+        <v>4.0242</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1664</v>
+        <v>-0.1496</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.1616</v>
+        <v>-2.8424</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2266</v>
+        <v>-0.2083</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.3054</v>
+        <v>-3.9577</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2362</v>
+        <v>-0.2179</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.4878</v>
+        <v>-4.1401</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4387</v>
+        <v>-0.4309</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.3353</v>
+        <v>-8.187099999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.8</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3152</v>
+        <v>1.3188</v>
       </c>
       <c r="J142" t="n">
-        <v>26.304</v>
+        <v>26.376</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.5</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9317</v>
+        <v>0.9191</v>
       </c>
       <c r="J143" t="n">
-        <v>18.634</v>
+        <v>18.382</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.33</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7005</v>
+        <v>0.6912</v>
       </c>
       <c r="J144" t="n">
-        <v>14.01</v>
+        <v>13.824</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4525</v>
+        <v>0.4277</v>
       </c>
       <c r="J145" t="n">
-        <v>9.050000000000001</v>
+        <v>8.554</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3764</v>
+        <v>-0.3394</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.528</v>
+        <v>-6.788</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.21</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4851</v>
+        <v>0.4497</v>
       </c>
       <c r="J147" t="n">
-        <v>9.702</v>
+        <v>8.994</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.95</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0722</v>
+        <v>-0.0602</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.444</v>
+        <v>-1.204</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.78</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2566</v>
+        <v>-0.238</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.132</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3411</v>
+        <v>-0.3254</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.822</v>
+        <v>-6.508</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4488</v>
+        <v>-0.4421</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.976000000000001</v>
+        <v>-8.842000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6057</v>
+        <v>0.5796</v>
       </c>
       <c r="J152" t="n">
-        <v>14.5368</v>
+        <v>13.9104</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2033</v>
+        <v>0.1614</v>
       </c>
       <c r="J153" t="n">
-        <v>4.8792</v>
+        <v>3.8736</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.87</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1747</v>
+        <v>-0.1549</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.1928</v>
+        <v>-3.7176</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2466</v>
+        <v>-0.2267</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.9184</v>
+        <v>-5.4408</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.62</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4142</v>
+        <v>-0.4048</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.940799999999999</v>
+        <v>-9.715199999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.37</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.784</v>
       </c>
       <c r="J157" t="n">
-        <v>19.1976</v>
+        <v>18.816</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.24</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5987</v>
+        <v>0.5859</v>
       </c>
       <c r="J158" t="n">
-        <v>14.3688</v>
+        <v>14.0616</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.96</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1826</v>
+        <v>-0.1485</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.3824</v>
+        <v>-3.564</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2448</v>
+        <v>-0.2062</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.8752</v>
+        <v>-4.9488</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4347</v>
+        <v>-0.3918</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.4328</v>
+        <v>-9.4032</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.34</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4562</v>
+        <v>0.3966</v>
       </c>
       <c r="J162" t="n">
-        <v>10.4926</v>
+        <v>9.1218</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.27</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3846</v>
+        <v>0.323</v>
       </c>
       <c r="J163" t="n">
-        <v>8.845800000000001</v>
+        <v>7.429</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1884</v>
+        <v>0.1487</v>
       </c>
       <c r="J164" t="n">
-        <v>4.3332</v>
+        <v>3.4201</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.1</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1743</v>
+        <v>0.1368</v>
       </c>
       <c r="J165" t="n">
-        <v>4.0089</v>
+        <v>3.1464</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1113</v>
+        <v>-0.0935</v>
       </c>
       <c r="J166" t="n">
-        <v>-2.5599</v>
+        <v>-2.1505</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.23</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3726</v>
+        <v>0.3666</v>
       </c>
       <c r="J167" t="n">
-        <v>8.569800000000001</v>
+        <v>8.431800000000001</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2229</v>
+        <v>0.2073</v>
       </c>
       <c r="J168" t="n">
-        <v>5.1267</v>
+        <v>4.7679</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.04</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0945</v>
+        <v>0.0809</v>
       </c>
       <c r="J169" t="n">
-        <v>2.1735</v>
+        <v>1.8607</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.99</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0275</v>
+        <v>-0.0195</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.6325</v>
+        <v>-0.4485</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2556</v>
+        <v>-0.236</v>
       </c>
       <c r="J171" t="n">
-        <v>-5.8788</v>
+        <v>-5.428</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.35</v>
       </c>
       <c r="I172" t="n">
-        <v>0.608</v>
+        <v>0.5794</v>
       </c>
       <c r="J172" t="n">
-        <v>14.592</v>
+        <v>13.9056</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2862</v>
+        <v>0.2371</v>
       </c>
       <c r="J173" t="n">
-        <v>6.8688</v>
+        <v>5.6904</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.05</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1445</v>
+        <v>0.1117</v>
       </c>
       <c r="J174" t="n">
-        <v>3.468</v>
+        <v>2.6808</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1716</v>
+        <v>-0.1511</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.1184</v>
+        <v>-3.6264</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3221</v>
+        <v>-0.3057</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.7304</v>
+        <v>-7.3368</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.4</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8299</v>
+        <v>0.8139</v>
       </c>
       <c r="J177" t="n">
-        <v>19.9176</v>
+        <v>19.5336</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.32</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7117</v>
+        <v>0.6963</v>
       </c>
       <c r="J178" t="n">
-        <v>17.0808</v>
+        <v>16.7112</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.02</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0789</v>
+        <v>0.0621</v>
       </c>
       <c r="J179" t="n">
-        <v>1.8936</v>
+        <v>1.4904</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.98</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1234</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.9616</v>
+        <v>-2.3088</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1938</v>
+        <v>-0.1591</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.6512</v>
+        <v>-3.8184</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.14</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3927</v>
+        <v>0.3459</v>
       </c>
       <c r="J182" t="n">
-        <v>6.6759</v>
+        <v>5.8803</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.93</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0911</v>
+        <v>-0.0775</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.5487</v>
+        <v>-1.3175</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.77</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2615</v>
+        <v>-0.2443</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.4455</v>
+        <v>-4.1531</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.61</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4079</v>
+        <v>-0.397</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.9343</v>
+        <v>-6.749</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.5</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.5041</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.576499999999999</v>
+        <v>-8.569699999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.6</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0648</v>
+        <v>1.0549</v>
       </c>
       <c r="J187" t="n">
-        <v>18.1016</v>
+        <v>17.9333</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8118</v>
+        <v>0.7992</v>
       </c>
       <c r="J188" t="n">
-        <v>13.8006</v>
+        <v>13.5864</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.31</v>
       </c>
       <c r="I189" t="n">
-        <v>0.673</v>
+        <v>0.6644</v>
       </c>
       <c r="J189" t="n">
-        <v>11.441</v>
+        <v>11.2948</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.3</v>
       </c>
       <c r="I190" t="n">
-        <v>0.6586</v>
+        <v>0.6506</v>
       </c>
       <c r="J190" t="n">
-        <v>11.1962</v>
+        <v>11.0602</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.03</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0824</v>
+        <v>0.0612</v>
       </c>
       <c r="J191" t="n">
-        <v>1.4008</v>
+        <v>1.0404</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.62</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6682</v>
+        <v>0.6257</v>
       </c>
       <c r="J192" t="n">
-        <v>14.0322</v>
+        <v>13.1397</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.38</v>
       </c>
       <c r="I193" t="n">
-        <v>0.486</v>
+        <v>0.4345</v>
       </c>
       <c r="J193" t="n">
-        <v>10.206</v>
+        <v>9.124499999999999</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.039</v>
+        <v>0.0265</v>
       </c>
       <c r="J194" t="n">
-        <v>0.819</v>
+        <v>0.5565</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1135</v>
+        <v>-0.0958</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.3835</v>
+        <v>-2.0118</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1135</v>
+        <v>-0.0958</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.3835</v>
+        <v>-2.0118</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2794</v>
+        <v>0.266</v>
       </c>
       <c r="J197" t="n">
-        <v>5.8674</v>
+        <v>5.586</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.08</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1731</v>
+        <v>0.1558</v>
       </c>
       <c r="J198" t="n">
-        <v>3.6351</v>
+        <v>3.2718</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.04</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1033</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J199" t="n">
-        <v>2.1693</v>
+        <v>1.8375</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.88</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1653</v>
+        <v>-0.1455</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.4713</v>
+        <v>-3.0555</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.62</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4157</v>
+        <v>-0.4066</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.729699999999999</v>
+        <v>-8.538600000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.98</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0173</v>
+        <v>-0.0095</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.3287</v>
+        <v>-0.1805</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.93</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0897</v>
+        <v>-0.0762</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.7043</v>
+        <v>-1.4478</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.77</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2609</v>
+        <v>-0.2439</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.9571</v>
+        <v>-4.6341</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.66</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.362</v>
+        <v>-0.3479</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.878</v>
+        <v>-6.6101</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.57</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4424</v>
+        <v>-0.4348</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.4056</v>
+        <v>-8.261200000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.68</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1632</v>
+        <v>1.1575</v>
       </c>
       <c r="J207" t="n">
-        <v>22.1008</v>
+        <v>21.9925</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.68</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1632</v>
+        <v>1.1575</v>
       </c>
       <c r="J208" t="n">
-        <v>22.1008</v>
+        <v>21.9925</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.33</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6998</v>
+        <v>0.6909</v>
       </c>
       <c r="J209" t="n">
-        <v>13.2962</v>
+        <v>13.1271</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.17</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4513</v>
+        <v>0.4263</v>
       </c>
       <c r="J210" t="n">
-        <v>8.5747</v>
+        <v>8.0997</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.9</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4047</v>
+        <v>-0.368</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.6893</v>
+        <v>-6.992</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.06</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1863</v>
+        <v>0.1465</v>
       </c>
       <c r="J212" t="n">
-        <v>4.4712</v>
+        <v>3.516</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.03</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1143</v>
+        <v>0.0848</v>
       </c>
       <c r="J213" t="n">
-        <v>2.7432</v>
+        <v>2.0352</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1143</v>
+        <v>0.0848</v>
       </c>
       <c r="J214" t="n">
-        <v>2.7432</v>
+        <v>2.0352</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.77</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2738</v>
+        <v>-0.2547</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.5712</v>
+        <v>-6.1128</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.349</v>
+        <v>-0.3338</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.375999999999999</v>
+        <v>-8.011200000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.55</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0375</v>
+        <v>1.0272</v>
       </c>
       <c r="J217" t="n">
-        <v>24.9</v>
+        <v>24.6528</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.14</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4158</v>
+        <v>0.3796</v>
       </c>
       <c r="J218" t="n">
-        <v>9.979200000000001</v>
+        <v>9.1104</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.07</v>
       </c>
       <c r="I219" t="n">
-        <v>0.237</v>
+        <v>0.2061</v>
       </c>
       <c r="J219" t="n">
-        <v>5.688</v>
+        <v>4.9464</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.04</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1465</v>
+        <v>0.122</v>
       </c>
       <c r="J220" t="n">
-        <v>3.516</v>
+        <v>2.928</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2283</v>
+        <v>-0.1913</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.4792</v>
+        <v>-4.5912</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.21</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5284</v>
+        <v>0.5198</v>
       </c>
       <c r="J222" t="n">
-        <v>8.982799999999999</v>
+        <v>8.836600000000001</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.73</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2931</v>
+        <v>-0.2782</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.9827</v>
+        <v>-4.7294</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.6</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.4088</v>
+        <v>-0.3983</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.9496</v>
+        <v>-6.7711</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.54</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4619</v>
+        <v>-0.4561</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.8523</v>
+        <v>-7.7537</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.54</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4619</v>
+        <v>-0.4561</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.8523</v>
+        <v>-7.7537</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>2.34</v>
       </c>
       <c r="I227" t="n">
-        <v>1.9136</v>
+        <v>1.9789</v>
       </c>
       <c r="J227" t="n">
-        <v>32.5312</v>
+        <v>33.6413</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.59</v>
       </c>
       <c r="I228" t="n">
-        <v>1.0314</v>
+        <v>1.0235</v>
       </c>
       <c r="J228" t="n">
-        <v>17.5338</v>
+        <v>17.3995</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.31</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6595</v>
+        <v>0.6548</v>
       </c>
       <c r="J229" t="n">
-        <v>11.2115</v>
+        <v>11.1316</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.21</v>
       </c>
       <c r="I230" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4992</v>
       </c>
       <c r="J230" t="n">
-        <v>8.593500000000001</v>
+        <v>8.4864</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.91</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3947</v>
+        <v>-0.362</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.7099</v>
+        <v>-6.154</v>
       </c>
     </row>
   </sheetData>
